--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_educacion.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_educacion.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="datos" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="metadatos" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="datos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="metadatos" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -54,6 +54,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -346,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q331"/>
+  <dimension ref="A1:Q334"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,7 +575,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -582,7 +650,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -657,7 +725,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -732,7 +800,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -807,7 +875,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -882,7 +950,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -957,7 +1025,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -1032,7 +1100,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1175,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -1182,7 +1250,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -1257,7 +1325,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -1332,7 +1400,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -1407,7 +1475,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1550,7 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1625,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -1632,7 +1700,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -1707,7 +1775,7 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -1782,7 +1850,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -1857,7 +1925,7 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -1932,7 +2000,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -2007,7 +2075,7 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2153,7 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -2160,7 +2228,7 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -2235,7 +2303,7 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -2310,7 +2378,7 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -2385,7 +2453,7 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -2460,7 +2528,7 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -2535,7 +2603,7 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2678,7 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -2685,7 +2753,7 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -2763,7 +2831,7 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -2838,7 +2906,7 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -2913,7 +2981,7 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -2988,7 +3056,7 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -3063,7 +3131,7 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3206,7 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -3213,7 +3281,7 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -3288,7 +3356,7 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -3363,7 +3431,7 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -3438,7 +3506,7 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -3513,7 +3581,7 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -3591,7 +3659,7 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -3666,7 +3734,7 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -3741,7 +3809,7 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -3816,7 +3884,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3962,7 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -3972,7 +4040,7 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -4050,7 +4118,7 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -4128,7 +4196,7 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -4206,7 +4274,7 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -4284,7 +4352,7 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -4362,7 +4430,7 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4508,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -4515,7 +4583,7 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -4590,7 +4658,7 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4736,7 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -4746,7 +4814,7 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -4824,7 +4892,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -4899,7 +4967,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -4974,7 +5042,7 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -5049,7 +5117,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -5124,7 +5192,7 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -5199,7 +5267,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -5274,7 +5342,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -5349,7 +5417,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -5424,7 +5492,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -5499,7 +5567,12 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -5574,7 +5647,12 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -5649,7 +5727,12 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -5724,7 +5807,12 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -5799,7 +5887,12 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -5874,7 +5967,12 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -5949,7 +6047,12 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -6024,7 +6127,12 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -6099,7 +6207,12 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -6174,7 +6287,12 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -6249,7 +6367,12 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -6317,9 +6440,6 @@
           <t>Tasa bruta de escolarización primaria</t>
         </is>
       </c>
-      <c r="N79" t="n">
-        <v>89.086311340332</v>
-      </c>
       <c r="O79" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -6327,7 +6447,12 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -6395,9 +6520,6 @@
           <t>Tasa bruta de escolarización primaria</t>
         </is>
       </c>
-      <c r="N80" t="n">
-        <v>90.5719680786133</v>
-      </c>
       <c r="O80" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -6405,7 +6527,12 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -6473,9 +6600,6 @@
           <t>Tasa bruta de escolarización primaria</t>
         </is>
       </c>
-      <c r="N81" t="n">
-        <v>91.3041534423828</v>
-      </c>
       <c r="O81" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -6483,7 +6607,12 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -6551,9 +6680,6 @@
           <t>Tasa bruta de escolarización primaria</t>
         </is>
       </c>
-      <c r="N82" t="n">
-        <v>90.82086181640619</v>
-      </c>
       <c r="O82" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -6561,7 +6687,12 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -6629,9 +6760,6 @@
           <t>Tasa bruta de escolarización primaria</t>
         </is>
       </c>
-      <c r="N83" t="n">
-        <v>92.03941345214839</v>
-      </c>
       <c r="O83" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -6639,7 +6767,12 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -6707,9 +6840,6 @@
           <t>Tasa bruta de escolarización primaria</t>
         </is>
       </c>
-      <c r="N84" t="n">
-        <v>95.639892578125</v>
-      </c>
       <c r="O84" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -6717,7 +6847,12 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -6785,9 +6920,6 @@
           <t>Tasa bruta de escolarización primaria</t>
         </is>
       </c>
-      <c r="N85" t="n">
-        <v>98.1688766479492</v>
-      </c>
       <c r="O85" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -6795,7 +6927,12 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -6863,9 +7000,6 @@
           <t>Tasa bruta de escolarización primaria</t>
         </is>
       </c>
-      <c r="N86" t="n">
-        <v>101.076736450195</v>
-      </c>
       <c r="O86" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -6873,7 +7007,12 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -6941,9 +7080,6 @@
           <t>Tasa bruta de escolarización primaria</t>
         </is>
       </c>
-      <c r="N87" t="n">
-        <v>102.413162231445</v>
-      </c>
       <c r="O87" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -6951,7 +7087,12 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -7019,9 +7160,6 @@
           <t>Tasa bruta de escolarización primaria</t>
         </is>
       </c>
-      <c r="N88" t="n">
-        <v>104.085968017578</v>
-      </c>
       <c r="O88" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -7029,7 +7167,12 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -7097,9 +7240,6 @@
           <t>Tasa bruta de escolarización primaria</t>
         </is>
       </c>
-      <c r="N89" t="n">
-        <v>105.414100646973</v>
-      </c>
       <c r="O89" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -7107,7 +7247,12 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -7175,9 +7320,6 @@
           <t>Tasa bruta de escolarización primaria</t>
         </is>
       </c>
-      <c r="N90" t="n">
-        <v>106.078842163086</v>
-      </c>
       <c r="O90" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -7185,7 +7327,12 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -7253,9 +7400,6 @@
           <t>Tasa bruta de escolarización primaria</t>
         </is>
       </c>
-      <c r="N91" t="n">
-        <v>105.254440307617</v>
-      </c>
       <c r="O91" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -7263,7 +7407,12 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -7331,9 +7480,6 @@
           <t>Tasa bruta de escolarización primaria</t>
         </is>
       </c>
-      <c r="N92" t="n">
-        <v>103.982536315918</v>
-      </c>
       <c r="O92" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -7341,7 +7487,12 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -7409,9 +7560,6 @@
           <t>Tasa bruta de escolarización primaria</t>
         </is>
       </c>
-      <c r="N93" t="n">
-        <v>104.39527130127</v>
-      </c>
       <c r="O93" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -7419,7 +7567,12 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -7487,9 +7640,6 @@
           <t>Tasa bruta de escolarización primaria</t>
         </is>
       </c>
-      <c r="N94" t="n">
-        <v>104.340309143066</v>
-      </c>
       <c r="O94" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -7497,7 +7647,12 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -7565,9 +7720,6 @@
           <t>Tasa bruta de escolarización primaria</t>
         </is>
       </c>
-      <c r="N95" t="n">
-        <v>103.786468505859</v>
-      </c>
       <c r="O95" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -7575,7 +7727,12 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -7643,9 +7800,6 @@
           <t>Tasa bruta de escolarización primaria</t>
         </is>
       </c>
-      <c r="N96" t="n">
-        <v>103.345626831055</v>
-      </c>
       <c r="O96" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -7653,7 +7807,12 @@
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -7721,9 +7880,6 @@
           <t>Tasa bruta de escolarización primaria</t>
         </is>
       </c>
-      <c r="N97" t="n">
-        <v>102.946510314941</v>
-      </c>
       <c r="O97" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -7731,7 +7887,12 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -7799,9 +7960,6 @@
           <t>Tasa bruta de escolarización primaria</t>
         </is>
       </c>
-      <c r="N98" t="n">
-        <v>103.632537841797</v>
-      </c>
       <c r="O98" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -7809,7 +7967,12 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -7877,9 +8040,6 @@
           <t>Tasa bruta de escolarización primaria</t>
         </is>
       </c>
-      <c r="N99" t="n">
-        <v>107.00602722168</v>
-      </c>
       <c r="O99" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -7887,7 +8047,12 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -7955,9 +8120,6 @@
           <t>Tasa bruta de escolarización primaria</t>
         </is>
       </c>
-      <c r="N100" t="n">
-        <v>108.725692749023</v>
-      </c>
       <c r="O100" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -7965,7 +8127,12 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -8033,9 +8200,6 @@
           <t>Tasa bruta de escolarización primaria</t>
         </is>
       </c>
-      <c r="N101" t="n">
-        <v>107.152236938477</v>
-      </c>
       <c r="O101" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -8043,7 +8207,12 @@
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -8118,7 +8287,12 @@
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -8193,7 +8367,12 @@
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -8261,9 +8440,6 @@
           <t>Tasa bruta de escolarización primaria</t>
         </is>
       </c>
-      <c r="N104" t="n">
-        <v>98.7612991333008</v>
-      </c>
       <c r="O104" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -8271,7 +8447,12 @@
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -8339,9 +8520,6 @@
           <t>Tasa bruta de escolarización primaria</t>
         </is>
       </c>
-      <c r="N105" t="n">
-        <v>100.005096435547</v>
-      </c>
       <c r="O105" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -8349,7 +8527,12 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -8424,7 +8607,12 @@
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -8492,9 +8680,6 @@
           <t>Tasa bruta de escolarización primaria</t>
         </is>
       </c>
-      <c r="N107" t="n">
-        <v>98.338996887207</v>
-      </c>
       <c r="O107" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -8502,7 +8687,12 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q107" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -8570,9 +8760,6 @@
           <t>Tasa bruta de escolarización primaria</t>
         </is>
       </c>
-      <c r="N108" t="n">
-        <v>99.864990234375</v>
-      </c>
       <c r="O108" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -8580,7 +8767,12 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q108" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -8648,9 +8840,6 @@
           <t>Tasa bruta de escolarización primaria</t>
         </is>
       </c>
-      <c r="N109" t="n">
-        <v>102.415657043457</v>
-      </c>
       <c r="O109" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -8658,7 +8847,12 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q109" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -8726,9 +8920,6 @@
           <t>Tasa bruta de escolarización primaria</t>
         </is>
       </c>
-      <c r="N110" t="n">
-        <v>104.676307678223</v>
-      </c>
       <c r="O110" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -8736,7 +8927,12 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q110" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -8804,9 +9000,6 @@
           <t>Tasa bruta de escolarización primaria</t>
         </is>
       </c>
-      <c r="N111" t="n">
-        <v>102.77710723877</v>
-      </c>
       <c r="O111" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -8814,7 +9007,12 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q111" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -8882,9 +9080,6 @@
           <t>Tasa bruta de escolarización primaria</t>
         </is>
       </c>
-      <c r="N112" t="n">
-        <v>102.658088684082</v>
-      </c>
       <c r="O112" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -8892,7 +9087,12 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q112" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -8960,9 +9160,6 @@
           <t>Tasa bruta de escolarización primaria</t>
         </is>
       </c>
-      <c r="N113" t="n">
-        <v>102.275398254395</v>
-      </c>
       <c r="O113" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -8970,7 +9167,12 @@
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q113" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -9038,9 +9240,6 @@
           <t>Tasa bruta de escolarización primaria</t>
         </is>
       </c>
-      <c r="N114" t="n">
-        <v>102.063499450684</v>
-      </c>
       <c r="O114" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -9048,7 +9247,12 @@
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q114" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -9116,9 +9320,6 @@
           <t>Tasa bruta de escolarización primaria</t>
         </is>
       </c>
-      <c r="N115" t="n">
-        <v>103.891387939453</v>
-      </c>
       <c r="O115" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -9126,7 +9327,12 @@
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q115" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -9194,9 +9400,6 @@
           <t>Tasa bruta de escolarización primaria</t>
         </is>
       </c>
-      <c r="N116" t="n">
-        <v>101.032890319824</v>
-      </c>
       <c r="O116" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -9204,7 +9407,12 @@
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q116" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -9272,9 +9480,6 @@
           <t>Tasa bruta de escolarización primaria</t>
         </is>
       </c>
-      <c r="N117" t="n">
-        <v>101.235862731934</v>
-      </c>
       <c r="O117" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -9282,7 +9487,12 @@
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q117" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -9350,9 +9560,6 @@
           <t>Tasa bruta de escolarización primaria</t>
         </is>
       </c>
-      <c r="N118" t="n">
-        <v>100.685157775879</v>
-      </c>
       <c r="O118" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -9360,7 +9567,12 @@
       </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q118" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -9428,9 +9640,6 @@
           <t>Tasa bruta de escolarización primaria</t>
         </is>
       </c>
-      <c r="N119" t="n">
-        <v>100.664756774902</v>
-      </c>
       <c r="O119" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -9438,7 +9647,12 @@
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q119" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -9506,9 +9720,6 @@
           <t>Tasa bruta de escolarización primaria</t>
         </is>
       </c>
-      <c r="N120" t="n">
-        <v>100.787887573242</v>
-      </c>
       <c r="O120" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -9516,7 +9727,12 @@
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q120" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -9584,9 +9800,6 @@
           <t>Tasa bruta de escolarización primaria</t>
         </is>
       </c>
-      <c r="N121" t="n">
-        <v>101.162292480469</v>
-      </c>
       <c r="O121" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -9594,7 +9807,12 @@
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q121" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -9662,9 +9880,6 @@
           <t>Tasa bruta de escolarización primaria</t>
         </is>
       </c>
-      <c r="N122" t="n">
-        <v>100.276649475098</v>
-      </c>
       <c r="O122" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -9672,7 +9887,12 @@
       </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q122" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -9740,9 +9960,6 @@
           <t>Tasa bruta de escolarización primaria</t>
         </is>
       </c>
-      <c r="N123" t="n">
-        <v>99.8761825561523</v>
-      </c>
       <c r="O123" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -9750,7 +9967,12 @@
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q123" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -9818,9 +10040,6 @@
           <t>Tasa bruta de escolarización primaria</t>
         </is>
       </c>
-      <c r="N124" t="n">
-        <v>97.506591796875</v>
-      </c>
       <c r="O124" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -9828,7 +10047,12 @@
       </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q124" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -9896,9 +10120,6 @@
           <t>Tasa bruta de escolarización primaria</t>
         </is>
       </c>
-      <c r="N125" t="n">
-        <v>95.05072021484381</v>
-      </c>
       <c r="O125" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -9906,7 +10127,12 @@
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q125" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -9981,7 +10207,12 @@
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q126" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -10056,7 +10287,12 @@
       </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q127" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -10131,7 +10367,12 @@
       </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q128" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -10206,7 +10447,12 @@
       </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q129" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -10274,9 +10520,6 @@
           <t>Tasa bruta de escolarización primaria</t>
         </is>
       </c>
-      <c r="N130" t="n">
-        <v>109.259559631348</v>
-      </c>
       <c r="O130" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -10284,7 +10527,12 @@
       </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q130" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -10352,9 +10600,6 @@
           <t>Tasa bruta de escolarización primaria</t>
         </is>
       </c>
-      <c r="N131" t="n">
-        <v>111.130409240723</v>
-      </c>
       <c r="O131" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -10362,7 +10607,12 @@
       </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q131" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -10430,9 +10680,6 @@
           <t>Tasa bruta de escolarización primaria</t>
         </is>
       </c>
-      <c r="N132" t="n">
-        <v>113.693878173828</v>
-      </c>
       <c r="O132" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -10440,7 +10687,12 @@
       </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q132" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -10515,7 +10767,12 @@
       </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q133" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -10551,7 +10808,7 @@
         </is>
       </c>
       <c r="G134" t="n">
-        <v>1960</v>
+        <v>2026</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
@@ -10575,12 +10832,12 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>SE.SEC.ENRR</t>
+          <t>SE.PRM.ENRR</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Tasa bruta de escolarización secundaria</t>
+          <t>Tasa bruta de escolarización primaria</t>
         </is>
       </c>
       <c r="O134" t="inlineStr">
@@ -10590,7 +10847,12 @@
       </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q134" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -10626,7 +10888,7 @@
         </is>
       </c>
       <c r="G135" t="n">
-        <v>1961</v>
+        <v>1960</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
@@ -10665,7 +10927,12 @@
       </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q135" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -10701,7 +10968,7 @@
         </is>
       </c>
       <c r="G136" t="n">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
@@ -10740,7 +11007,12 @@
       </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q136" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -10776,7 +11048,7 @@
         </is>
       </c>
       <c r="G137" t="n">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
@@ -10815,7 +11087,12 @@
       </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q137" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -10851,7 +11128,7 @@
         </is>
       </c>
       <c r="G138" t="n">
-        <v>1964</v>
+        <v>1963</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
@@ -10890,7 +11167,12 @@
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q138" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -10926,7 +11208,7 @@
         </is>
       </c>
       <c r="G139" t="n">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
@@ -10965,7 +11247,12 @@
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q139" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -11001,7 +11288,7 @@
         </is>
       </c>
       <c r="G140" t="n">
-        <v>1966</v>
+        <v>1965</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
@@ -11040,7 +11327,12 @@
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q140" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -11076,7 +11368,7 @@
         </is>
       </c>
       <c r="G141" t="n">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
@@ -11115,7 +11407,12 @@
       </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q141" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -11151,7 +11448,7 @@
         </is>
       </c>
       <c r="G142" t="n">
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
@@ -11190,7 +11487,12 @@
       </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q142" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -11226,7 +11528,7 @@
         </is>
       </c>
       <c r="G143" t="n">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="H143" t="inlineStr">
         <is>
@@ -11265,7 +11567,12 @@
       </c>
       <c r="P143" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q143" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -11301,7 +11608,7 @@
         </is>
       </c>
       <c r="G144" t="n">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
@@ -11340,7 +11647,12 @@
       </c>
       <c r="P144" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q144" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -11376,7 +11688,7 @@
         </is>
       </c>
       <c r="G145" t="n">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="H145" t="inlineStr">
         <is>
@@ -11408,9 +11720,6 @@
           <t>Tasa bruta de escolarización secundaria</t>
         </is>
       </c>
-      <c r="N145" t="n">
-        <v>30.5217304229736</v>
-      </c>
       <c r="O145" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -11418,7 +11727,12 @@
       </c>
       <c r="P145" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q145" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -11454,7 +11768,7 @@
         </is>
       </c>
       <c r="G146" t="n">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
@@ -11486,9 +11800,6 @@
           <t>Tasa bruta de escolarización secundaria</t>
         </is>
       </c>
-      <c r="N146" t="n">
-        <v>33.1764907836914</v>
-      </c>
       <c r="O146" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -11496,7 +11807,12 @@
       </c>
       <c r="P146" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q146" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -11532,7 +11848,7 @@
         </is>
       </c>
       <c r="G147" t="n">
-        <v>1973</v>
+        <v>1972</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
@@ -11564,9 +11880,6 @@
           <t>Tasa bruta de escolarización secundaria</t>
         </is>
       </c>
-      <c r="N147" t="n">
-        <v>35.5657501220703</v>
-      </c>
       <c r="O147" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -11574,7 +11887,12 @@
       </c>
       <c r="P147" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q147" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -11610,7 +11928,7 @@
         </is>
       </c>
       <c r="G148" t="n">
-        <v>1974</v>
+        <v>1973</v>
       </c>
       <c r="H148" t="inlineStr">
         <is>
@@ -11642,9 +11960,6 @@
           <t>Tasa bruta de escolarización secundaria</t>
         </is>
       </c>
-      <c r="N148" t="n">
-        <v>37.7445297241211</v>
-      </c>
       <c r="O148" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -11652,7 +11967,12 @@
       </c>
       <c r="P148" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q148" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -11688,7 +12008,7 @@
         </is>
       </c>
       <c r="G149" t="n">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
@@ -11720,9 +12040,6 @@
           <t>Tasa bruta de escolarización secundaria</t>
         </is>
       </c>
-      <c r="N149" t="n">
-        <v>39.6757888793945</v>
-      </c>
       <c r="O149" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -11730,7 +12047,12 @@
       </c>
       <c r="P149" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q149" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -11766,7 +12088,7 @@
         </is>
       </c>
       <c r="G150" t="n">
-        <v>1976</v>
+        <v>1975</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
@@ -11798,9 +12120,6 @@
           <t>Tasa bruta de escolarización secundaria</t>
         </is>
       </c>
-      <c r="N150" t="n">
-        <v>43.916919708252</v>
-      </c>
       <c r="O150" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -11808,7 +12127,12 @@
       </c>
       <c r="P150" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q150" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -11844,7 +12168,7 @@
         </is>
       </c>
       <c r="G151" t="n">
-        <v>1977</v>
+        <v>1976</v>
       </c>
       <c r="H151" t="inlineStr">
         <is>
@@ -11876,9 +12200,6 @@
           <t>Tasa bruta de escolarización secundaria</t>
         </is>
       </c>
-      <c r="N151" t="n">
-        <v>46.5141181945801</v>
-      </c>
       <c r="O151" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -11886,7 +12207,12 @@
       </c>
       <c r="P151" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q151" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -11922,7 +12248,7 @@
         </is>
       </c>
       <c r="G152" t="n">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="H152" t="inlineStr">
         <is>
@@ -11954,9 +12280,6 @@
           <t>Tasa bruta de escolarización secundaria</t>
         </is>
       </c>
-      <c r="N152" t="n">
-        <v>47.7237510681152</v>
-      </c>
       <c r="O152" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -11964,7 +12287,12 @@
       </c>
       <c r="P152" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q152" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -12000,7 +12328,7 @@
         </is>
       </c>
       <c r="G153" t="n">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
@@ -12032,9 +12360,6 @@
           <t>Tasa bruta de escolarización secundaria</t>
         </is>
       </c>
-      <c r="N153" t="n">
-        <v>49.0558891296387</v>
-      </c>
       <c r="O153" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -12042,7 +12367,12 @@
       </c>
       <c r="P153" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q153" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -12078,7 +12408,7 @@
         </is>
       </c>
       <c r="G154" t="n">
-        <v>1980</v>
+        <v>1979</v>
       </c>
       <c r="H154" t="inlineStr">
         <is>
@@ -12110,9 +12440,6 @@
           <t>Tasa bruta de escolarización secundaria</t>
         </is>
       </c>
-      <c r="N154" t="n">
-        <v>50.0724411010742</v>
-      </c>
       <c r="O154" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -12120,7 +12447,12 @@
       </c>
       <c r="P154" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q154" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -12156,7 +12488,7 @@
         </is>
       </c>
       <c r="G155" t="n">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="H155" t="inlineStr">
         <is>
@@ -12188,9 +12520,6 @@
           <t>Tasa bruta de escolarización secundaria</t>
         </is>
       </c>
-      <c r="N155" t="n">
-        <v>50.6321105957031</v>
-      </c>
       <c r="O155" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -12198,7 +12527,12 @@
       </c>
       <c r="P155" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q155" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -12234,7 +12568,7 @@
         </is>
       </c>
       <c r="G156" t="n">
-        <v>1982</v>
+        <v>1981</v>
       </c>
       <c r="H156" t="inlineStr">
         <is>
@@ -12266,9 +12600,6 @@
           <t>Tasa bruta de escolarización secundaria</t>
         </is>
       </c>
-      <c r="N156" t="n">
-        <v>51.1844291687012</v>
-      </c>
       <c r="O156" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -12276,7 +12607,12 @@
       </c>
       <c r="P156" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q156" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -12312,7 +12648,7 @@
         </is>
       </c>
       <c r="G157" t="n">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="H157" t="inlineStr">
         <is>
@@ -12344,9 +12680,6 @@
           <t>Tasa bruta de escolarización secundaria</t>
         </is>
       </c>
-      <c r="N157" t="n">
-        <v>52.3728790283203</v>
-      </c>
       <c r="O157" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -12354,7 +12687,12 @@
       </c>
       <c r="P157" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q157" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -12390,7 +12728,7 @@
         </is>
       </c>
       <c r="G158" t="n">
-        <v>1984</v>
+        <v>1983</v>
       </c>
       <c r="H158" t="inlineStr">
         <is>
@@ -12422,9 +12760,6 @@
           <t>Tasa bruta de escolarización secundaria</t>
         </is>
       </c>
-      <c r="N158" t="n">
-        <v>53.0127182006836</v>
-      </c>
       <c r="O158" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -12432,7 +12767,12 @@
       </c>
       <c r="P158" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q158" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -12468,7 +12808,7 @@
         </is>
       </c>
       <c r="G159" t="n">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="H159" t="inlineStr">
         <is>
@@ -12500,9 +12840,6 @@
           <t>Tasa bruta de escolarización secundaria</t>
         </is>
       </c>
-      <c r="N159" t="n">
-        <v>54.5595817565918</v>
-      </c>
       <c r="O159" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -12510,7 +12847,12 @@
       </c>
       <c r="P159" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q159" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -12546,7 +12888,7 @@
         </is>
       </c>
       <c r="G160" t="n">
-        <v>1986</v>
+        <v>1985</v>
       </c>
       <c r="H160" t="inlineStr">
         <is>
@@ -12578,9 +12920,6 @@
           <t>Tasa bruta de escolarización secundaria</t>
         </is>
       </c>
-      <c r="N160" t="n">
-        <v>55.3031311035156</v>
-      </c>
       <c r="O160" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -12588,7 +12927,12 @@
       </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q160" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -12624,7 +12968,7 @@
         </is>
       </c>
       <c r="G161" t="n">
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="H161" t="inlineStr">
         <is>
@@ -12656,9 +13000,6 @@
           <t>Tasa bruta de escolarización secundaria</t>
         </is>
       </c>
-      <c r="N161" t="n">
-        <v>54.3160591125488</v>
-      </c>
       <c r="O161" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -12666,7 +13007,12 @@
       </c>
       <c r="P161" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q161" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -12702,7 +13048,7 @@
         </is>
       </c>
       <c r="G162" t="n">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="H162" t="inlineStr">
         <is>
@@ -12734,9 +13080,6 @@
           <t>Tasa bruta de escolarización secundaria</t>
         </is>
       </c>
-      <c r="N162" t="n">
-        <v>54.0853614807129</v>
-      </c>
       <c r="O162" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -12744,7 +13087,12 @@
       </c>
       <c r="P162" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q162" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -12780,7 +13128,7 @@
         </is>
       </c>
       <c r="G163" t="n">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="H163" t="inlineStr">
         <is>
@@ -12812,9 +13160,6 @@
           <t>Tasa bruta de escolarización secundaria</t>
         </is>
       </c>
-      <c r="N163" t="n">
-        <v>53.3951301574707</v>
-      </c>
       <c r="O163" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -12822,7 +13167,12 @@
       </c>
       <c r="P163" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q163" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -12858,7 +13208,7 @@
         </is>
       </c>
       <c r="G164" t="n">
-        <v>1990</v>
+        <v>1989</v>
       </c>
       <c r="H164" t="inlineStr">
         <is>
@@ -12890,9 +13240,6 @@
           <t>Tasa bruta de escolarización secundaria</t>
         </is>
       </c>
-      <c r="N164" t="n">
-        <v>53.3853302001953</v>
-      </c>
       <c r="O164" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -12900,7 +13247,12 @@
       </c>
       <c r="P164" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q164" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -12936,7 +13288,7 @@
         </is>
       </c>
       <c r="G165" t="n">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="H165" t="inlineStr">
         <is>
@@ -12968,9 +13320,6 @@
           <t>Tasa bruta de escolarización secundaria</t>
         </is>
       </c>
-      <c r="N165" t="n">
-        <v>53.7813987731934</v>
-      </c>
       <c r="O165" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -12978,7 +13327,12 @@
       </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q165" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -13014,7 +13368,7 @@
         </is>
       </c>
       <c r="G166" t="n">
-        <v>1992</v>
+        <v>1991</v>
       </c>
       <c r="H166" t="inlineStr">
         <is>
@@ -13046,9 +13400,6 @@
           <t>Tasa bruta de escolarización secundaria</t>
         </is>
       </c>
-      <c r="N166" t="n">
-        <v>54.664478302002</v>
-      </c>
       <c r="O166" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -13056,7 +13407,12 @@
       </c>
       <c r="P166" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q166" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -13092,7 +13448,7 @@
         </is>
       </c>
       <c r="G167" t="n">
-        <v>1993</v>
+        <v>1992</v>
       </c>
       <c r="H167" t="inlineStr">
         <is>
@@ -13124,9 +13480,6 @@
           <t>Tasa bruta de escolarización secundaria</t>
         </is>
       </c>
-      <c r="N167" t="n">
-        <v>55.1568489074707</v>
-      </c>
       <c r="O167" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -13134,7 +13487,12 @@
       </c>
       <c r="P167" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q167" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -13170,7 +13528,7 @@
         </is>
       </c>
       <c r="G168" t="n">
-        <v>1994</v>
+        <v>1993</v>
       </c>
       <c r="H168" t="inlineStr">
         <is>
@@ -13209,7 +13567,12 @@
       </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q168" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -13245,7 +13608,7 @@
         </is>
       </c>
       <c r="G169" t="n">
-        <v>1995</v>
+        <v>1994</v>
       </c>
       <c r="H169" t="inlineStr">
         <is>
@@ -13284,7 +13647,12 @@
       </c>
       <c r="P169" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q169" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -13320,7 +13688,7 @@
         </is>
       </c>
       <c r="G170" t="n">
-        <v>1996</v>
+        <v>1995</v>
       </c>
       <c r="H170" t="inlineStr">
         <is>
@@ -13359,7 +13727,12 @@
       </c>
       <c r="P170" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q170" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -13395,7 +13768,7 @@
         </is>
       </c>
       <c r="G171" t="n">
-        <v>1997</v>
+        <v>1996</v>
       </c>
       <c r="H171" t="inlineStr">
         <is>
@@ -13434,7 +13807,12 @@
       </c>
       <c r="P171" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q171" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -13470,7 +13848,7 @@
         </is>
       </c>
       <c r="G172" t="n">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="H172" t="inlineStr">
         <is>
@@ -13509,7 +13887,12 @@
       </c>
       <c r="P172" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q172" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -13545,7 +13928,7 @@
         </is>
       </c>
       <c r="G173" t="n">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="H173" t="inlineStr">
         <is>
@@ -13577,9 +13960,6 @@
           <t>Tasa bruta de escolarización secundaria</t>
         </is>
       </c>
-      <c r="N173" t="n">
-        <v>56.0293006896973</v>
-      </c>
       <c r="O173" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -13587,7 +13967,12 @@
       </c>
       <c r="P173" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q173" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -13623,7 +14008,7 @@
         </is>
       </c>
       <c r="G174" t="n">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="H174" t="inlineStr">
         <is>
@@ -13655,9 +14040,6 @@
           <t>Tasa bruta de escolarización secundaria</t>
         </is>
       </c>
-      <c r="N174" t="n">
-        <v>59.0772895812988</v>
-      </c>
       <c r="O174" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -13665,7 +14047,12 @@
       </c>
       <c r="P174" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q174" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -13701,7 +14088,7 @@
         </is>
       </c>
       <c r="G175" t="n">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="H175" t="inlineStr">
         <is>
@@ -13733,9 +14120,6 @@
           <t>Tasa bruta de escolarización secundaria</t>
         </is>
       </c>
-      <c r="N175" t="n">
-        <v>63.1789817810059</v>
-      </c>
       <c r="O175" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -13743,7 +14127,12 @@
       </c>
       <c r="P175" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q175" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -13779,7 +14168,7 @@
         </is>
       </c>
       <c r="G176" t="n">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="H176" t="inlineStr">
         <is>
@@ -13811,9 +14200,6 @@
           <t>Tasa bruta de escolarización secundaria</t>
         </is>
       </c>
-      <c r="N176" t="n">
-        <v>67.2197189331055</v>
-      </c>
       <c r="O176" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -13821,7 +14207,12 @@
       </c>
       <c r="P176" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q176" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -13857,7 +14248,7 @@
         </is>
       </c>
       <c r="G177" t="n">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="H177" t="inlineStr">
         <is>
@@ -13889,9 +14280,6 @@
           <t>Tasa bruta de escolarización secundaria</t>
         </is>
       </c>
-      <c r="N177" t="n">
-        <v>68.4049072265625</v>
-      </c>
       <c r="O177" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -13899,7 +14287,12 @@
       </c>
       <c r="P177" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q177" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -13935,7 +14328,7 @@
         </is>
       </c>
       <c r="G178" t="n">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="H178" t="inlineStr">
         <is>
@@ -13967,9 +14360,6 @@
           <t>Tasa bruta de escolarización secundaria</t>
         </is>
       </c>
-      <c r="N178" t="n">
-        <v>71.01963806152339</v>
-      </c>
       <c r="O178" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -13977,7 +14367,12 @@
       </c>
       <c r="P178" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q178" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -14013,7 +14408,7 @@
         </is>
       </c>
       <c r="G179" t="n">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="H179" t="inlineStr">
         <is>
@@ -14045,9 +14440,6 @@
           <t>Tasa bruta de escolarización secundaria</t>
         </is>
       </c>
-      <c r="N179" t="n">
-        <v>73.34352874755859</v>
-      </c>
       <c r="O179" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -14055,7 +14447,12 @@
       </c>
       <c r="P179" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q179" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -14091,7 +14488,7 @@
         </is>
       </c>
       <c r="G180" t="n">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="H180" t="inlineStr">
         <is>
@@ -14123,9 +14520,6 @@
           <t>Tasa bruta de escolarización secundaria</t>
         </is>
       </c>
-      <c r="N180" t="n">
-        <v>75.8546676635742</v>
-      </c>
       <c r="O180" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -14133,7 +14527,12 @@
       </c>
       <c r="P180" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q180" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -14169,7 +14568,7 @@
         </is>
       </c>
       <c r="G181" t="n">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="H181" t="inlineStr">
         <is>
@@ -14201,9 +14600,6 @@
           <t>Tasa bruta de escolarización secundaria</t>
         </is>
       </c>
-      <c r="N181" t="n">
-        <v>78.2070236206055</v>
-      </c>
       <c r="O181" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -14211,7 +14607,12 @@
       </c>
       <c r="P181" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q181" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -14247,7 +14648,7 @@
         </is>
       </c>
       <c r="G182" t="n">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="H182" t="inlineStr">
         <is>
@@ -14279,9 +14680,6 @@
           <t>Tasa bruta de escolarización secundaria</t>
         </is>
       </c>
-      <c r="N182" t="n">
-        <v>79.8805770874023</v>
-      </c>
       <c r="O182" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -14289,7 +14687,12 @@
       </c>
       <c r="P182" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q182" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -14325,7 +14728,7 @@
         </is>
       </c>
       <c r="G183" t="n">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="H183" t="inlineStr">
         <is>
@@ -14357,9 +14760,6 @@
           <t>Tasa bruta de escolarización secundaria</t>
         </is>
       </c>
-      <c r="N183" t="n">
-        <v>80.7918167114258</v>
-      </c>
       <c r="O183" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -14367,7 +14767,12 @@
       </c>
       <c r="P183" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q183" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -14403,7 +14808,7 @@
         </is>
       </c>
       <c r="G184" t="n">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="H184" t="inlineStr">
         <is>
@@ -14435,9 +14840,6 @@
           <t>Tasa bruta de escolarización secundaria</t>
         </is>
       </c>
-      <c r="N184" t="n">
-        <v>80.72409820556641</v>
-      </c>
       <c r="O184" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -14445,7 +14847,12 @@
       </c>
       <c r="P184" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q184" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -14481,7 +14888,7 @@
         </is>
       </c>
       <c r="G185" t="n">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="H185" t="inlineStr">
         <is>
@@ -14513,9 +14920,6 @@
           <t>Tasa bruta de escolarización secundaria</t>
         </is>
       </c>
-      <c r="N185" t="n">
-        <v>81.67828369140619</v>
-      </c>
       <c r="O185" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -14523,7 +14927,12 @@
       </c>
       <c r="P185" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q185" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -14559,7 +14968,7 @@
         </is>
       </c>
       <c r="G186" t="n">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="H186" t="inlineStr">
         <is>
@@ -14591,9 +15000,6 @@
           <t>Tasa bruta de escolarización secundaria</t>
         </is>
       </c>
-      <c r="N186" t="n">
-        <v>83.8216934204102</v>
-      </c>
       <c r="O186" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -14601,7 +15007,12 @@
       </c>
       <c r="P186" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q186" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -14637,7 +15048,7 @@
         </is>
       </c>
       <c r="G187" t="n">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="H187" t="inlineStr">
         <is>
@@ -14669,9 +15080,6 @@
           <t>Tasa bruta de escolarización secundaria</t>
         </is>
       </c>
-      <c r="N187" t="n">
-        <v>91.47254943847661</v>
-      </c>
       <c r="O187" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -14679,7 +15087,12 @@
       </c>
       <c r="P187" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q187" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -14715,7 +15128,7 @@
         </is>
       </c>
       <c r="G188" t="n">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="H188" t="inlineStr">
         <is>
@@ -14747,9 +15160,6 @@
           <t>Tasa bruta de escolarización secundaria</t>
         </is>
       </c>
-      <c r="N188" t="n">
-        <v>90.80812072753911</v>
-      </c>
       <c r="O188" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -14757,7 +15167,12 @@
       </c>
       <c r="P188" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q188" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -14793,7 +15208,7 @@
         </is>
       </c>
       <c r="G189" t="n">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="H189" t="inlineStr">
         <is>
@@ -14825,9 +15240,6 @@
           <t>Tasa bruta de escolarización secundaria</t>
         </is>
       </c>
-      <c r="N189" t="n">
-        <v>88.83022308349609</v>
-      </c>
       <c r="O189" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -14835,7 +15247,12 @@
       </c>
       <c r="P189" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q189" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -14871,7 +15288,7 @@
         </is>
       </c>
       <c r="G190" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="H190" t="inlineStr">
         <is>
@@ -14903,9 +15320,6 @@
           <t>Tasa bruta de escolarización secundaria</t>
         </is>
       </c>
-      <c r="N190" t="n">
-        <v>85.13294982910161</v>
-      </c>
       <c r="O190" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -14913,7 +15327,12 @@
       </c>
       <c r="P190" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q190" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -14949,7 +15368,7 @@
         </is>
       </c>
       <c r="G191" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="H191" t="inlineStr">
         <is>
@@ -14981,9 +15400,6 @@
           <t>Tasa bruta de escolarización secundaria</t>
         </is>
       </c>
-      <c r="N191" t="n">
-        <v>83.9518280029297</v>
-      </c>
       <c r="O191" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -14991,7 +15407,12 @@
       </c>
       <c r="P191" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q191" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -15027,7 +15448,7 @@
         </is>
       </c>
       <c r="G192" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="H192" t="inlineStr">
         <is>
@@ -15066,7 +15487,12 @@
       </c>
       <c r="P192" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q192" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -15102,7 +15528,7 @@
         </is>
       </c>
       <c r="G193" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="H193" t="inlineStr">
         <is>
@@ -15141,7 +15567,12 @@
       </c>
       <c r="P193" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q193" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -15177,7 +15608,7 @@
         </is>
       </c>
       <c r="G194" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="H194" t="inlineStr">
         <is>
@@ -15216,7 +15647,12 @@
       </c>
       <c r="P194" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q194" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -15252,7 +15688,7 @@
         </is>
       </c>
       <c r="G195" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="H195" t="inlineStr">
         <is>
@@ -15291,7 +15727,12 @@
       </c>
       <c r="P195" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q195" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -15327,7 +15768,7 @@
         </is>
       </c>
       <c r="G196" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="H196" t="inlineStr">
         <is>
@@ -15359,9 +15800,6 @@
           <t>Tasa bruta de escolarización secundaria</t>
         </is>
       </c>
-      <c r="N196" t="n">
-        <v>96.79067230224609</v>
-      </c>
       <c r="O196" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -15369,7 +15807,12 @@
       </c>
       <c r="P196" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q196" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -15405,7 +15848,7 @@
         </is>
       </c>
       <c r="G197" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="H197" t="inlineStr">
         <is>
@@ -15437,9 +15880,6 @@
           <t>Tasa bruta de escolarización secundaria</t>
         </is>
       </c>
-      <c r="N197" t="n">
-        <v>97.229606628418</v>
-      </c>
       <c r="O197" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -15447,7 +15887,12 @@
       </c>
       <c r="P197" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q197" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -15483,7 +15928,7 @@
         </is>
       </c>
       <c r="G198" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="H198" t="inlineStr">
         <is>
@@ -15515,9 +15960,6 @@
           <t>Tasa bruta de escolarización secundaria</t>
         </is>
       </c>
-      <c r="N198" t="n">
-        <v>97.7908172607422</v>
-      </c>
       <c r="O198" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -15525,7 +15967,12 @@
       </c>
       <c r="P198" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q198" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -15561,7 +16008,7 @@
         </is>
       </c>
       <c r="G199" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="H199" t="inlineStr">
         <is>
@@ -15600,7 +16047,12 @@
       </c>
       <c r="P199" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q199" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -15636,7 +16088,7 @@
         </is>
       </c>
       <c r="G200" t="n">
-        <v>1960</v>
+        <v>2025</v>
       </c>
       <c r="H200" t="inlineStr">
         <is>
@@ -15660,12 +16112,12 @@
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>SE.TER.ENRR</t>
+          <t>SE.SEC.ENRR</t>
         </is>
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Tasa bruta de escolarización terciaria</t>
+          <t>Tasa bruta de escolarización secundaria</t>
         </is>
       </c>
       <c r="O200" t="inlineStr">
@@ -15675,7 +16127,12 @@
       </c>
       <c r="P200" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q200" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -15711,7 +16168,7 @@
         </is>
       </c>
       <c r="G201" t="n">
-        <v>1961</v>
+        <v>2026</v>
       </c>
       <c r="H201" t="inlineStr">
         <is>
@@ -15735,12 +16192,12 @@
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>SE.TER.ENRR</t>
+          <t>SE.SEC.ENRR</t>
         </is>
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>Tasa bruta de escolarización terciaria</t>
+          <t>Tasa bruta de escolarización secundaria</t>
         </is>
       </c>
       <c r="O201" t="inlineStr">
@@ -15750,7 +16207,12 @@
       </c>
       <c r="P201" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q201" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -15786,7 +16248,7 @@
         </is>
       </c>
       <c r="G202" t="n">
-        <v>1962</v>
+        <v>1960</v>
       </c>
       <c r="H202" t="inlineStr">
         <is>
@@ -15825,7 +16287,12 @@
       </c>
       <c r="P202" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q202" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -15861,7 +16328,7 @@
         </is>
       </c>
       <c r="G203" t="n">
-        <v>1963</v>
+        <v>1961</v>
       </c>
       <c r="H203" t="inlineStr">
         <is>
@@ -15900,7 +16367,12 @@
       </c>
       <c r="P203" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q203" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -15936,7 +16408,7 @@
         </is>
       </c>
       <c r="G204" t="n">
-        <v>1964</v>
+        <v>1962</v>
       </c>
       <c r="H204" t="inlineStr">
         <is>
@@ -15975,7 +16447,12 @@
       </c>
       <c r="P204" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q204" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -16011,7 +16488,7 @@
         </is>
       </c>
       <c r="G205" t="n">
-        <v>1965</v>
+        <v>1963</v>
       </c>
       <c r="H205" t="inlineStr">
         <is>
@@ -16050,7 +16527,12 @@
       </c>
       <c r="P205" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q205" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -16086,7 +16568,7 @@
         </is>
       </c>
       <c r="G206" t="n">
-        <v>1966</v>
+        <v>1964</v>
       </c>
       <c r="H206" t="inlineStr">
         <is>
@@ -16125,7 +16607,12 @@
       </c>
       <c r="P206" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q206" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -16161,7 +16648,7 @@
         </is>
       </c>
       <c r="G207" t="n">
-        <v>1967</v>
+        <v>1965</v>
       </c>
       <c r="H207" t="inlineStr">
         <is>
@@ -16200,7 +16687,12 @@
       </c>
       <c r="P207" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q207" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -16236,7 +16728,7 @@
         </is>
       </c>
       <c r="G208" t="n">
-        <v>1968</v>
+        <v>1966</v>
       </c>
       <c r="H208" t="inlineStr">
         <is>
@@ -16275,7 +16767,12 @@
       </c>
       <c r="P208" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q208" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -16311,7 +16808,7 @@
         </is>
       </c>
       <c r="G209" t="n">
-        <v>1969</v>
+        <v>1967</v>
       </c>
       <c r="H209" t="inlineStr">
         <is>
@@ -16350,7 +16847,12 @@
       </c>
       <c r="P209" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q209" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -16386,7 +16888,7 @@
         </is>
       </c>
       <c r="G210" t="n">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="H210" t="inlineStr">
         <is>
@@ -16425,7 +16927,12 @@
       </c>
       <c r="P210" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q210" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -16461,7 +16968,7 @@
         </is>
       </c>
       <c r="G211" t="n">
-        <v>1971</v>
+        <v>1969</v>
       </c>
       <c r="H211" t="inlineStr">
         <is>
@@ -16493,9 +17000,6 @@
           <t>Tasa bruta de escolarización terciaria</t>
         </is>
       </c>
-      <c r="N211" t="n">
-        <v>9.16672992706299</v>
-      </c>
       <c r="O211" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -16503,7 +17007,12 @@
       </c>
       <c r="P211" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q211" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -16539,7 +17048,7 @@
         </is>
       </c>
       <c r="G212" t="n">
-        <v>1972</v>
+        <v>1970</v>
       </c>
       <c r="H212" t="inlineStr">
         <is>
@@ -16571,9 +17080,6 @@
           <t>Tasa bruta de escolarización terciaria</t>
         </is>
       </c>
-      <c r="N212" t="n">
-        <v>10.608229637146</v>
-      </c>
       <c r="O212" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -16581,7 +17087,12 @@
       </c>
       <c r="P212" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q212" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -16617,7 +17128,7 @@
         </is>
       </c>
       <c r="G213" t="n">
-        <v>1973</v>
+        <v>1971</v>
       </c>
       <c r="H213" t="inlineStr">
         <is>
@@ -16649,9 +17160,6 @@
           <t>Tasa bruta de escolarización terciaria</t>
         </is>
       </c>
-      <c r="N213" t="n">
-        <v>11.8261995315552</v>
-      </c>
       <c r="O213" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -16659,7 +17167,12 @@
       </c>
       <c r="P213" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q213" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -16695,7 +17208,7 @@
         </is>
       </c>
       <c r="G214" t="n">
-        <v>1974</v>
+        <v>1972</v>
       </c>
       <c r="H214" t="inlineStr">
         <is>
@@ -16727,9 +17240,6 @@
           <t>Tasa bruta de escolarización terciaria</t>
         </is>
       </c>
-      <c r="N214" t="n">
-        <v>12.688380241394</v>
-      </c>
       <c r="O214" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -16737,7 +17247,12 @@
       </c>
       <c r="P214" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q214" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -16773,7 +17288,7 @@
         </is>
       </c>
       <c r="G215" t="n">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="H215" t="inlineStr">
         <is>
@@ -16805,9 +17320,6 @@
           <t>Tasa bruta de escolarización terciaria</t>
         </is>
       </c>
-      <c r="N215" t="n">
-        <v>14.1456604003906</v>
-      </c>
       <c r="O215" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -16815,7 +17327,12 @@
       </c>
       <c r="P215" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q215" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -16851,7 +17368,7 @@
         </is>
       </c>
       <c r="G216" t="n">
-        <v>1976</v>
+        <v>1974</v>
       </c>
       <c r="H216" t="inlineStr">
         <is>
@@ -16883,9 +17400,6 @@
           <t>Tasa bruta de escolarización terciaria</t>
         </is>
       </c>
-      <c r="N216" t="n">
-        <v>15.4267597198486</v>
-      </c>
       <c r="O216" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -16893,7 +17407,12 @@
       </c>
       <c r="P216" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q216" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -16929,7 +17448,7 @@
         </is>
       </c>
       <c r="G217" t="n">
-        <v>1977</v>
+        <v>1975</v>
       </c>
       <c r="H217" t="inlineStr">
         <is>
@@ -16968,7 +17487,12 @@
       </c>
       <c r="P217" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q217" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -17004,7 +17528,7 @@
         </is>
       </c>
       <c r="G218" t="n">
-        <v>1978</v>
+        <v>1976</v>
       </c>
       <c r="H218" t="inlineStr">
         <is>
@@ -17036,9 +17560,6 @@
           <t>Tasa bruta de escolarización terciaria</t>
         </is>
       </c>
-      <c r="N218" t="n">
-        <v>17.8186893463135</v>
-      </c>
       <c r="O218" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -17046,7 +17567,12 @@
       </c>
       <c r="P218" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q218" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -17082,7 +17608,7 @@
         </is>
       </c>
       <c r="G219" t="n">
-        <v>1979</v>
+        <v>1977</v>
       </c>
       <c r="H219" t="inlineStr">
         <is>
@@ -17114,9 +17640,6 @@
           <t>Tasa bruta de escolarización terciaria</t>
         </is>
       </c>
-      <c r="N219" t="n">
-        <v>18.3426303863525</v>
-      </c>
       <c r="O219" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -17124,7 +17647,12 @@
       </c>
       <c r="P219" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q219" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -17160,7 +17688,7 @@
         </is>
       </c>
       <c r="G220" t="n">
-        <v>1980</v>
+        <v>1978</v>
       </c>
       <c r="H220" t="inlineStr">
         <is>
@@ -17192,9 +17720,6 @@
           <t>Tasa bruta de escolarización terciaria</t>
         </is>
       </c>
-      <c r="N220" t="n">
-        <v>18.9691390991211</v>
-      </c>
       <c r="O220" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -17202,7 +17727,12 @@
       </c>
       <c r="P220" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q220" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -17238,7 +17768,7 @@
         </is>
       </c>
       <c r="G221" t="n">
-        <v>1981</v>
+        <v>1979</v>
       </c>
       <c r="H221" t="inlineStr">
         <is>
@@ -17270,9 +17800,6 @@
           <t>Tasa bruta de escolarización terciaria</t>
         </is>
       </c>
-      <c r="N221" t="n">
-        <v>18.9722003936768</v>
-      </c>
       <c r="O221" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -17280,7 +17807,12 @@
       </c>
       <c r="P221" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q221" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -17316,7 +17848,7 @@
         </is>
       </c>
       <c r="G222" t="n">
-        <v>1982</v>
+        <v>1980</v>
       </c>
       <c r="H222" t="inlineStr">
         <is>
@@ -17348,9 +17880,6 @@
           <t>Tasa bruta de escolarización terciaria</t>
         </is>
       </c>
-      <c r="N222" t="n">
-        <v>20.0155601501465</v>
-      </c>
       <c r="O222" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -17358,7 +17887,12 @@
       </c>
       <c r="P222" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q222" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17928,7 @@
         </is>
       </c>
       <c r="G223" t="n">
-        <v>1983</v>
+        <v>1981</v>
       </c>
       <c r="H223" t="inlineStr">
         <is>
@@ -17426,9 +17960,6 @@
           <t>Tasa bruta de escolarización terciaria</t>
         </is>
       </c>
-      <c r="N223" t="n">
-        <v>20.6762008666992</v>
-      </c>
       <c r="O223" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -17436,7 +17967,12 @@
       </c>
       <c r="P223" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q223" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -17472,7 +18008,7 @@
         </is>
       </c>
       <c r="G224" t="n">
-        <v>1984</v>
+        <v>1982</v>
       </c>
       <c r="H224" t="inlineStr">
         <is>
@@ -17504,9 +18040,6 @@
           <t>Tasa bruta de escolarización terciaria</t>
         </is>
       </c>
-      <c r="N224" t="n">
-        <v>21.8267993927002</v>
-      </c>
       <c r="O224" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -17514,7 +18047,12 @@
       </c>
       <c r="P224" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q224" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -17550,7 +18088,7 @@
         </is>
       </c>
       <c r="G225" t="n">
-        <v>1985</v>
+        <v>1983</v>
       </c>
       <c r="H225" t="inlineStr">
         <is>
@@ -17582,9 +18120,6 @@
           <t>Tasa bruta de escolarización terciaria</t>
         </is>
       </c>
-      <c r="N225" t="n">
-        <v>21.6080799102783</v>
-      </c>
       <c r="O225" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -17592,7 +18127,12 @@
       </c>
       <c r="P225" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q225" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -17628,7 +18168,7 @@
         </is>
       </c>
       <c r="G226" t="n">
-        <v>1986</v>
+        <v>1984</v>
       </c>
       <c r="H226" t="inlineStr">
         <is>
@@ -17660,9 +18200,6 @@
           <t>Tasa bruta de escolarización terciaria</t>
         </is>
       </c>
-      <c r="N226" t="n">
-        <v>24.5814800262451</v>
-      </c>
       <c r="O226" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -17670,7 +18207,12 @@
       </c>
       <c r="P226" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q226" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -17706,7 +18248,7 @@
         </is>
       </c>
       <c r="G227" t="n">
-        <v>1987</v>
+        <v>1985</v>
       </c>
       <c r="H227" t="inlineStr">
         <is>
@@ -17738,9 +18280,6 @@
           <t>Tasa bruta de escolarización terciaria</t>
         </is>
       </c>
-      <c r="N227" t="n">
-        <v>23.5750999450684</v>
-      </c>
       <c r="O227" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -17748,7 +18287,12 @@
       </c>
       <c r="P227" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q227" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -17784,7 +18328,7 @@
         </is>
       </c>
       <c r="G228" t="n">
-        <v>1988</v>
+        <v>1986</v>
       </c>
       <c r="H228" t="inlineStr">
         <is>
@@ -17816,9 +18360,6 @@
           <t>Tasa bruta de escolarización terciaria</t>
         </is>
       </c>
-      <c r="N228" t="n">
-        <v>24.520809173584</v>
-      </c>
       <c r="O228" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -17826,7 +18367,12 @@
       </c>
       <c r="P228" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q228" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -17862,7 +18408,7 @@
         </is>
       </c>
       <c r="G229" t="n">
-        <v>1989</v>
+        <v>1987</v>
       </c>
       <c r="H229" t="inlineStr">
         <is>
@@ -17894,9 +18440,6 @@
           <t>Tasa bruta de escolarización terciaria</t>
         </is>
       </c>
-      <c r="N229" t="n">
-        <v>25.8283996582031</v>
-      </c>
       <c r="O229" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -17904,7 +18447,12 @@
       </c>
       <c r="P229" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q229" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -17940,7 +18488,7 @@
         </is>
       </c>
       <c r="G230" t="n">
-        <v>1990</v>
+        <v>1988</v>
       </c>
       <c r="H230" t="inlineStr">
         <is>
@@ -17972,9 +18520,6 @@
           <t>Tasa bruta de escolarización terciaria</t>
         </is>
       </c>
-      <c r="N230" t="n">
-        <v>26.8769798278809</v>
-      </c>
       <c r="O230" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -17982,7 +18527,12 @@
       </c>
       <c r="P230" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q230" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -18018,7 +18568,7 @@
         </is>
       </c>
       <c r="G231" t="n">
-        <v>1991</v>
+        <v>1989</v>
       </c>
       <c r="H231" t="inlineStr">
         <is>
@@ -18050,9 +18600,6 @@
           <t>Tasa bruta de escolarización terciaria</t>
         </is>
       </c>
-      <c r="N231" t="n">
-        <v>27.4910392761231</v>
-      </c>
       <c r="O231" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -18060,7 +18607,12 @@
       </c>
       <c r="P231" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q231" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -18096,7 +18648,7 @@
         </is>
       </c>
       <c r="G232" t="n">
-        <v>1992</v>
+        <v>1990</v>
       </c>
       <c r="H232" t="inlineStr">
         <is>
@@ -18128,9 +18680,6 @@
           <t>Tasa bruta de escolarización terciaria</t>
         </is>
       </c>
-      <c r="N232" t="n">
-        <v>27.0434608459473</v>
-      </c>
       <c r="O232" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -18138,7 +18687,12 @@
       </c>
       <c r="P232" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q232" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -18174,7 +18728,7 @@
         </is>
       </c>
       <c r="G233" t="n">
-        <v>1993</v>
+        <v>1991</v>
       </c>
       <c r="H233" t="inlineStr">
         <is>
@@ -18213,7 +18767,12 @@
       </c>
       <c r="P233" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q233" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -18249,7 +18808,7 @@
         </is>
       </c>
       <c r="G234" t="n">
-        <v>1994</v>
+        <v>1992</v>
       </c>
       <c r="H234" t="inlineStr">
         <is>
@@ -18288,7 +18847,12 @@
       </c>
       <c r="P234" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q234" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -18324,7 +18888,7 @@
         </is>
       </c>
       <c r="G235" t="n">
-        <v>1995</v>
+        <v>1993</v>
       </c>
       <c r="H235" t="inlineStr">
         <is>
@@ -18363,7 +18927,12 @@
       </c>
       <c r="P235" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q235" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -18399,7 +18968,7 @@
         </is>
       </c>
       <c r="G236" t="n">
-        <v>1996</v>
+        <v>1994</v>
       </c>
       <c r="H236" t="inlineStr">
         <is>
@@ -18438,7 +19007,12 @@
       </c>
       <c r="P236" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q236" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -18474,7 +19048,7 @@
         </is>
       </c>
       <c r="G237" t="n">
-        <v>1997</v>
+        <v>1995</v>
       </c>
       <c r="H237" t="inlineStr">
         <is>
@@ -18513,7 +19087,12 @@
       </c>
       <c r="P237" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q237" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -18549,7 +19128,7 @@
         </is>
       </c>
       <c r="G238" t="n">
-        <v>1998</v>
+        <v>1996</v>
       </c>
       <c r="H238" t="inlineStr">
         <is>
@@ -18588,7 +19167,12 @@
       </c>
       <c r="P238" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q238" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -18624,7 +19208,7 @@
         </is>
       </c>
       <c r="G239" t="n">
-        <v>1999</v>
+        <v>1997</v>
       </c>
       <c r="H239" t="inlineStr">
         <is>
@@ -18663,7 +19247,12 @@
       </c>
       <c r="P239" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q239" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -18699,7 +19288,7 @@
         </is>
       </c>
       <c r="G240" t="n">
-        <v>2000</v>
+        <v>1998</v>
       </c>
       <c r="H240" t="inlineStr">
         <is>
@@ -18731,9 +19320,6 @@
           <t>Tasa bruta de escolarización terciaria</t>
         </is>
       </c>
-      <c r="N240" t="n">
-        <v>27.8114891052246</v>
-      </c>
       <c r="O240" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -18741,7 +19327,12 @@
       </c>
       <c r="P240" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q240" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -18777,7 +19368,7 @@
         </is>
       </c>
       <c r="G241" t="n">
-        <v>2001</v>
+        <v>1999</v>
       </c>
       <c r="H241" t="inlineStr">
         <is>
@@ -18816,7 +19407,12 @@
       </c>
       <c r="P241" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q241" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -18852,7 +19448,7 @@
         </is>
       </c>
       <c r="G242" t="n">
-        <v>2002</v>
+        <v>2000</v>
       </c>
       <c r="H242" t="inlineStr">
         <is>
@@ -18884,9 +19480,6 @@
           <t>Tasa bruta de escolarización terciaria</t>
         </is>
       </c>
-      <c r="N242" t="n">
-        <v>37.518970489502</v>
-      </c>
       <c r="O242" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -18894,7 +19487,12 @@
       </c>
       <c r="P242" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q242" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -18930,7 +19528,7 @@
         </is>
       </c>
       <c r="G243" t="n">
-        <v>2003</v>
+        <v>2001</v>
       </c>
       <c r="H243" t="inlineStr">
         <is>
@@ -18962,9 +19560,6 @@
           <t>Tasa bruta de escolarización terciaria</t>
         </is>
       </c>
-      <c r="N243" t="n">
-        <v>39.2063407897949</v>
-      </c>
       <c r="O243" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -18972,7 +19567,12 @@
       </c>
       <c r="P243" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q243" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -19008,7 +19608,7 @@
         </is>
       </c>
       <c r="G244" t="n">
-        <v>2004</v>
+        <v>2002</v>
       </c>
       <c r="H244" t="inlineStr">
         <is>
@@ -19040,9 +19640,6 @@
           <t>Tasa bruta de escolarización terciaria</t>
         </is>
       </c>
-      <c r="N244" t="n">
-        <v>41.2058296203613</v>
-      </c>
       <c r="O244" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -19050,7 +19647,12 @@
       </c>
       <c r="P244" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q244" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -19086,7 +19688,7 @@
         </is>
       </c>
       <c r="G245" t="n">
-        <v>2005</v>
+        <v>2003</v>
       </c>
       <c r="H245" t="inlineStr">
         <is>
@@ -19125,7 +19727,12 @@
       </c>
       <c r="P245" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q245" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -19161,7 +19768,7 @@
         </is>
       </c>
       <c r="G246" t="n">
-        <v>2006</v>
+        <v>2004</v>
       </c>
       <c r="H246" t="inlineStr">
         <is>
@@ -19200,7 +19807,12 @@
       </c>
       <c r="P246" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q246" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -19236,7 +19848,7 @@
         </is>
       </c>
       <c r="G247" t="n">
-        <v>2007</v>
+        <v>2005</v>
       </c>
       <c r="H247" t="inlineStr">
         <is>
@@ -19275,7 +19887,12 @@
       </c>
       <c r="P247" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q247" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -19311,7 +19928,7 @@
         </is>
       </c>
       <c r="G248" t="n">
-        <v>2008</v>
+        <v>2006</v>
       </c>
       <c r="H248" t="inlineStr">
         <is>
@@ -19343,9 +19960,6 @@
           <t>Tasa bruta de escolarización terciaria</t>
         </is>
       </c>
-      <c r="N248" t="n">
-        <v>78.2515029907227</v>
-      </c>
       <c r="O248" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -19353,7 +19967,12 @@
       </c>
       <c r="P248" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q248" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -19389,7 +20008,7 @@
         </is>
       </c>
       <c r="G249" t="n">
-        <v>2009</v>
+        <v>2007</v>
       </c>
       <c r="H249" t="inlineStr">
         <is>
@@ -19421,9 +20040,6 @@
           <t>Tasa bruta de escolarización terciaria</t>
         </is>
       </c>
-      <c r="N249" t="n">
-        <v>78.26992034912109</v>
-      </c>
       <c r="O249" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -19431,7 +20047,12 @@
       </c>
       <c r="P249" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q249" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -19467,7 +20088,7 @@
         </is>
       </c>
       <c r="G250" t="n">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="H250" t="inlineStr">
         <is>
@@ -19506,7 +20127,12 @@
       </c>
       <c r="P250" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q250" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -19542,7 +20168,7 @@
         </is>
       </c>
       <c r="G251" t="n">
-        <v>2011</v>
+        <v>2009</v>
       </c>
       <c r="H251" t="inlineStr">
         <is>
@@ -19581,7 +20207,12 @@
       </c>
       <c r="P251" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q251" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -19617,7 +20248,7 @@
         </is>
       </c>
       <c r="G252" t="n">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="H252" t="inlineStr">
         <is>
@@ -19656,7 +20287,12 @@
       </c>
       <c r="P252" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q252" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -19692,7 +20328,7 @@
         </is>
       </c>
       <c r="G253" t="n">
-        <v>2013</v>
+        <v>2011</v>
       </c>
       <c r="H253" t="inlineStr">
         <is>
@@ -19731,7 +20367,12 @@
       </c>
       <c r="P253" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q253" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -19767,7 +20408,7 @@
         </is>
       </c>
       <c r="G254" t="n">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="H254" t="inlineStr">
         <is>
@@ -19806,7 +20447,12 @@
       </c>
       <c r="P254" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q254" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -19842,7 +20488,7 @@
         </is>
       </c>
       <c r="G255" t="n">
-        <v>2015</v>
+        <v>2013</v>
       </c>
       <c r="H255" t="inlineStr">
         <is>
@@ -19881,7 +20527,12 @@
       </c>
       <c r="P255" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q255" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -19917,7 +20568,7 @@
         </is>
       </c>
       <c r="G256" t="n">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="H256" t="inlineStr">
         <is>
@@ -19956,7 +20607,12 @@
       </c>
       <c r="P256" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q256" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -19992,7 +20648,7 @@
         </is>
       </c>
       <c r="G257" t="n">
-        <v>2017</v>
+        <v>2015</v>
       </c>
       <c r="H257" t="inlineStr">
         <is>
@@ -20031,7 +20687,12 @@
       </c>
       <c r="P257" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q257" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -20067,7 +20728,7 @@
         </is>
       </c>
       <c r="G258" t="n">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="H258" t="inlineStr">
         <is>
@@ -20106,7 +20767,12 @@
       </c>
       <c r="P258" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q258" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -20142,7 +20808,7 @@
         </is>
       </c>
       <c r="G259" t="n">
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="H259" t="inlineStr">
         <is>
@@ -20181,7 +20847,12 @@
       </c>
       <c r="P259" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q259" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -20217,7 +20888,7 @@
         </is>
       </c>
       <c r="G260" t="n">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="H260" t="inlineStr">
         <is>
@@ -20256,7 +20927,12 @@
       </c>
       <c r="P260" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q260" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -20292,7 +20968,7 @@
         </is>
       </c>
       <c r="G261" t="n">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="H261" t="inlineStr">
         <is>
@@ -20331,7 +21007,12 @@
       </c>
       <c r="P261" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q261" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -20367,7 +21048,7 @@
         </is>
       </c>
       <c r="G262" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="H262" t="inlineStr">
         <is>
@@ -20406,7 +21087,12 @@
       </c>
       <c r="P262" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q262" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -20442,7 +21128,7 @@
         </is>
       </c>
       <c r="G263" t="n">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="H263" t="inlineStr">
         <is>
@@ -20481,7 +21167,12 @@
       </c>
       <c r="P263" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q263" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -20517,7 +21208,7 @@
         </is>
       </c>
       <c r="G264" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="H264" t="inlineStr">
         <is>
@@ -20556,7 +21247,12 @@
       </c>
       <c r="P264" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q264" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -20592,7 +21288,7 @@
         </is>
       </c>
       <c r="G265" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="H265" t="inlineStr">
         <is>
@@ -20631,7 +21327,12 @@
       </c>
       <c r="P265" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q265" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -20667,7 +21368,7 @@
         </is>
       </c>
       <c r="G266" t="n">
-        <v>1960</v>
+        <v>2024</v>
       </c>
       <c r="H266" t="inlineStr">
         <is>
@@ -20681,22 +21382,22 @@
       </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t>Gasto educativo</t>
+          <t>Escolarización</t>
         </is>
       </c>
       <c r="K266" t="inlineStr">
         <is>
-          <t>gasto_educativo</t>
+          <t>escolarizacion</t>
         </is>
       </c>
       <c r="L266" t="inlineStr">
         <is>
-          <t>SE.XPD.TOTL.GD.ZS</t>
+          <t>SE.TER.ENRR</t>
         </is>
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>Gasto público en educación como porcentaje del PIB</t>
+          <t>Tasa bruta de escolarización terciaria</t>
         </is>
       </c>
       <c r="O266" t="inlineStr">
@@ -20706,7 +21407,12 @@
       </c>
       <c r="P266" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q266" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -20742,7 +21448,7 @@
         </is>
       </c>
       <c r="G267" t="n">
-        <v>1961</v>
+        <v>2025</v>
       </c>
       <c r="H267" t="inlineStr">
         <is>
@@ -20756,22 +21462,22 @@
       </c>
       <c r="J267" t="inlineStr">
         <is>
-          <t>Gasto educativo</t>
+          <t>Escolarización</t>
         </is>
       </c>
       <c r="K267" t="inlineStr">
         <is>
-          <t>gasto_educativo</t>
+          <t>escolarizacion</t>
         </is>
       </c>
       <c r="L267" t="inlineStr">
         <is>
-          <t>SE.XPD.TOTL.GD.ZS</t>
+          <t>SE.TER.ENRR</t>
         </is>
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>Gasto público en educación como porcentaje del PIB</t>
+          <t>Tasa bruta de escolarización terciaria</t>
         </is>
       </c>
       <c r="O267" t="inlineStr">
@@ -20781,7 +21487,12 @@
       </c>
       <c r="P267" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q267" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -20817,7 +21528,7 @@
         </is>
       </c>
       <c r="G268" t="n">
-        <v>1962</v>
+        <v>2026</v>
       </c>
       <c r="H268" t="inlineStr">
         <is>
@@ -20831,22 +21542,22 @@
       </c>
       <c r="J268" t="inlineStr">
         <is>
-          <t>Gasto educativo</t>
+          <t>Escolarización</t>
         </is>
       </c>
       <c r="K268" t="inlineStr">
         <is>
-          <t>gasto_educativo</t>
+          <t>escolarizacion</t>
         </is>
       </c>
       <c r="L268" t="inlineStr">
         <is>
-          <t>SE.XPD.TOTL.GD.ZS</t>
+          <t>SE.TER.ENRR</t>
         </is>
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>Gasto público en educación como porcentaje del PIB</t>
+          <t>Tasa bruta de escolarización terciaria</t>
         </is>
       </c>
       <c r="O268" t="inlineStr">
@@ -20856,7 +21567,12 @@
       </c>
       <c r="P268" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q268" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -20892,7 +21608,7 @@
         </is>
       </c>
       <c r="G269" t="n">
-        <v>1963</v>
+        <v>1960</v>
       </c>
       <c r="H269" t="inlineStr">
         <is>
@@ -20931,7 +21647,7 @@
       </c>
       <c r="P269" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -20967,7 +21683,7 @@
         </is>
       </c>
       <c r="G270" t="n">
-        <v>1964</v>
+        <v>1961</v>
       </c>
       <c r="H270" t="inlineStr">
         <is>
@@ -21006,7 +21722,7 @@
       </c>
       <c r="P270" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -21042,7 +21758,7 @@
         </is>
       </c>
       <c r="G271" t="n">
-        <v>1965</v>
+        <v>1962</v>
       </c>
       <c r="H271" t="inlineStr">
         <is>
@@ -21081,7 +21797,7 @@
       </c>
       <c r="P271" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -21117,7 +21833,7 @@
         </is>
       </c>
       <c r="G272" t="n">
-        <v>1966</v>
+        <v>1963</v>
       </c>
       <c r="H272" t="inlineStr">
         <is>
@@ -21156,7 +21872,7 @@
       </c>
       <c r="P272" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -21192,7 +21908,7 @@
         </is>
       </c>
       <c r="G273" t="n">
-        <v>1967</v>
+        <v>1964</v>
       </c>
       <c r="H273" t="inlineStr">
         <is>
@@ -21231,7 +21947,7 @@
       </c>
       <c r="P273" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -21267,7 +21983,7 @@
         </is>
       </c>
       <c r="G274" t="n">
-        <v>1968</v>
+        <v>1965</v>
       </c>
       <c r="H274" t="inlineStr">
         <is>
@@ -21306,7 +22022,7 @@
       </c>
       <c r="P274" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -21342,7 +22058,7 @@
         </is>
       </c>
       <c r="G275" t="n">
-        <v>1969</v>
+        <v>1966</v>
       </c>
       <c r="H275" t="inlineStr">
         <is>
@@ -21381,7 +22097,7 @@
       </c>
       <c r="P275" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -21417,7 +22133,7 @@
         </is>
       </c>
       <c r="G276" t="n">
-        <v>1970</v>
+        <v>1967</v>
       </c>
       <c r="H276" t="inlineStr">
         <is>
@@ -21449,9 +22165,6 @@
           <t>Gasto público en educación como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N276" t="n">
-        <v>4.16286993026733</v>
-      </c>
       <c r="O276" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -21459,7 +22172,7 @@
       </c>
       <c r="P276" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -21495,7 +22208,7 @@
         </is>
       </c>
       <c r="G277" t="n">
-        <v>1971</v>
+        <v>1968</v>
       </c>
       <c r="H277" t="inlineStr">
         <is>
@@ -21527,9 +22240,6 @@
           <t>Gasto público en educación como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N277" t="n">
-        <v>4.1799201965332</v>
-      </c>
       <c r="O277" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -21537,7 +22247,7 @@
       </c>
       <c r="P277" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -21573,7 +22283,7 @@
         </is>
       </c>
       <c r="G278" t="n">
-        <v>1972</v>
+        <v>1969</v>
       </c>
       <c r="H278" t="inlineStr">
         <is>
@@ -21605,9 +22315,6 @@
           <t>Gasto público en educación como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N278" t="n">
-        <v>4.83728981018066</v>
-      </c>
       <c r="O278" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -21615,7 +22322,7 @@
       </c>
       <c r="P278" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -21651,7 +22358,7 @@
         </is>
       </c>
       <c r="G279" t="n">
-        <v>1973</v>
+        <v>1970</v>
       </c>
       <c r="H279" t="inlineStr">
         <is>
@@ -21683,6 +22390,9 @@
           <t>Gasto público en educación como porcentaje del PIB</t>
         </is>
       </c>
+      <c r="N279" t="n">
+        <v>4.16286993026733</v>
+      </c>
       <c r="O279" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -21690,7 +22400,7 @@
       </c>
       <c r="P279" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -21726,7 +22436,7 @@
         </is>
       </c>
       <c r="G280" t="n">
-        <v>1974</v>
+        <v>1971</v>
       </c>
       <c r="H280" t="inlineStr">
         <is>
@@ -21759,7 +22469,7 @@
         </is>
       </c>
       <c r="N280" t="n">
-        <v>3.94795989990234</v>
+        <v>4.1799201965332</v>
       </c>
       <c r="O280" t="inlineStr">
         <is>
@@ -21768,7 +22478,7 @@
       </c>
       <c r="P280" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -21804,7 +22514,7 @@
         </is>
       </c>
       <c r="G281" t="n">
-        <v>1975</v>
+        <v>1972</v>
       </c>
       <c r="H281" t="inlineStr">
         <is>
@@ -21837,7 +22547,7 @@
         </is>
       </c>
       <c r="N281" t="n">
-        <v>5.19851016998291</v>
+        <v>4.83728981018066</v>
       </c>
       <c r="O281" t="inlineStr">
         <is>
@@ -21846,7 +22556,7 @@
       </c>
       <c r="P281" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -21882,7 +22592,7 @@
         </is>
       </c>
       <c r="G282" t="n">
-        <v>1976</v>
+        <v>1973</v>
       </c>
       <c r="H282" t="inlineStr">
         <is>
@@ -21921,7 +22631,7 @@
       </c>
       <c r="P282" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -21957,7 +22667,7 @@
         </is>
       </c>
       <c r="G283" t="n">
-        <v>1977</v>
+        <v>1974</v>
       </c>
       <c r="H283" t="inlineStr">
         <is>
@@ -21990,7 +22700,7 @@
         </is>
       </c>
       <c r="N283" t="n">
-        <v>5.25665998458862</v>
+        <v>3.94795989990234</v>
       </c>
       <c r="O283" t="inlineStr">
         <is>
@@ -21999,7 +22709,7 @@
       </c>
       <c r="P283" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -22035,7 +22745,7 @@
         </is>
       </c>
       <c r="G284" t="n">
-        <v>1978</v>
+        <v>1975</v>
       </c>
       <c r="H284" t="inlineStr">
         <is>
@@ -22067,6 +22777,9 @@
           <t>Gasto público en educación como porcentaje del PIB</t>
         </is>
       </c>
+      <c r="N284" t="n">
+        <v>5.19851016998291</v>
+      </c>
       <c r="O284" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -22074,7 +22787,7 @@
       </c>
       <c r="P284" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -22110,7 +22823,7 @@
         </is>
       </c>
       <c r="G285" t="n">
-        <v>1979</v>
+        <v>1976</v>
       </c>
       <c r="H285" t="inlineStr">
         <is>
@@ -22149,7 +22862,7 @@
       </c>
       <c r="P285" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -22185,7 +22898,7 @@
         </is>
       </c>
       <c r="G286" t="n">
-        <v>1980</v>
+        <v>1977</v>
       </c>
       <c r="H286" t="inlineStr">
         <is>
@@ -22218,7 +22931,7 @@
         </is>
       </c>
       <c r="N286" t="n">
-        <v>4.40072011947632</v>
+        <v>5.25665998458862</v>
       </c>
       <c r="O286" t="inlineStr">
         <is>
@@ -22227,7 +22940,7 @@
       </c>
       <c r="P286" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -22263,7 +22976,7 @@
         </is>
       </c>
       <c r="G287" t="n">
-        <v>1981</v>
+        <v>1978</v>
       </c>
       <c r="H287" t="inlineStr">
         <is>
@@ -22295,9 +23008,6 @@
           <t>Gasto público en educación como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N287" t="n">
-        <v>5.18743991851807</v>
-      </c>
       <c r="O287" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -22305,7 +23015,7 @@
       </c>
       <c r="P287" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -22341,7 +23051,7 @@
         </is>
       </c>
       <c r="G288" t="n">
-        <v>1982</v>
+        <v>1979</v>
       </c>
       <c r="H288" t="inlineStr">
         <is>
@@ -22373,9 +23083,6 @@
           <t>Gasto público en educación como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N288" t="n">
-        <v>5.00895023345947</v>
-      </c>
       <c r="O288" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -22383,7 +23090,7 @@
       </c>
       <c r="P288" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -22419,7 +23126,7 @@
         </is>
       </c>
       <c r="G289" t="n">
-        <v>1983</v>
+        <v>1980</v>
       </c>
       <c r="H289" t="inlineStr">
         <is>
@@ -22452,7 +23159,7 @@
         </is>
       </c>
       <c r="N289" t="n">
-        <v>6.0598201751709</v>
+        <v>4.40072011947632</v>
       </c>
       <c r="O289" t="inlineStr">
         <is>
@@ -22461,7 +23168,7 @@
       </c>
       <c r="P289" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -22497,7 +23204,7 @@
         </is>
       </c>
       <c r="G290" t="n">
-        <v>1984</v>
+        <v>1981</v>
       </c>
       <c r="H290" t="inlineStr">
         <is>
@@ -22530,7 +23237,7 @@
         </is>
       </c>
       <c r="N290" t="n">
-        <v>4.06372976303101</v>
+        <v>5.18743991851807</v>
       </c>
       <c r="O290" t="inlineStr">
         <is>
@@ -22539,7 +23246,7 @@
       </c>
       <c r="P290" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -22575,7 +23282,7 @@
         </is>
       </c>
       <c r="G291" t="n">
-        <v>1985</v>
+        <v>1982</v>
       </c>
       <c r="H291" t="inlineStr">
         <is>
@@ -22607,6 +23314,9 @@
           <t>Gasto público en educación como porcentaje del PIB</t>
         </is>
       </c>
+      <c r="N291" t="n">
+        <v>5.00895023345947</v>
+      </c>
       <c r="O291" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -22614,7 +23324,7 @@
       </c>
       <c r="P291" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -22650,7 +23360,7 @@
         </is>
       </c>
       <c r="G292" t="n">
-        <v>1986</v>
+        <v>1983</v>
       </c>
       <c r="H292" t="inlineStr">
         <is>
@@ -22682,6 +23392,9 @@
           <t>Gasto público en educación como porcentaje del PIB</t>
         </is>
       </c>
+      <c r="N292" t="n">
+        <v>6.0598201751709</v>
+      </c>
       <c r="O292" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -22689,7 +23402,7 @@
       </c>
       <c r="P292" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -22725,7 +23438,7 @@
         </is>
       </c>
       <c r="G293" t="n">
-        <v>1987</v>
+        <v>1984</v>
       </c>
       <c r="H293" t="inlineStr">
         <is>
@@ -22758,7 +23471,7 @@
         </is>
       </c>
       <c r="N293" t="n">
-        <v>3.92751002311706</v>
+        <v>4.06372976303101</v>
       </c>
       <c r="O293" t="inlineStr">
         <is>
@@ -22767,7 +23480,7 @@
       </c>
       <c r="P293" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -22803,7 +23516,7 @@
         </is>
       </c>
       <c r="G294" t="n">
-        <v>1988</v>
+        <v>1985</v>
       </c>
       <c r="H294" t="inlineStr">
         <is>
@@ -22835,9 +23548,6 @@
           <t>Gasto público en educación como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N294" t="n">
-        <v>3.62941002845764</v>
-      </c>
       <c r="O294" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -22845,7 +23555,7 @@
       </c>
       <c r="P294" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -22881,7 +23591,7 @@
         </is>
       </c>
       <c r="G295" t="n">
-        <v>1989</v>
+        <v>1986</v>
       </c>
       <c r="H295" t="inlineStr">
         <is>
@@ -22920,7 +23630,7 @@
       </c>
       <c r="P295" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -22956,7 +23666,7 @@
         </is>
       </c>
       <c r="G296" t="n">
-        <v>1990</v>
+        <v>1987</v>
       </c>
       <c r="H296" t="inlineStr">
         <is>
@@ -22989,7 +23699,7 @@
         </is>
       </c>
       <c r="N296" t="n">
-        <v>2.44671010971069</v>
+        <v>3.92751002311706</v>
       </c>
       <c r="O296" t="inlineStr">
         <is>
@@ -22998,7 +23708,7 @@
       </c>
       <c r="P296" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -23034,7 +23744,7 @@
         </is>
       </c>
       <c r="G297" t="n">
-        <v>1991</v>
+        <v>1988</v>
       </c>
       <c r="H297" t="inlineStr">
         <is>
@@ -23066,6 +23776,9 @@
           <t>Gasto público en educación como porcentaje del PIB</t>
         </is>
       </c>
+      <c r="N297" t="n">
+        <v>3.62941002845764</v>
+      </c>
       <c r="O297" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -23073,7 +23786,7 @@
       </c>
       <c r="P297" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -23109,7 +23822,7 @@
         </is>
       </c>
       <c r="G298" t="n">
-        <v>1992</v>
+        <v>1989</v>
       </c>
       <c r="H298" t="inlineStr">
         <is>
@@ -23141,9 +23854,6 @@
           <t>Gasto público en educación como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N298" t="n">
-        <v>4.31067991256714</v>
-      </c>
       <c r="O298" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -23151,7 +23861,7 @@
       </c>
       <c r="P298" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -23187,7 +23897,7 @@
         </is>
       </c>
       <c r="G299" t="n">
-        <v>1993</v>
+        <v>1990</v>
       </c>
       <c r="H299" t="inlineStr">
         <is>
@@ -23220,7 +23930,7 @@
         </is>
       </c>
       <c r="N299" t="n">
-        <v>3.81783008575439</v>
+        <v>2.44671010971069</v>
       </c>
       <c r="O299" t="inlineStr">
         <is>
@@ -23229,7 +23939,7 @@
       </c>
       <c r="P299" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -23265,7 +23975,7 @@
         </is>
       </c>
       <c r="G300" t="n">
-        <v>1994</v>
+        <v>1991</v>
       </c>
       <c r="H300" t="inlineStr">
         <is>
@@ -23297,9 +24007,6 @@
           <t>Gasto público en educación como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N300" t="n">
-        <v>5.00603008270264</v>
-      </c>
       <c r="O300" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -23307,7 +24014,7 @@
       </c>
       <c r="P300" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -23343,7 +24050,7 @@
         </is>
       </c>
       <c r="G301" t="n">
-        <v>1995</v>
+        <v>1992</v>
       </c>
       <c r="H301" t="inlineStr">
         <is>
@@ -23375,6 +24082,9 @@
           <t>Gasto público en educación como porcentaje del PIB</t>
         </is>
       </c>
+      <c r="N301" t="n">
+        <v>4.31067991256714</v>
+      </c>
       <c r="O301" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -23382,7 +24092,7 @@
       </c>
       <c r="P301" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -23418,7 +24128,7 @@
         </is>
       </c>
       <c r="G302" t="n">
-        <v>1996</v>
+        <v>1993</v>
       </c>
       <c r="H302" t="inlineStr">
         <is>
@@ -23450,6 +24160,9 @@
           <t>Gasto público en educación como porcentaje del PIB</t>
         </is>
       </c>
+      <c r="N302" t="n">
+        <v>3.81783008575439</v>
+      </c>
       <c r="O302" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -23457,7 +24170,7 @@
       </c>
       <c r="P302" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -23493,7 +24206,7 @@
         </is>
       </c>
       <c r="G303" t="n">
-        <v>1997</v>
+        <v>1994</v>
       </c>
       <c r="H303" t="inlineStr">
         <is>
@@ -23525,6 +24238,9 @@
           <t>Gasto público en educación como porcentaje del PIB</t>
         </is>
       </c>
+      <c r="N303" t="n">
+        <v>5.00603008270264</v>
+      </c>
       <c r="O303" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -23532,7 +24248,7 @@
       </c>
       <c r="P303" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -23568,7 +24284,7 @@
         </is>
       </c>
       <c r="G304" t="n">
-        <v>1998</v>
+        <v>1995</v>
       </c>
       <c r="H304" t="inlineStr">
         <is>
@@ -23607,7 +24323,7 @@
       </c>
       <c r="P304" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -23643,7 +24359,7 @@
         </is>
       </c>
       <c r="G305" t="n">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="H305" t="inlineStr">
         <is>
@@ -23682,7 +24398,7 @@
       </c>
       <c r="P305" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -23718,7 +24434,7 @@
         </is>
       </c>
       <c r="G306" t="n">
-        <v>2000</v>
+        <v>1997</v>
       </c>
       <c r="H306" t="inlineStr">
         <is>
@@ -23757,7 +24473,7 @@
       </c>
       <c r="P306" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -23793,7 +24509,7 @@
         </is>
       </c>
       <c r="G307" t="n">
-        <v>2001</v>
+        <v>1998</v>
       </c>
       <c r="H307" t="inlineStr">
         <is>
@@ -23832,7 +24548,7 @@
       </c>
       <c r="P307" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -23868,7 +24584,7 @@
         </is>
       </c>
       <c r="G308" t="n">
-        <v>2002</v>
+        <v>1999</v>
       </c>
       <c r="H308" t="inlineStr">
         <is>
@@ -23907,7 +24623,7 @@
       </c>
       <c r="P308" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -23943,7 +24659,7 @@
         </is>
       </c>
       <c r="G309" t="n">
-        <v>2003</v>
+        <v>2000</v>
       </c>
       <c r="H309" t="inlineStr">
         <is>
@@ -23982,7 +24698,7 @@
       </c>
       <c r="P309" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -24018,7 +24734,7 @@
         </is>
       </c>
       <c r="G310" t="n">
-        <v>2004</v>
+        <v>2001</v>
       </c>
       <c r="H310" t="inlineStr">
         <is>
@@ -24057,7 +24773,7 @@
       </c>
       <c r="P310" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -24093,7 +24809,7 @@
         </is>
       </c>
       <c r="G311" t="n">
-        <v>2005</v>
+        <v>2002</v>
       </c>
       <c r="H311" t="inlineStr">
         <is>
@@ -24132,7 +24848,7 @@
       </c>
       <c r="P311" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -24168,7 +24884,7 @@
         </is>
       </c>
       <c r="G312" t="n">
-        <v>2006</v>
+        <v>2003</v>
       </c>
       <c r="H312" t="inlineStr">
         <is>
@@ -24200,9 +24916,6 @@
           <t>Gasto público en educación como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N312" t="n">
-        <v>3.66905999183655</v>
-      </c>
       <c r="O312" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -24210,7 +24923,7 @@
       </c>
       <c r="P312" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -24246,7 +24959,7 @@
         </is>
       </c>
       <c r="G313" t="n">
-        <v>2007</v>
+        <v>2004</v>
       </c>
       <c r="H313" t="inlineStr">
         <is>
@@ -24278,9 +24991,6 @@
           <t>Gasto público en educación como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N313" t="n">
-        <v>3.62732005119324</v>
-      </c>
       <c r="O313" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -24288,7 +24998,7 @@
       </c>
       <c r="P313" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -24324,7 +25034,7 @@
         </is>
       </c>
       <c r="G314" t="n">
-        <v>2008</v>
+        <v>2005</v>
       </c>
       <c r="H314" t="inlineStr">
         <is>
@@ -24363,7 +25073,7 @@
       </c>
       <c r="P314" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -24399,7 +25109,7 @@
         </is>
       </c>
       <c r="G315" t="n">
-        <v>2009</v>
+        <v>2006</v>
       </c>
       <c r="H315" t="inlineStr">
         <is>
@@ -24432,7 +25142,7 @@
         </is>
       </c>
       <c r="N315" t="n">
-        <v>6.87467002868652</v>
+        <v>3.66905999183655</v>
       </c>
       <c r="O315" t="inlineStr">
         <is>
@@ -24441,7 +25151,7 @@
       </c>
       <c r="P315" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -24477,7 +25187,7 @@
         </is>
       </c>
       <c r="G316" t="n">
-        <v>2010</v>
+        <v>2007</v>
       </c>
       <c r="H316" t="inlineStr">
         <is>
@@ -24509,6 +25219,9 @@
           <t>Gasto público en educación como porcentaje del PIB</t>
         </is>
       </c>
+      <c r="N316" t="n">
+        <v>3.62732005119324</v>
+      </c>
       <c r="O316" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -24516,7 +25229,7 @@
       </c>
       <c r="P316" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -24552,7 +25265,7 @@
         </is>
       </c>
       <c r="G317" t="n">
-        <v>2011</v>
+        <v>2008</v>
       </c>
       <c r="H317" t="inlineStr">
         <is>
@@ -24591,7 +25304,7 @@
       </c>
       <c r="P317" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -24627,7 +25340,7 @@
         </is>
       </c>
       <c r="G318" t="n">
-        <v>2012</v>
+        <v>2009</v>
       </c>
       <c r="H318" t="inlineStr">
         <is>
@@ -24659,6 +25372,9 @@
           <t>Gasto público en educación como porcentaje del PIB</t>
         </is>
       </c>
+      <c r="N318" t="n">
+        <v>6.87467002868652</v>
+      </c>
       <c r="O318" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -24666,7 +25382,7 @@
       </c>
       <c r="P318" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -24702,7 +25418,7 @@
         </is>
       </c>
       <c r="G319" t="n">
-        <v>2013</v>
+        <v>2010</v>
       </c>
       <c r="H319" t="inlineStr">
         <is>
@@ -24741,7 +25457,7 @@
       </c>
       <c r="P319" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -24777,7 +25493,7 @@
         </is>
       </c>
       <c r="G320" t="n">
-        <v>2014</v>
+        <v>2011</v>
       </c>
       <c r="H320" t="inlineStr">
         <is>
@@ -24816,7 +25532,7 @@
       </c>
       <c r="P320" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -24852,7 +25568,7 @@
         </is>
       </c>
       <c r="G321" t="n">
-        <v>2015</v>
+        <v>2012</v>
       </c>
       <c r="H321" t="inlineStr">
         <is>
@@ -24891,7 +25607,7 @@
       </c>
       <c r="P321" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -24927,7 +25643,7 @@
         </is>
       </c>
       <c r="G322" t="n">
-        <v>2016</v>
+        <v>2013</v>
       </c>
       <c r="H322" t="inlineStr">
         <is>
@@ -24966,7 +25682,7 @@
       </c>
       <c r="P322" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -25002,7 +25718,7 @@
         </is>
       </c>
       <c r="G323" t="n">
-        <v>2017</v>
+        <v>2014</v>
       </c>
       <c r="H323" t="inlineStr">
         <is>
@@ -25041,7 +25757,7 @@
       </c>
       <c r="P323" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -25077,7 +25793,7 @@
         </is>
       </c>
       <c r="G324" t="n">
-        <v>2018</v>
+        <v>2015</v>
       </c>
       <c r="H324" t="inlineStr">
         <is>
@@ -25116,7 +25832,7 @@
       </c>
       <c r="P324" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -25152,7 +25868,7 @@
         </is>
       </c>
       <c r="G325" t="n">
-        <v>2019</v>
+        <v>2016</v>
       </c>
       <c r="H325" t="inlineStr">
         <is>
@@ -25191,7 +25907,7 @@
       </c>
       <c r="P325" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -25227,7 +25943,7 @@
         </is>
       </c>
       <c r="G326" t="n">
-        <v>2020</v>
+        <v>2017</v>
       </c>
       <c r="H326" t="inlineStr">
         <is>
@@ -25266,7 +25982,7 @@
       </c>
       <c r="P326" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -25302,7 +26018,7 @@
         </is>
       </c>
       <c r="G327" t="n">
-        <v>2021</v>
+        <v>2018</v>
       </c>
       <c r="H327" t="inlineStr">
         <is>
@@ -25341,7 +26057,7 @@
       </c>
       <c r="P327" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -25377,7 +26093,7 @@
         </is>
       </c>
       <c r="G328" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="H328" t="inlineStr">
         <is>
@@ -25416,7 +26132,7 @@
       </c>
       <c r="P328" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -25452,7 +26168,7 @@
         </is>
       </c>
       <c r="G329" t="n">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="H329" t="inlineStr">
         <is>
@@ -25491,7 +26207,7 @@
       </c>
       <c r="P329" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -25527,7 +26243,7 @@
         </is>
       </c>
       <c r="G330" t="n">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="H330" t="inlineStr">
         <is>
@@ -25566,7 +26282,7 @@
       </c>
       <c r="P330" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -25602,46 +26318,271 @@
         </is>
       </c>
       <c r="G331" t="n">
+        <v>2022</v>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>educacion</t>
+        </is>
+      </c>
+      <c r="J331" t="inlineStr">
+        <is>
+          <t>Gasto educativo</t>
+        </is>
+      </c>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>gasto_educativo</t>
+        </is>
+      </c>
+      <c r="L331" t="inlineStr">
+        <is>
+          <t>SE.XPD.TOTL.GD.ZS</t>
+        </is>
+      </c>
+      <c r="M331" t="inlineStr">
+        <is>
+          <t>Gasto público en educación como porcentaje del PIB</t>
+        </is>
+      </c>
+      <c r="O331" t="inlineStr">
+        <is>
+          <t>Banco Mundial - World Development Indicators</t>
+        </is>
+      </c>
+      <c r="P331" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>Venezuela</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>Venezuela, RB</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>Latin America &amp; Caribbean</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>Not classified</t>
+        </is>
+      </c>
+      <c r="G332" t="n">
+        <v>2023</v>
+      </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="I332" t="inlineStr">
+        <is>
+          <t>educacion</t>
+        </is>
+      </c>
+      <c r="J332" t="inlineStr">
+        <is>
+          <t>Gasto educativo</t>
+        </is>
+      </c>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>gasto_educativo</t>
+        </is>
+      </c>
+      <c r="L332" t="inlineStr">
+        <is>
+          <t>SE.XPD.TOTL.GD.ZS</t>
+        </is>
+      </c>
+      <c r="M332" t="inlineStr">
+        <is>
+          <t>Gasto público en educación como porcentaje del PIB</t>
+        </is>
+      </c>
+      <c r="O332" t="inlineStr">
+        <is>
+          <t>Banco Mundial - World Development Indicators</t>
+        </is>
+      </c>
+      <c r="P332" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>Venezuela</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>Venezuela, RB</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>Latin America &amp; Caribbean</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>Not classified</t>
+        </is>
+      </c>
+      <c r="G333" t="n">
+        <v>2024</v>
+      </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="I333" t="inlineStr">
+        <is>
+          <t>educacion</t>
+        </is>
+      </c>
+      <c r="J333" t="inlineStr">
+        <is>
+          <t>Gasto educativo</t>
+        </is>
+      </c>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>gasto_educativo</t>
+        </is>
+      </c>
+      <c r="L333" t="inlineStr">
+        <is>
+          <t>SE.XPD.TOTL.GD.ZS</t>
+        </is>
+      </c>
+      <c r="M333" t="inlineStr">
+        <is>
+          <t>Gasto público en educación como porcentaje del PIB</t>
+        </is>
+      </c>
+      <c r="O333" t="inlineStr">
+        <is>
+          <t>Banco Mundial - World Development Indicators</t>
+        </is>
+      </c>
+      <c r="P333" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>Venezuela</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>Venezuela, RB</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>Latin America &amp; Caribbean</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>Not classified</t>
+        </is>
+      </c>
+      <c r="G334" t="n">
         <v>2025</v>
       </c>
-      <c r="H331" t="inlineStr">
-        <is>
-          <t>Educación</t>
-        </is>
-      </c>
-      <c r="I331" t="inlineStr">
-        <is>
-          <t>educacion</t>
-        </is>
-      </c>
-      <c r="J331" t="inlineStr">
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="I334" t="inlineStr">
+        <is>
+          <t>educacion</t>
+        </is>
+      </c>
+      <c r="J334" t="inlineStr">
         <is>
           <t>Gasto educativo</t>
         </is>
       </c>
-      <c r="K331" t="inlineStr">
+      <c r="K334" t="inlineStr">
         <is>
           <t>gasto_educativo</t>
         </is>
       </c>
-      <c r="L331" t="inlineStr">
+      <c r="L334" t="inlineStr">
         <is>
           <t>SE.XPD.TOTL.GD.ZS</t>
         </is>
       </c>
-      <c r="M331" t="inlineStr">
+      <c r="M334" t="inlineStr">
         <is>
           <t>Gasto público en educación como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="O331" t="inlineStr">
-        <is>
-          <t>Banco Mundial - World Development Indicators</t>
-        </is>
-      </c>
-      <c r="P331" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
+      <c r="O334" t="inlineStr">
+        <is>
+          <t>Banco Mundial - World Development Indicators</t>
+        </is>
+      </c>
+      <c r="P334" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -25691,7 +26632,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -25712,7 +26653,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
   </sheetData>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_educacion.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_educacion.xlsx
@@ -17,7 +17,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="[$-es-ES]#,##0"/>
+    <numFmt numFmtId="165" formatCode="[$-es-ES]#,##0.00"/>
+  </numFmts>
   <fonts count="5">
     <font>
       <name val="Calibri"/>
@@ -69,7 +72,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -83,6 +86,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -114,6 +123,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -144,6 +156,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -597,7 +612,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="G7" s="7" t="n">
         <v>1960</v>
       </c>
       <c r="H7" s="4" t="inlineStr">
@@ -674,7 +689,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="G8" s="7" t="n">
         <v>1961</v>
       </c>
       <c r="H8" s="4" t="inlineStr">
@@ -751,7 +766,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G9" s="4" t="n">
+      <c r="G9" s="7" t="n">
         <v>1962</v>
       </c>
       <c r="H9" s="4" t="inlineStr">
@@ -828,7 +843,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G10" s="4" t="n">
+      <c r="G10" s="7" t="n">
         <v>1963</v>
       </c>
       <c r="H10" s="4" t="inlineStr">
@@ -905,7 +920,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G11" s="4" t="n">
+      <c r="G11" s="7" t="n">
         <v>1964</v>
       </c>
       <c r="H11" s="4" t="inlineStr">
@@ -982,7 +997,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G12" s="4" t="n">
+      <c r="G12" s="7" t="n">
         <v>1965</v>
       </c>
       <c r="H12" s="4" t="inlineStr">
@@ -1059,7 +1074,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G13" s="4" t="n">
+      <c r="G13" s="7" t="n">
         <v>1966</v>
       </c>
       <c r="H13" s="4" t="inlineStr">
@@ -1136,7 +1151,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G14" s="4" t="n">
+      <c r="G14" s="7" t="n">
         <v>1967</v>
       </c>
       <c r="H14" s="4" t="inlineStr">
@@ -1213,7 +1228,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G15" s="4" t="n">
+      <c r="G15" s="7" t="n">
         <v>1968</v>
       </c>
       <c r="H15" s="4" t="inlineStr">
@@ -1290,7 +1305,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G16" s="4" t="n">
+      <c r="G16" s="7" t="n">
         <v>1969</v>
       </c>
       <c r="H16" s="4" t="inlineStr">
@@ -1367,7 +1382,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G17" s="4" t="n">
+      <c r="G17" s="7" t="n">
         <v>1970</v>
       </c>
       <c r="H17" s="4" t="inlineStr">
@@ -1444,7 +1459,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G18" s="4" t="n">
+      <c r="G18" s="7" t="n">
         <v>1971</v>
       </c>
       <c r="H18" s="4" t="inlineStr">
@@ -1521,7 +1536,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G19" s="4" t="n">
+      <c r="G19" s="7" t="n">
         <v>1972</v>
       </c>
       <c r="H19" s="4" t="inlineStr">
@@ -1598,7 +1613,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G20" s="4" t="n">
+      <c r="G20" s="7" t="n">
         <v>1973</v>
       </c>
       <c r="H20" s="4" t="inlineStr">
@@ -1675,7 +1690,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G21" s="4" t="n">
+      <c r="G21" s="7" t="n">
         <v>1974</v>
       </c>
       <c r="H21" s="4" t="inlineStr">
@@ -1752,7 +1767,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G22" s="4" t="n">
+      <c r="G22" s="7" t="n">
         <v>1975</v>
       </c>
       <c r="H22" s="4" t="inlineStr">
@@ -1829,7 +1844,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G23" s="4" t="n">
+      <c r="G23" s="7" t="n">
         <v>1976</v>
       </c>
       <c r="H23" s="4" t="inlineStr">
@@ -1906,7 +1921,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G24" s="4" t="n">
+      <c r="G24" s="7" t="n">
         <v>1977</v>
       </c>
       <c r="H24" s="4" t="inlineStr">
@@ -1983,7 +1998,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G25" s="4" t="n">
+      <c r="G25" s="7" t="n">
         <v>1978</v>
       </c>
       <c r="H25" s="4" t="inlineStr">
@@ -2060,7 +2075,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G26" s="4" t="n">
+      <c r="G26" s="7" t="n">
         <v>1979</v>
       </c>
       <c r="H26" s="4" t="inlineStr">
@@ -2137,7 +2152,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G27" s="4" t="n">
+      <c r="G27" s="7" t="n">
         <v>1980</v>
       </c>
       <c r="H27" s="4" t="inlineStr">
@@ -2214,7 +2229,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G28" s="4" t="n">
+      <c r="G28" s="7" t="n">
         <v>1981</v>
       </c>
       <c r="H28" s="4" t="inlineStr">
@@ -2247,7 +2262,7 @@
           <t>Tasa de alfabetización adulta</t>
         </is>
       </c>
-      <c r="N28" s="4" t="n">
+      <c r="N28" s="8" t="n">
         <v>84.73000335693359</v>
       </c>
       <c r="O28" s="4" t="inlineStr">
@@ -2293,7 +2308,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G29" s="4" t="n">
+      <c r="G29" s="7" t="n">
         <v>1982</v>
       </c>
       <c r="H29" s="4" t="inlineStr">
@@ -2370,7 +2385,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G30" s="4" t="n">
+      <c r="G30" s="7" t="n">
         <v>1983</v>
       </c>
       <c r="H30" s="4" t="inlineStr">
@@ -2447,7 +2462,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G31" s="4" t="n">
+      <c r="G31" s="7" t="n">
         <v>1984</v>
       </c>
       <c r="H31" s="4" t="inlineStr">
@@ -2524,7 +2539,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G32" s="4" t="n">
+      <c r="G32" s="7" t="n">
         <v>1985</v>
       </c>
       <c r="H32" s="4" t="inlineStr">
@@ -2601,7 +2616,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G33" s="4" t="n">
+      <c r="G33" s="7" t="n">
         <v>1986</v>
       </c>
       <c r="H33" s="4" t="inlineStr">
@@ -2678,7 +2693,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G34" s="4" t="n">
+      <c r="G34" s="7" t="n">
         <v>1987</v>
       </c>
       <c r="H34" s="4" t="inlineStr">
@@ -2755,7 +2770,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G35" s="4" t="n">
+      <c r="G35" s="7" t="n">
         <v>1988</v>
       </c>
       <c r="H35" s="4" t="inlineStr">
@@ -2832,7 +2847,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G36" s="4" t="n">
+      <c r="G36" s="7" t="n">
         <v>1989</v>
       </c>
       <c r="H36" s="4" t="inlineStr">
@@ -2909,7 +2924,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G37" s="4" t="n">
+      <c r="G37" s="7" t="n">
         <v>1990</v>
       </c>
       <c r="H37" s="4" t="inlineStr">
@@ -2942,7 +2957,7 @@
           <t>Tasa de alfabetización adulta</t>
         </is>
       </c>
-      <c r="N37" s="4" t="n">
+      <c r="N37" s="8" t="n">
         <v>89.8300018310547</v>
       </c>
       <c r="O37" s="4" t="inlineStr">
@@ -2988,7 +3003,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G38" s="4" t="n">
+      <c r="G38" s="7" t="n">
         <v>1991</v>
       </c>
       <c r="H38" s="4" t="inlineStr">
@@ -3065,7 +3080,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G39" s="4" t="n">
+      <c r="G39" s="7" t="n">
         <v>1992</v>
       </c>
       <c r="H39" s="4" t="inlineStr">
@@ -3142,7 +3157,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G40" s="4" t="n">
+      <c r="G40" s="7" t="n">
         <v>1993</v>
       </c>
       <c r="H40" s="4" t="inlineStr">
@@ -3219,7 +3234,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G41" s="4" t="n">
+      <c r="G41" s="7" t="n">
         <v>1994</v>
       </c>
       <c r="H41" s="4" t="inlineStr">
@@ -3296,7 +3311,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G42" s="4" t="n">
+      <c r="G42" s="7" t="n">
         <v>1995</v>
       </c>
       <c r="H42" s="4" t="inlineStr">
@@ -3373,7 +3388,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G43" s="4" t="n">
+      <c r="G43" s="7" t="n">
         <v>1996</v>
       </c>
       <c r="H43" s="4" t="inlineStr">
@@ -3450,7 +3465,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G44" s="4" t="n">
+      <c r="G44" s="7" t="n">
         <v>1997</v>
       </c>
       <c r="H44" s="4" t="inlineStr">
@@ -3527,7 +3542,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G45" s="4" t="n">
+      <c r="G45" s="7" t="n">
         <v>1998</v>
       </c>
       <c r="H45" s="4" t="inlineStr">
@@ -3604,7 +3619,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G46" s="4" t="n">
+      <c r="G46" s="7" t="n">
         <v>1999</v>
       </c>
       <c r="H46" s="4" t="inlineStr">
@@ -3681,7 +3696,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G47" s="4" t="n">
+      <c r="G47" s="7" t="n">
         <v>2000</v>
       </c>
       <c r="H47" s="4" t="inlineStr">
@@ -3758,7 +3773,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G48" s="4" t="n">
+      <c r="G48" s="7" t="n">
         <v>2001</v>
       </c>
       <c r="H48" s="4" t="inlineStr">
@@ -3791,7 +3806,7 @@
           <t>Tasa de alfabetización adulta</t>
         </is>
       </c>
-      <c r="N48" s="4" t="n">
+      <c r="N48" s="8" t="n">
         <v>92.98000335693359</v>
       </c>
       <c r="O48" s="4" t="inlineStr">
@@ -3837,7 +3852,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G49" s="4" t="n">
+      <c r="G49" s="7" t="n">
         <v>2002</v>
       </c>
       <c r="H49" s="4" t="inlineStr">
@@ -3914,7 +3929,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G50" s="4" t="n">
+      <c r="G50" s="7" t="n">
         <v>2003</v>
       </c>
       <c r="H50" s="4" t="inlineStr">
@@ -3991,7 +4006,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G51" s="4" t="n">
+      <c r="G51" s="7" t="n">
         <v>2004</v>
       </c>
       <c r="H51" s="4" t="inlineStr">
@@ -4068,7 +4083,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G52" s="4" t="n">
+      <c r="G52" s="7" t="n">
         <v>2005</v>
       </c>
       <c r="H52" s="4" t="inlineStr">
@@ -4101,7 +4116,7 @@
           <t>Tasa de alfabetización adulta</t>
         </is>
       </c>
-      <c r="N52" s="4" t="n">
+      <c r="N52" s="8" t="n">
         <v>94.37070138031279</v>
       </c>
       <c r="O52" s="4" t="inlineStr">
@@ -4147,7 +4162,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G53" s="4" t="n">
+      <c r="G53" s="7" t="n">
         <v>2006</v>
       </c>
       <c r="H53" s="4" t="inlineStr">
@@ -4180,7 +4195,7 @@
           <t>Tasa de alfabetización adulta</t>
         </is>
       </c>
-      <c r="N53" s="4" t="n">
+      <c r="N53" s="8" t="n">
         <v>94.6620701964151</v>
       </c>
       <c r="O53" s="4" t="inlineStr">
@@ -4226,7 +4241,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G54" s="4" t="n">
+      <c r="G54" s="7" t="n">
         <v>2007</v>
       </c>
       <c r="H54" s="4" t="inlineStr">
@@ -4259,7 +4274,7 @@
           <t>Tasa de alfabetización adulta</t>
         </is>
       </c>
-      <c r="N54" s="4" t="n">
+      <c r="N54" s="8" t="n">
         <v>95.15000152587891</v>
       </c>
       <c r="O54" s="4" t="inlineStr">
@@ -4305,7 +4320,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G55" s="4" t="n">
+      <c r="G55" s="7" t="n">
         <v>2008</v>
       </c>
       <c r="H55" s="4" t="inlineStr">
@@ -4338,7 +4353,7 @@
           <t>Tasa de alfabetización adulta</t>
         </is>
       </c>
-      <c r="N55" s="4" t="n">
+      <c r="N55" s="8" t="n">
         <v>95.3116995541662</v>
       </c>
       <c r="O55" s="4" t="inlineStr">
@@ -4384,7 +4399,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G56" s="4" t="n">
+      <c r="G56" s="7" t="n">
         <v>2009</v>
       </c>
       <c r="H56" s="4" t="inlineStr">
@@ -4417,7 +4432,7 @@
           <t>Tasa de alfabetización adulta</t>
         </is>
       </c>
-      <c r="N56" s="4" t="n">
+      <c r="N56" s="8" t="n">
         <v>95.5100021362305</v>
       </c>
       <c r="O56" s="4" t="inlineStr">
@@ -4463,7 +4478,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G57" s="4" t="n">
+      <c r="G57" s="7" t="n">
         <v>2010</v>
       </c>
       <c r="H57" s="4" t="inlineStr">
@@ -4496,7 +4511,7 @@
           <t>Tasa de alfabetización adulta</t>
         </is>
       </c>
-      <c r="N57" s="4" t="n">
+      <c r="N57" s="8" t="n">
         <v>95.39242132337429</v>
       </c>
       <c r="O57" s="4" t="inlineStr">
@@ -4542,7 +4557,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G58" s="4" t="n">
+      <c r="G58" s="7" t="n">
         <v>2011</v>
       </c>
       <c r="H58" s="4" t="inlineStr">
@@ -4575,7 +4590,7 @@
           <t>Tasa de alfabetización adulta</t>
         </is>
       </c>
-      <c r="N58" s="4" t="n">
+      <c r="N58" s="8" t="n">
         <v>94.76999664306641</v>
       </c>
       <c r="O58" s="4" t="inlineStr">
@@ -4621,7 +4636,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G59" s="4" t="n">
+      <c r="G59" s="7" t="n">
         <v>2012</v>
       </c>
       <c r="H59" s="4" t="inlineStr">
@@ -4654,7 +4669,7 @@
           <t>Tasa de alfabetización adulta</t>
         </is>
       </c>
-      <c r="N59" s="4" t="n">
+      <c r="N59" s="8" t="n">
         <v>95.9871889937429</v>
       </c>
       <c r="O59" s="4" t="inlineStr">
@@ -4700,7 +4715,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G60" s="4" t="n">
+      <c r="G60" s="7" t="n">
         <v>2013</v>
       </c>
       <c r="H60" s="4" t="inlineStr">
@@ -4777,7 +4792,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G61" s="4" t="n">
+      <c r="G61" s="7" t="n">
         <v>2014</v>
       </c>
       <c r="H61" s="4" t="inlineStr">
@@ -4854,7 +4869,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G62" s="4" t="n">
+      <c r="G62" s="7" t="n">
         <v>2015</v>
       </c>
       <c r="H62" s="4" t="inlineStr">
@@ -4887,7 +4902,7 @@
           <t>Tasa de alfabetización adulta</t>
         </is>
       </c>
-      <c r="N62" s="4" t="n">
+      <c r="N62" s="8" t="n">
         <v>96.61000061035161</v>
       </c>
       <c r="O62" s="4" t="inlineStr">
@@ -4933,7 +4948,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G63" s="4" t="n">
+      <c r="G63" s="7" t="n">
         <v>2016</v>
       </c>
       <c r="H63" s="4" t="inlineStr">
@@ -4966,7 +4981,7 @@
           <t>Tasa de alfabetización adulta</t>
         </is>
       </c>
-      <c r="N63" s="4" t="n">
+      <c r="N63" s="8" t="n">
         <v>97.129997253418</v>
       </c>
       <c r="O63" s="4" t="inlineStr">
@@ -5012,7 +5027,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G64" s="4" t="n">
+      <c r="G64" s="7" t="n">
         <v>2017</v>
       </c>
       <c r="H64" s="4" t="inlineStr">
@@ -5045,7 +5060,7 @@
           <t>Tasa de alfabetización adulta</t>
         </is>
       </c>
-      <c r="N64" s="4" t="n">
+      <c r="N64" s="8" t="n">
         <v>97.18371831284141</v>
       </c>
       <c r="O64" s="4" t="inlineStr">
@@ -5091,7 +5106,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G65" s="4" t="n">
+      <c r="G65" s="7" t="n">
         <v>2018</v>
       </c>
       <c r="H65" s="4" t="inlineStr">
@@ -5168,7 +5183,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G66" s="4" t="n">
+      <c r="G66" s="7" t="n">
         <v>2019</v>
       </c>
       <c r="H66" s="4" t="inlineStr">
@@ -5245,7 +5260,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G67" s="4" t="n">
+      <c r="G67" s="7" t="n">
         <v>2020</v>
       </c>
       <c r="H67" s="4" t="inlineStr">
@@ -5322,7 +5337,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G68" s="4" t="n">
+      <c r="G68" s="7" t="n">
         <v>2021</v>
       </c>
       <c r="H68" s="4" t="inlineStr">
@@ -5399,7 +5414,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G69" s="4" t="n">
+      <c r="G69" s="7" t="n">
         <v>2022</v>
       </c>
       <c r="H69" s="4" t="inlineStr">
@@ -5476,7 +5491,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G70" s="4" t="n">
+      <c r="G70" s="7" t="n">
         <v>2023</v>
       </c>
       <c r="H70" s="4" t="inlineStr">
@@ -5553,7 +5568,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G71" s="4" t="n">
+      <c r="G71" s="7" t="n">
         <v>2024</v>
       </c>
       <c r="H71" s="4" t="inlineStr">
@@ -5630,7 +5645,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G72" s="4" t="n">
+      <c r="G72" s="7" t="n">
         <v>2025</v>
       </c>
       <c r="H72" s="4" t="inlineStr">
@@ -5707,7 +5722,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G73" s="4" t="n">
+      <c r="G73" s="7" t="n">
         <v>1960</v>
       </c>
       <c r="H73" s="4" t="inlineStr">
@@ -5788,7 +5803,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G74" s="4" t="n">
+      <c r="G74" s="7" t="n">
         <v>1961</v>
       </c>
       <c r="H74" s="4" t="inlineStr">
@@ -5869,7 +5884,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G75" s="4" t="n">
+      <c r="G75" s="7" t="n">
         <v>1962</v>
       </c>
       <c r="H75" s="4" t="inlineStr">
@@ -5950,7 +5965,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G76" s="4" t="n">
+      <c r="G76" s="7" t="n">
         <v>1963</v>
       </c>
       <c r="H76" s="4" t="inlineStr">
@@ -6031,7 +6046,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G77" s="4" t="n">
+      <c r="G77" s="7" t="n">
         <v>1964</v>
       </c>
       <c r="H77" s="4" t="inlineStr">
@@ -6112,7 +6127,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G78" s="4" t="n">
+      <c r="G78" s="7" t="n">
         <v>1965</v>
       </c>
       <c r="H78" s="4" t="inlineStr">
@@ -6193,7 +6208,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G79" s="4" t="n">
+      <c r="G79" s="7" t="n">
         <v>1966</v>
       </c>
       <c r="H79" s="4" t="inlineStr">
@@ -6274,7 +6289,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G80" s="4" t="n">
+      <c r="G80" s="7" t="n">
         <v>1967</v>
       </c>
       <c r="H80" s="4" t="inlineStr">
@@ -6355,7 +6370,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G81" s="4" t="n">
+      <c r="G81" s="7" t="n">
         <v>1968</v>
       </c>
       <c r="H81" s="4" t="inlineStr">
@@ -6436,7 +6451,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G82" s="4" t="n">
+      <c r="G82" s="7" t="n">
         <v>1969</v>
       </c>
       <c r="H82" s="4" t="inlineStr">
@@ -6517,7 +6532,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G83" s="4" t="n">
+      <c r="G83" s="7" t="n">
         <v>1970</v>
       </c>
       <c r="H83" s="4" t="inlineStr">
@@ -6598,7 +6613,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G84" s="4" t="n">
+      <c r="G84" s="7" t="n">
         <v>1971</v>
       </c>
       <c r="H84" s="4" t="inlineStr">
@@ -6679,7 +6694,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G85" s="4" t="n">
+      <c r="G85" s="7" t="n">
         <v>1972</v>
       </c>
       <c r="H85" s="4" t="inlineStr">
@@ -6760,7 +6775,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G86" s="4" t="n">
+      <c r="G86" s="7" t="n">
         <v>1973</v>
       </c>
       <c r="H86" s="4" t="inlineStr">
@@ -6841,7 +6856,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G87" s="4" t="n">
+      <c r="G87" s="7" t="n">
         <v>1974</v>
       </c>
       <c r="H87" s="4" t="inlineStr">
@@ -6922,7 +6937,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G88" s="4" t="n">
+      <c r="G88" s="7" t="n">
         <v>1975</v>
       </c>
       <c r="H88" s="4" t="inlineStr">
@@ -7003,7 +7018,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G89" s="4" t="n">
+      <c r="G89" s="7" t="n">
         <v>1976</v>
       </c>
       <c r="H89" s="4" t="inlineStr">
@@ -7084,7 +7099,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G90" s="4" t="n">
+      <c r="G90" s="7" t="n">
         <v>1977</v>
       </c>
       <c r="H90" s="4" t="inlineStr">
@@ -7165,7 +7180,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G91" s="4" t="n">
+      <c r="G91" s="7" t="n">
         <v>1978</v>
       </c>
       <c r="H91" s="4" t="inlineStr">
@@ -7246,7 +7261,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G92" s="4" t="n">
+      <c r="G92" s="7" t="n">
         <v>1979</v>
       </c>
       <c r="H92" s="4" t="inlineStr">
@@ -7327,7 +7342,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G93" s="4" t="n">
+      <c r="G93" s="7" t="n">
         <v>1980</v>
       </c>
       <c r="H93" s="4" t="inlineStr">
@@ -7408,7 +7423,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G94" s="4" t="n">
+      <c r="G94" s="7" t="n">
         <v>1981</v>
       </c>
       <c r="H94" s="4" t="inlineStr">
@@ -7489,7 +7504,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G95" s="4" t="n">
+      <c r="G95" s="7" t="n">
         <v>1982</v>
       </c>
       <c r="H95" s="4" t="inlineStr">
@@ -7570,7 +7585,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G96" s="4" t="n">
+      <c r="G96" s="7" t="n">
         <v>1983</v>
       </c>
       <c r="H96" s="4" t="inlineStr">
@@ -7651,7 +7666,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G97" s="4" t="n">
+      <c r="G97" s="7" t="n">
         <v>1984</v>
       </c>
       <c r="H97" s="4" t="inlineStr">
@@ -7732,7 +7747,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G98" s="4" t="n">
+      <c r="G98" s="7" t="n">
         <v>1985</v>
       </c>
       <c r="H98" s="4" t="inlineStr">
@@ -7813,7 +7828,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G99" s="4" t="n">
+      <c r="G99" s="7" t="n">
         <v>1986</v>
       </c>
       <c r="H99" s="4" t="inlineStr">
@@ -7894,7 +7909,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G100" s="4" t="n">
+      <c r="G100" s="7" t="n">
         <v>1987</v>
       </c>
       <c r="H100" s="4" t="inlineStr">
@@ -7975,7 +7990,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G101" s="4" t="n">
+      <c r="G101" s="7" t="n">
         <v>1988</v>
       </c>
       <c r="H101" s="4" t="inlineStr">
@@ -8056,7 +8071,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G102" s="4" t="n">
+      <c r="G102" s="7" t="n">
         <v>1989</v>
       </c>
       <c r="H102" s="4" t="inlineStr">
@@ -8137,7 +8152,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G103" s="4" t="n">
+      <c r="G103" s="7" t="n">
         <v>1990</v>
       </c>
       <c r="H103" s="4" t="inlineStr">
@@ -8218,7 +8233,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G104" s="4" t="n">
+      <c r="G104" s="7" t="n">
         <v>1991</v>
       </c>
       <c r="H104" s="4" t="inlineStr">
@@ -8299,7 +8314,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G105" s="4" t="n">
+      <c r="G105" s="7" t="n">
         <v>1992</v>
       </c>
       <c r="H105" s="4" t="inlineStr">
@@ -8380,7 +8395,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G106" s="4" t="n">
+      <c r="G106" s="7" t="n">
         <v>1993</v>
       </c>
       <c r="H106" s="4" t="inlineStr">
@@ -8461,7 +8476,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G107" s="4" t="n">
+      <c r="G107" s="7" t="n">
         <v>1994</v>
       </c>
       <c r="H107" s="4" t="inlineStr">
@@ -8542,7 +8557,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G108" s="4" t="n">
+      <c r="G108" s="7" t="n">
         <v>1995</v>
       </c>
       <c r="H108" s="4" t="inlineStr">
@@ -8623,7 +8638,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G109" s="4" t="n">
+      <c r="G109" s="7" t="n">
         <v>1996</v>
       </c>
       <c r="H109" s="4" t="inlineStr">
@@ -8704,7 +8719,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G110" s="4" t="n">
+      <c r="G110" s="7" t="n">
         <v>1997</v>
       </c>
       <c r="H110" s="4" t="inlineStr">
@@ -8785,7 +8800,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G111" s="4" t="n">
+      <c r="G111" s="7" t="n">
         <v>1998</v>
       </c>
       <c r="H111" s="4" t="inlineStr">
@@ -8866,7 +8881,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G112" s="4" t="n">
+      <c r="G112" s="7" t="n">
         <v>1999</v>
       </c>
       <c r="H112" s="4" t="inlineStr">
@@ -8947,7 +8962,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G113" s="4" t="n">
+      <c r="G113" s="7" t="n">
         <v>2000</v>
       </c>
       <c r="H113" s="4" t="inlineStr">
@@ -9028,7 +9043,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G114" s="4" t="n">
+      <c r="G114" s="7" t="n">
         <v>2001</v>
       </c>
       <c r="H114" s="4" t="inlineStr">
@@ -9109,7 +9124,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G115" s="4" t="n">
+      <c r="G115" s="7" t="n">
         <v>2002</v>
       </c>
       <c r="H115" s="4" t="inlineStr">
@@ -9190,7 +9205,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G116" s="4" t="n">
+      <c r="G116" s="7" t="n">
         <v>2003</v>
       </c>
       <c r="H116" s="4" t="inlineStr">
@@ -9271,7 +9286,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G117" s="4" t="n">
+      <c r="G117" s="7" t="n">
         <v>2004</v>
       </c>
       <c r="H117" s="4" t="inlineStr">
@@ -9352,7 +9367,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G118" s="4" t="n">
+      <c r="G118" s="7" t="n">
         <v>2005</v>
       </c>
       <c r="H118" s="4" t="inlineStr">
@@ -9433,7 +9448,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G119" s="4" t="n">
+      <c r="G119" s="7" t="n">
         <v>2006</v>
       </c>
       <c r="H119" s="4" t="inlineStr">
@@ -9514,7 +9529,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G120" s="4" t="n">
+      <c r="G120" s="7" t="n">
         <v>2007</v>
       </c>
       <c r="H120" s="4" t="inlineStr">
@@ -9595,7 +9610,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G121" s="4" t="n">
+      <c r="G121" s="7" t="n">
         <v>2008</v>
       </c>
       <c r="H121" s="4" t="inlineStr">
@@ -9676,7 +9691,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G122" s="4" t="n">
+      <c r="G122" s="7" t="n">
         <v>2009</v>
       </c>
       <c r="H122" s="4" t="inlineStr">
@@ -9757,7 +9772,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G123" s="4" t="n">
+      <c r="G123" s="7" t="n">
         <v>2010</v>
       </c>
       <c r="H123" s="4" t="inlineStr">
@@ -9838,7 +9853,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G124" s="4" t="n">
+      <c r="G124" s="7" t="n">
         <v>2011</v>
       </c>
       <c r="H124" s="4" t="inlineStr">
@@ -9919,7 +9934,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G125" s="4" t="n">
+      <c r="G125" s="7" t="n">
         <v>2012</v>
       </c>
       <c r="H125" s="4" t="inlineStr">
@@ -10000,7 +10015,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G126" s="4" t="n">
+      <c r="G126" s="7" t="n">
         <v>2013</v>
       </c>
       <c r="H126" s="4" t="inlineStr">
@@ -10081,7 +10096,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G127" s="4" t="n">
+      <c r="G127" s="7" t="n">
         <v>2014</v>
       </c>
       <c r="H127" s="4" t="inlineStr">
@@ -10162,7 +10177,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G128" s="4" t="n">
+      <c r="G128" s="7" t="n">
         <v>2015</v>
       </c>
       <c r="H128" s="4" t="inlineStr">
@@ -10243,7 +10258,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G129" s="4" t="n">
+      <c r="G129" s="7" t="n">
         <v>2016</v>
       </c>
       <c r="H129" s="4" t="inlineStr">
@@ -10324,7 +10339,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G130" s="4" t="n">
+      <c r="G130" s="7" t="n">
         <v>2017</v>
       </c>
       <c r="H130" s="4" t="inlineStr">
@@ -10405,7 +10420,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G131" s="4" t="n">
+      <c r="G131" s="7" t="n">
         <v>2018</v>
       </c>
       <c r="H131" s="4" t="inlineStr">
@@ -10486,7 +10501,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G132" s="4" t="n">
+      <c r="G132" s="7" t="n">
         <v>2019</v>
       </c>
       <c r="H132" s="4" t="inlineStr">
@@ -10567,7 +10582,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G133" s="4" t="n">
+      <c r="G133" s="7" t="n">
         <v>2020</v>
       </c>
       <c r="H133" s="4" t="inlineStr">
@@ -10648,7 +10663,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G134" s="4" t="n">
+      <c r="G134" s="7" t="n">
         <v>2021</v>
       </c>
       <c r="H134" s="4" t="inlineStr">
@@ -10729,7 +10744,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G135" s="4" t="n">
+      <c r="G135" s="7" t="n">
         <v>2022</v>
       </c>
       <c r="H135" s="4" t="inlineStr">
@@ -10810,7 +10825,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G136" s="4" t="n">
+      <c r="G136" s="7" t="n">
         <v>2023</v>
       </c>
       <c r="H136" s="4" t="inlineStr">
@@ -10891,7 +10906,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G137" s="4" t="n">
+      <c r="G137" s="7" t="n">
         <v>2024</v>
       </c>
       <c r="H137" s="4" t="inlineStr">
@@ -10972,7 +10987,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G138" s="4" t="n">
+      <c r="G138" s="7" t="n">
         <v>2025</v>
       </c>
       <c r="H138" s="4" t="inlineStr">
@@ -11053,7 +11068,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G139" s="4" t="n">
+      <c r="G139" s="7" t="n">
         <v>2026</v>
       </c>
       <c r="H139" s="4" t="inlineStr">
@@ -11134,7 +11149,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G140" s="4" t="n">
+      <c r="G140" s="7" t="n">
         <v>1960</v>
       </c>
       <c r="H140" s="4" t="inlineStr">
@@ -11215,7 +11230,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G141" s="4" t="n">
+      <c r="G141" s="7" t="n">
         <v>1961</v>
       </c>
       <c r="H141" s="4" t="inlineStr">
@@ -11296,7 +11311,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G142" s="4" t="n">
+      <c r="G142" s="7" t="n">
         <v>1962</v>
       </c>
       <c r="H142" s="4" t="inlineStr">
@@ -11377,7 +11392,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G143" s="4" t="n">
+      <c r="G143" s="7" t="n">
         <v>1963</v>
       </c>
       <c r="H143" s="4" t="inlineStr">
@@ -11458,7 +11473,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G144" s="4" t="n">
+      <c r="G144" s="7" t="n">
         <v>1964</v>
       </c>
       <c r="H144" s="4" t="inlineStr">
@@ -11539,7 +11554,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G145" s="4" t="n">
+      <c r="G145" s="7" t="n">
         <v>1965</v>
       </c>
       <c r="H145" s="4" t="inlineStr">
@@ -11620,7 +11635,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G146" s="4" t="n">
+      <c r="G146" s="7" t="n">
         <v>1966</v>
       </c>
       <c r="H146" s="4" t="inlineStr">
@@ -11701,7 +11716,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G147" s="4" t="n">
+      <c r="G147" s="7" t="n">
         <v>1967</v>
       </c>
       <c r="H147" s="4" t="inlineStr">
@@ -11782,7 +11797,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G148" s="4" t="n">
+      <c r="G148" s="7" t="n">
         <v>1968</v>
       </c>
       <c r="H148" s="4" t="inlineStr">
@@ -11863,7 +11878,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G149" s="4" t="n">
+      <c r="G149" s="7" t="n">
         <v>1969</v>
       </c>
       <c r="H149" s="4" t="inlineStr">
@@ -11944,7 +11959,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G150" s="4" t="n">
+      <c r="G150" s="7" t="n">
         <v>1970</v>
       </c>
       <c r="H150" s="4" t="inlineStr">
@@ -12025,7 +12040,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G151" s="4" t="n">
+      <c r="G151" s="7" t="n">
         <v>1971</v>
       </c>
       <c r="H151" s="4" t="inlineStr">
@@ -12106,7 +12121,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G152" s="4" t="n">
+      <c r="G152" s="7" t="n">
         <v>1972</v>
       </c>
       <c r="H152" s="4" t="inlineStr">
@@ -12187,7 +12202,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G153" s="4" t="n">
+      <c r="G153" s="7" t="n">
         <v>1973</v>
       </c>
       <c r="H153" s="4" t="inlineStr">
@@ -12268,7 +12283,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G154" s="4" t="n">
+      <c r="G154" s="7" t="n">
         <v>1974</v>
       </c>
       <c r="H154" s="4" t="inlineStr">
@@ -12349,7 +12364,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G155" s="4" t="n">
+      <c r="G155" s="7" t="n">
         <v>1975</v>
       </c>
       <c r="H155" s="4" t="inlineStr">
@@ -12430,7 +12445,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G156" s="4" t="n">
+      <c r="G156" s="7" t="n">
         <v>1976</v>
       </c>
       <c r="H156" s="4" t="inlineStr">
@@ -12511,7 +12526,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G157" s="4" t="n">
+      <c r="G157" s="7" t="n">
         <v>1977</v>
       </c>
       <c r="H157" s="4" t="inlineStr">
@@ -12592,7 +12607,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G158" s="4" t="n">
+      <c r="G158" s="7" t="n">
         <v>1978</v>
       </c>
       <c r="H158" s="4" t="inlineStr">
@@ -12673,7 +12688,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G159" s="4" t="n">
+      <c r="G159" s="7" t="n">
         <v>1979</v>
       </c>
       <c r="H159" s="4" t="inlineStr">
@@ -12754,7 +12769,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G160" s="4" t="n">
+      <c r="G160" s="7" t="n">
         <v>1980</v>
       </c>
       <c r="H160" s="4" t="inlineStr">
@@ -12835,7 +12850,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G161" s="4" t="n">
+      <c r="G161" s="7" t="n">
         <v>1981</v>
       </c>
       <c r="H161" s="4" t="inlineStr">
@@ -12916,7 +12931,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G162" s="4" t="n">
+      <c r="G162" s="7" t="n">
         <v>1982</v>
       </c>
       <c r="H162" s="4" t="inlineStr">
@@ -12997,7 +13012,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G163" s="4" t="n">
+      <c r="G163" s="7" t="n">
         <v>1983</v>
       </c>
       <c r="H163" s="4" t="inlineStr">
@@ -13078,7 +13093,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G164" s="4" t="n">
+      <c r="G164" s="7" t="n">
         <v>1984</v>
       </c>
       <c r="H164" s="4" t="inlineStr">
@@ -13159,7 +13174,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G165" s="4" t="n">
+      <c r="G165" s="7" t="n">
         <v>1985</v>
       </c>
       <c r="H165" s="4" t="inlineStr">
@@ -13240,7 +13255,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G166" s="4" t="n">
+      <c r="G166" s="7" t="n">
         <v>1986</v>
       </c>
       <c r="H166" s="4" t="inlineStr">
@@ -13321,7 +13336,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G167" s="4" t="n">
+      <c r="G167" s="7" t="n">
         <v>1987</v>
       </c>
       <c r="H167" s="4" t="inlineStr">
@@ -13402,7 +13417,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G168" s="4" t="n">
+      <c r="G168" s="7" t="n">
         <v>1988</v>
       </c>
       <c r="H168" s="4" t="inlineStr">
@@ -13483,7 +13498,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G169" s="4" t="n">
+      <c r="G169" s="7" t="n">
         <v>1989</v>
       </c>
       <c r="H169" s="4" t="inlineStr">
@@ -13564,7 +13579,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G170" s="4" t="n">
+      <c r="G170" s="7" t="n">
         <v>1990</v>
       </c>
       <c r="H170" s="4" t="inlineStr">
@@ -13645,7 +13660,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G171" s="4" t="n">
+      <c r="G171" s="7" t="n">
         <v>1991</v>
       </c>
       <c r="H171" s="4" t="inlineStr">
@@ -13726,7 +13741,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G172" s="4" t="n">
+      <c r="G172" s="7" t="n">
         <v>1992</v>
       </c>
       <c r="H172" s="4" t="inlineStr">
@@ -13807,7 +13822,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G173" s="4" t="n">
+      <c r="G173" s="7" t="n">
         <v>1993</v>
       </c>
       <c r="H173" s="4" t="inlineStr">
@@ -13888,7 +13903,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G174" s="4" t="n">
+      <c r="G174" s="7" t="n">
         <v>1994</v>
       </c>
       <c r="H174" s="4" t="inlineStr">
@@ -13969,7 +13984,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G175" s="4" t="n">
+      <c r="G175" s="7" t="n">
         <v>1995</v>
       </c>
       <c r="H175" s="4" t="inlineStr">
@@ -14050,7 +14065,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G176" s="4" t="n">
+      <c r="G176" s="7" t="n">
         <v>1996</v>
       </c>
       <c r="H176" s="4" t="inlineStr">
@@ -14131,7 +14146,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G177" s="4" t="n">
+      <c r="G177" s="7" t="n">
         <v>1997</v>
       </c>
       <c r="H177" s="4" t="inlineStr">
@@ -14212,7 +14227,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G178" s="4" t="n">
+      <c r="G178" s="7" t="n">
         <v>1998</v>
       </c>
       <c r="H178" s="4" t="inlineStr">
@@ -14293,7 +14308,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G179" s="4" t="n">
+      <c r="G179" s="7" t="n">
         <v>1999</v>
       </c>
       <c r="H179" s="4" t="inlineStr">
@@ -14374,7 +14389,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G180" s="4" t="n">
+      <c r="G180" s="7" t="n">
         <v>2000</v>
       </c>
       <c r="H180" s="4" t="inlineStr">
@@ -14455,7 +14470,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G181" s="4" t="n">
+      <c r="G181" s="7" t="n">
         <v>2001</v>
       </c>
       <c r="H181" s="4" t="inlineStr">
@@ -14536,7 +14551,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G182" s="4" t="n">
+      <c r="G182" s="7" t="n">
         <v>2002</v>
       </c>
       <c r="H182" s="4" t="inlineStr">
@@ -14617,7 +14632,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G183" s="4" t="n">
+      <c r="G183" s="7" t="n">
         <v>2003</v>
       </c>
       <c r="H183" s="4" t="inlineStr">
@@ -14698,7 +14713,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G184" s="4" t="n">
+      <c r="G184" s="7" t="n">
         <v>2004</v>
       </c>
       <c r="H184" s="4" t="inlineStr">
@@ -14779,7 +14794,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G185" s="4" t="n">
+      <c r="G185" s="7" t="n">
         <v>2005</v>
       </c>
       <c r="H185" s="4" t="inlineStr">
@@ -14860,7 +14875,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G186" s="4" t="n">
+      <c r="G186" s="7" t="n">
         <v>2006</v>
       </c>
       <c r="H186" s="4" t="inlineStr">
@@ -14941,7 +14956,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G187" s="4" t="n">
+      <c r="G187" s="7" t="n">
         <v>2007</v>
       </c>
       <c r="H187" s="4" t="inlineStr">
@@ -15022,7 +15037,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G188" s="4" t="n">
+      <c r="G188" s="7" t="n">
         <v>2008</v>
       </c>
       <c r="H188" s="4" t="inlineStr">
@@ -15103,7 +15118,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G189" s="4" t="n">
+      <c r="G189" s="7" t="n">
         <v>2009</v>
       </c>
       <c r="H189" s="4" t="inlineStr">
@@ -15184,7 +15199,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G190" s="4" t="n">
+      <c r="G190" s="7" t="n">
         <v>2010</v>
       </c>
       <c r="H190" s="4" t="inlineStr">
@@ -15265,7 +15280,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G191" s="4" t="n">
+      <c r="G191" s="7" t="n">
         <v>2011</v>
       </c>
       <c r="H191" s="4" t="inlineStr">
@@ -15346,7 +15361,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G192" s="4" t="n">
+      <c r="G192" s="7" t="n">
         <v>2012</v>
       </c>
       <c r="H192" s="4" t="inlineStr">
@@ -15427,7 +15442,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G193" s="4" t="n">
+      <c r="G193" s="7" t="n">
         <v>2013</v>
       </c>
       <c r="H193" s="4" t="inlineStr">
@@ -15508,7 +15523,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G194" s="4" t="n">
+      <c r="G194" s="7" t="n">
         <v>2014</v>
       </c>
       <c r="H194" s="4" t="inlineStr">
@@ -15589,7 +15604,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G195" s="4" t="n">
+      <c r="G195" s="7" t="n">
         <v>2015</v>
       </c>
       <c r="H195" s="4" t="inlineStr">
@@ -15670,7 +15685,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G196" s="4" t="n">
+      <c r="G196" s="7" t="n">
         <v>2016</v>
       </c>
       <c r="H196" s="4" t="inlineStr">
@@ -15751,7 +15766,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G197" s="4" t="n">
+      <c r="G197" s="7" t="n">
         <v>2017</v>
       </c>
       <c r="H197" s="4" t="inlineStr">
@@ -15832,7 +15847,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G198" s="4" t="n">
+      <c r="G198" s="7" t="n">
         <v>2018</v>
       </c>
       <c r="H198" s="4" t="inlineStr">
@@ -15913,7 +15928,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G199" s="4" t="n">
+      <c r="G199" s="7" t="n">
         <v>2019</v>
       </c>
       <c r="H199" s="4" t="inlineStr">
@@ -15994,7 +16009,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G200" s="4" t="n">
+      <c r="G200" s="7" t="n">
         <v>2020</v>
       </c>
       <c r="H200" s="4" t="inlineStr">
@@ -16075,7 +16090,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G201" s="4" t="n">
+      <c r="G201" s="7" t="n">
         <v>2021</v>
       </c>
       <c r="H201" s="4" t="inlineStr">
@@ -16156,7 +16171,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G202" s="4" t="n">
+      <c r="G202" s="7" t="n">
         <v>2022</v>
       </c>
       <c r="H202" s="4" t="inlineStr">
@@ -16237,7 +16252,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G203" s="4" t="n">
+      <c r="G203" s="7" t="n">
         <v>2023</v>
       </c>
       <c r="H203" s="4" t="inlineStr">
@@ -16318,7 +16333,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G204" s="4" t="n">
+      <c r="G204" s="7" t="n">
         <v>2024</v>
       </c>
       <c r="H204" s="4" t="inlineStr">
@@ -16399,7 +16414,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G205" s="4" t="n">
+      <c r="G205" s="7" t="n">
         <v>2025</v>
       </c>
       <c r="H205" s="4" t="inlineStr">
@@ -16480,7 +16495,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G206" s="4" t="n">
+      <c r="G206" s="7" t="n">
         <v>2026</v>
       </c>
       <c r="H206" s="4" t="inlineStr">
@@ -16561,7 +16576,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G207" s="4" t="n">
+      <c r="G207" s="7" t="n">
         <v>1960</v>
       </c>
       <c r="H207" s="4" t="inlineStr">
@@ -16642,7 +16657,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G208" s="4" t="n">
+      <c r="G208" s="7" t="n">
         <v>1961</v>
       </c>
       <c r="H208" s="4" t="inlineStr">
@@ -16723,7 +16738,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G209" s="4" t="n">
+      <c r="G209" s="7" t="n">
         <v>1962</v>
       </c>
       <c r="H209" s="4" t="inlineStr">
@@ -16804,7 +16819,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G210" s="4" t="n">
+      <c r="G210" s="7" t="n">
         <v>1963</v>
       </c>
       <c r="H210" s="4" t="inlineStr">
@@ -16885,7 +16900,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G211" s="4" t="n">
+      <c r="G211" s="7" t="n">
         <v>1964</v>
       </c>
       <c r="H211" s="4" t="inlineStr">
@@ -16966,7 +16981,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G212" s="4" t="n">
+      <c r="G212" s="7" t="n">
         <v>1965</v>
       </c>
       <c r="H212" s="4" t="inlineStr">
@@ -17047,7 +17062,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G213" s="4" t="n">
+      <c r="G213" s="7" t="n">
         <v>1966</v>
       </c>
       <c r="H213" s="4" t="inlineStr">
@@ -17128,7 +17143,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G214" s="4" t="n">
+      <c r="G214" s="7" t="n">
         <v>1967</v>
       </c>
       <c r="H214" s="4" t="inlineStr">
@@ -17209,7 +17224,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G215" s="4" t="n">
+      <c r="G215" s="7" t="n">
         <v>1968</v>
       </c>
       <c r="H215" s="4" t="inlineStr">
@@ -17290,7 +17305,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G216" s="4" t="n">
+      <c r="G216" s="7" t="n">
         <v>1969</v>
       </c>
       <c r="H216" s="4" t="inlineStr">
@@ -17371,7 +17386,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G217" s="4" t="n">
+      <c r="G217" s="7" t="n">
         <v>1970</v>
       </c>
       <c r="H217" s="4" t="inlineStr">
@@ -17452,7 +17467,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G218" s="4" t="n">
+      <c r="G218" s="7" t="n">
         <v>1971</v>
       </c>
       <c r="H218" s="4" t="inlineStr">
@@ -17533,7 +17548,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G219" s="4" t="n">
+      <c r="G219" s="7" t="n">
         <v>1972</v>
       </c>
       <c r="H219" s="4" t="inlineStr">
@@ -17614,7 +17629,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G220" s="4" t="n">
+      <c r="G220" s="7" t="n">
         <v>1973</v>
       </c>
       <c r="H220" s="4" t="inlineStr">
@@ -17695,7 +17710,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G221" s="4" t="n">
+      <c r="G221" s="7" t="n">
         <v>1974</v>
       </c>
       <c r="H221" s="4" t="inlineStr">
@@ -17776,7 +17791,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G222" s="4" t="n">
+      <c r="G222" s="7" t="n">
         <v>1975</v>
       </c>
       <c r="H222" s="4" t="inlineStr">
@@ -17857,7 +17872,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G223" s="4" t="n">
+      <c r="G223" s="7" t="n">
         <v>1976</v>
       </c>
       <c r="H223" s="4" t="inlineStr">
@@ -17938,7 +17953,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G224" s="4" t="n">
+      <c r="G224" s="7" t="n">
         <v>1977</v>
       </c>
       <c r="H224" s="4" t="inlineStr">
@@ -18019,7 +18034,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G225" s="4" t="n">
+      <c r="G225" s="7" t="n">
         <v>1978</v>
       </c>
       <c r="H225" s="4" t="inlineStr">
@@ -18100,7 +18115,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G226" s="4" t="n">
+      <c r="G226" s="7" t="n">
         <v>1979</v>
       </c>
       <c r="H226" s="4" t="inlineStr">
@@ -18181,7 +18196,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G227" s="4" t="n">
+      <c r="G227" s="7" t="n">
         <v>1980</v>
       </c>
       <c r="H227" s="4" t="inlineStr">
@@ -18262,7 +18277,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G228" s="4" t="n">
+      <c r="G228" s="7" t="n">
         <v>1981</v>
       </c>
       <c r="H228" s="4" t="inlineStr">
@@ -18343,7 +18358,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G229" s="4" t="n">
+      <c r="G229" s="7" t="n">
         <v>1982</v>
       </c>
       <c r="H229" s="4" t="inlineStr">
@@ -18424,7 +18439,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G230" s="4" t="n">
+      <c r="G230" s="7" t="n">
         <v>1983</v>
       </c>
       <c r="H230" s="4" t="inlineStr">
@@ -18505,7 +18520,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G231" s="4" t="n">
+      <c r="G231" s="7" t="n">
         <v>1984</v>
       </c>
       <c r="H231" s="4" t="inlineStr">
@@ -18586,7 +18601,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G232" s="4" t="n">
+      <c r="G232" s="7" t="n">
         <v>1985</v>
       </c>
       <c r="H232" s="4" t="inlineStr">
@@ -18667,7 +18682,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G233" s="4" t="n">
+      <c r="G233" s="7" t="n">
         <v>1986</v>
       </c>
       <c r="H233" s="4" t="inlineStr">
@@ -18748,7 +18763,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G234" s="4" t="n">
+      <c r="G234" s="7" t="n">
         <v>1987</v>
       </c>
       <c r="H234" s="4" t="inlineStr">
@@ -18829,7 +18844,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G235" s="4" t="n">
+      <c r="G235" s="7" t="n">
         <v>1988</v>
       </c>
       <c r="H235" s="4" t="inlineStr">
@@ -18910,7 +18925,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G236" s="4" t="n">
+      <c r="G236" s="7" t="n">
         <v>1989</v>
       </c>
       <c r="H236" s="4" t="inlineStr">
@@ -18991,7 +19006,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G237" s="4" t="n">
+      <c r="G237" s="7" t="n">
         <v>1990</v>
       </c>
       <c r="H237" s="4" t="inlineStr">
@@ -19072,7 +19087,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G238" s="4" t="n">
+      <c r="G238" s="7" t="n">
         <v>1991</v>
       </c>
       <c r="H238" s="4" t="inlineStr">
@@ -19153,7 +19168,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G239" s="4" t="n">
+      <c r="G239" s="7" t="n">
         <v>1992</v>
       </c>
       <c r="H239" s="4" t="inlineStr">
@@ -19234,7 +19249,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G240" s="4" t="n">
+      <c r="G240" s="7" t="n">
         <v>1993</v>
       </c>
       <c r="H240" s="4" t="inlineStr">
@@ -19315,7 +19330,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G241" s="4" t="n">
+      <c r="G241" s="7" t="n">
         <v>1994</v>
       </c>
       <c r="H241" s="4" t="inlineStr">
@@ -19396,7 +19411,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G242" s="4" t="n">
+      <c r="G242" s="7" t="n">
         <v>1995</v>
       </c>
       <c r="H242" s="4" t="inlineStr">
@@ -19477,7 +19492,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G243" s="4" t="n">
+      <c r="G243" s="7" t="n">
         <v>1996</v>
       </c>
       <c r="H243" s="4" t="inlineStr">
@@ -19558,7 +19573,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G244" s="4" t="n">
+      <c r="G244" s="7" t="n">
         <v>1997</v>
       </c>
       <c r="H244" s="4" t="inlineStr">
@@ -19639,7 +19654,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G245" s="4" t="n">
+      <c r="G245" s="7" t="n">
         <v>1998</v>
       </c>
       <c r="H245" s="4" t="inlineStr">
@@ -19720,7 +19735,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G246" s="4" t="n">
+      <c r="G246" s="7" t="n">
         <v>1999</v>
       </c>
       <c r="H246" s="4" t="inlineStr">
@@ -19801,7 +19816,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G247" s="4" t="n">
+      <c r="G247" s="7" t="n">
         <v>2000</v>
       </c>
       <c r="H247" s="4" t="inlineStr">
@@ -19882,7 +19897,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G248" s="4" t="n">
+      <c r="G248" s="7" t="n">
         <v>2001</v>
       </c>
       <c r="H248" s="4" t="inlineStr">
@@ -19963,7 +19978,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G249" s="4" t="n">
+      <c r="G249" s="7" t="n">
         <v>2002</v>
       </c>
       <c r="H249" s="4" t="inlineStr">
@@ -20044,7 +20059,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G250" s="4" t="n">
+      <c r="G250" s="7" t="n">
         <v>2003</v>
       </c>
       <c r="H250" s="4" t="inlineStr">
@@ -20125,7 +20140,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G251" s="4" t="n">
+      <c r="G251" s="7" t="n">
         <v>2004</v>
       </c>
       <c r="H251" s="4" t="inlineStr">
@@ -20206,7 +20221,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G252" s="4" t="n">
+      <c r="G252" s="7" t="n">
         <v>2005</v>
       </c>
       <c r="H252" s="4" t="inlineStr">
@@ -20287,7 +20302,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G253" s="4" t="n">
+      <c r="G253" s="7" t="n">
         <v>2006</v>
       </c>
       <c r="H253" s="4" t="inlineStr">
@@ -20368,7 +20383,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G254" s="4" t="n">
+      <c r="G254" s="7" t="n">
         <v>2007</v>
       </c>
       <c r="H254" s="4" t="inlineStr">
@@ -20449,7 +20464,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G255" s="4" t="n">
+      <c r="G255" s="7" t="n">
         <v>2008</v>
       </c>
       <c r="H255" s="4" t="inlineStr">
@@ -20530,7 +20545,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G256" s="4" t="n">
+      <c r="G256" s="7" t="n">
         <v>2009</v>
       </c>
       <c r="H256" s="4" t="inlineStr">
@@ -20611,7 +20626,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G257" s="4" t="n">
+      <c r="G257" s="7" t="n">
         <v>2010</v>
       </c>
       <c r="H257" s="4" t="inlineStr">
@@ -20692,7 +20707,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G258" s="4" t="n">
+      <c r="G258" s="7" t="n">
         <v>2011</v>
       </c>
       <c r="H258" s="4" t="inlineStr">
@@ -20773,7 +20788,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G259" s="4" t="n">
+      <c r="G259" s="7" t="n">
         <v>2012</v>
       </c>
       <c r="H259" s="4" t="inlineStr">
@@ -20854,7 +20869,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G260" s="4" t="n">
+      <c r="G260" s="7" t="n">
         <v>2013</v>
       </c>
       <c r="H260" s="4" t="inlineStr">
@@ -20935,7 +20950,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G261" s="4" t="n">
+      <c r="G261" s="7" t="n">
         <v>2014</v>
       </c>
       <c r="H261" s="4" t="inlineStr">
@@ -21016,7 +21031,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G262" s="4" t="n">
+      <c r="G262" s="7" t="n">
         <v>2015</v>
       </c>
       <c r="H262" s="4" t="inlineStr">
@@ -21097,7 +21112,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G263" s="4" t="n">
+      <c r="G263" s="7" t="n">
         <v>2016</v>
       </c>
       <c r="H263" s="4" t="inlineStr">
@@ -21178,7 +21193,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G264" s="4" t="n">
+      <c r="G264" s="7" t="n">
         <v>2017</v>
       </c>
       <c r="H264" s="4" t="inlineStr">
@@ -21259,7 +21274,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G265" s="4" t="n">
+      <c r="G265" s="7" t="n">
         <v>2018</v>
       </c>
       <c r="H265" s="4" t="inlineStr">
@@ -21340,7 +21355,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G266" s="4" t="n">
+      <c r="G266" s="7" t="n">
         <v>2019</v>
       </c>
       <c r="H266" s="4" t="inlineStr">
@@ -21421,7 +21436,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G267" s="4" t="n">
+      <c r="G267" s="7" t="n">
         <v>2020</v>
       </c>
       <c r="H267" s="4" t="inlineStr">
@@ -21502,7 +21517,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G268" s="4" t="n">
+      <c r="G268" s="7" t="n">
         <v>2021</v>
       </c>
       <c r="H268" s="4" t="inlineStr">
@@ -21583,7 +21598,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G269" s="4" t="n">
+      <c r="G269" s="7" t="n">
         <v>2022</v>
       </c>
       <c r="H269" s="4" t="inlineStr">
@@ -21664,7 +21679,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G270" s="4" t="n">
+      <c r="G270" s="7" t="n">
         <v>2023</v>
       </c>
       <c r="H270" s="4" t="inlineStr">
@@ -21745,7 +21760,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G271" s="4" t="n">
+      <c r="G271" s="7" t="n">
         <v>2024</v>
       </c>
       <c r="H271" s="4" t="inlineStr">
@@ -21826,7 +21841,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G272" s="4" t="n">
+      <c r="G272" s="7" t="n">
         <v>2025</v>
       </c>
       <c r="H272" s="4" t="inlineStr">
@@ -21907,7 +21922,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G273" s="4" t="n">
+      <c r="G273" s="7" t="n">
         <v>2026</v>
       </c>
       <c r="H273" s="4" t="inlineStr">
@@ -21988,7 +22003,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G274" s="4" t="n">
+      <c r="G274" s="7" t="n">
         <v>1960</v>
       </c>
       <c r="H274" s="4" t="inlineStr">
@@ -22065,7 +22080,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G275" s="4" t="n">
+      <c r="G275" s="7" t="n">
         <v>1961</v>
       </c>
       <c r="H275" s="4" t="inlineStr">
@@ -22142,7 +22157,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G276" s="4" t="n">
+      <c r="G276" s="7" t="n">
         <v>1962</v>
       </c>
       <c r="H276" s="4" t="inlineStr">
@@ -22219,7 +22234,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G277" s="4" t="n">
+      <c r="G277" s="7" t="n">
         <v>1963</v>
       </c>
       <c r="H277" s="4" t="inlineStr">
@@ -22296,7 +22311,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G278" s="4" t="n">
+      <c r="G278" s="7" t="n">
         <v>1964</v>
       </c>
       <c r="H278" s="4" t="inlineStr">
@@ -22373,7 +22388,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G279" s="4" t="n">
+      <c r="G279" s="7" t="n">
         <v>1965</v>
       </c>
       <c r="H279" s="4" t="inlineStr">
@@ -22450,7 +22465,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G280" s="4" t="n">
+      <c r="G280" s="7" t="n">
         <v>1966</v>
       </c>
       <c r="H280" s="4" t="inlineStr">
@@ -22527,7 +22542,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G281" s="4" t="n">
+      <c r="G281" s="7" t="n">
         <v>1967</v>
       </c>
       <c r="H281" s="4" t="inlineStr">
@@ -22604,7 +22619,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G282" s="4" t="n">
+      <c r="G282" s="7" t="n">
         <v>1968</v>
       </c>
       <c r="H282" s="4" t="inlineStr">
@@ -22681,7 +22696,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G283" s="4" t="n">
+      <c r="G283" s="7" t="n">
         <v>1969</v>
       </c>
       <c r="H283" s="4" t="inlineStr">
@@ -22758,7 +22773,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G284" s="4" t="n">
+      <c r="G284" s="7" t="n">
         <v>1970</v>
       </c>
       <c r="H284" s="4" t="inlineStr">
@@ -22791,7 +22806,7 @@
           <t>Gasto público en educación como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N284" s="4" t="n">
+      <c r="N284" s="8" t="n">
         <v>4.16286993026733</v>
       </c>
       <c r="O284" s="4" t="inlineStr">
@@ -22837,7 +22852,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G285" s="4" t="n">
+      <c r="G285" s="7" t="n">
         <v>1971</v>
       </c>
       <c r="H285" s="4" t="inlineStr">
@@ -22870,7 +22885,7 @@
           <t>Gasto público en educación como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N285" s="4" t="n">
+      <c r="N285" s="8" t="n">
         <v>4.1799201965332</v>
       </c>
       <c r="O285" s="4" t="inlineStr">
@@ -22916,7 +22931,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G286" s="4" t="n">
+      <c r="G286" s="7" t="n">
         <v>1972</v>
       </c>
       <c r="H286" s="4" t="inlineStr">
@@ -22949,7 +22964,7 @@
           <t>Gasto público en educación como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N286" s="4" t="n">
+      <c r="N286" s="8" t="n">
         <v>4.83728981018066</v>
       </c>
       <c r="O286" s="4" t="inlineStr">
@@ -22995,7 +23010,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G287" s="4" t="n">
+      <c r="G287" s="7" t="n">
         <v>1973</v>
       </c>
       <c r="H287" s="4" t="inlineStr">
@@ -23072,7 +23087,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G288" s="4" t="n">
+      <c r="G288" s="7" t="n">
         <v>1974</v>
       </c>
       <c r="H288" s="4" t="inlineStr">
@@ -23105,7 +23120,7 @@
           <t>Gasto público en educación como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N288" s="4" t="n">
+      <c r="N288" s="8" t="n">
         <v>3.94795989990234</v>
       </c>
       <c r="O288" s="4" t="inlineStr">
@@ -23151,7 +23166,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G289" s="4" t="n">
+      <c r="G289" s="7" t="n">
         <v>1975</v>
       </c>
       <c r="H289" s="4" t="inlineStr">
@@ -23184,7 +23199,7 @@
           <t>Gasto público en educación como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N289" s="4" t="n">
+      <c r="N289" s="8" t="n">
         <v>5.19851016998291</v>
       </c>
       <c r="O289" s="4" t="inlineStr">
@@ -23230,7 +23245,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G290" s="4" t="n">
+      <c r="G290" s="7" t="n">
         <v>1976</v>
       </c>
       <c r="H290" s="4" t="inlineStr">
@@ -23307,7 +23322,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G291" s="4" t="n">
+      <c r="G291" s="7" t="n">
         <v>1977</v>
       </c>
       <c r="H291" s="4" t="inlineStr">
@@ -23340,7 +23355,7 @@
           <t>Gasto público en educación como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N291" s="4" t="n">
+      <c r="N291" s="8" t="n">
         <v>5.25665998458862</v>
       </c>
       <c r="O291" s="4" t="inlineStr">
@@ -23386,7 +23401,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G292" s="4" t="n">
+      <c r="G292" s="7" t="n">
         <v>1978</v>
       </c>
       <c r="H292" s="4" t="inlineStr">
@@ -23463,7 +23478,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G293" s="4" t="n">
+      <c r="G293" s="7" t="n">
         <v>1979</v>
       </c>
       <c r="H293" s="4" t="inlineStr">
@@ -23540,7 +23555,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G294" s="4" t="n">
+      <c r="G294" s="7" t="n">
         <v>1980</v>
       </c>
       <c r="H294" s="4" t="inlineStr">
@@ -23573,7 +23588,7 @@
           <t>Gasto público en educación como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N294" s="4" t="n">
+      <c r="N294" s="8" t="n">
         <v>4.40072011947632</v>
       </c>
       <c r="O294" s="4" t="inlineStr">
@@ -23619,7 +23634,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G295" s="4" t="n">
+      <c r="G295" s="7" t="n">
         <v>1981</v>
       </c>
       <c r="H295" s="4" t="inlineStr">
@@ -23652,7 +23667,7 @@
           <t>Gasto público en educación como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N295" s="4" t="n">
+      <c r="N295" s="8" t="n">
         <v>5.18743991851807</v>
       </c>
       <c r="O295" s="4" t="inlineStr">
@@ -23698,7 +23713,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G296" s="4" t="n">
+      <c r="G296" s="7" t="n">
         <v>1982</v>
       </c>
       <c r="H296" s="4" t="inlineStr">
@@ -23731,7 +23746,7 @@
           <t>Gasto público en educación como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N296" s="4" t="n">
+      <c r="N296" s="8" t="n">
         <v>5.00895023345947</v>
       </c>
       <c r="O296" s="4" t="inlineStr">
@@ -23777,7 +23792,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G297" s="4" t="n">
+      <c r="G297" s="7" t="n">
         <v>1983</v>
       </c>
       <c r="H297" s="4" t="inlineStr">
@@ -23810,7 +23825,7 @@
           <t>Gasto público en educación como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N297" s="4" t="n">
+      <c r="N297" s="8" t="n">
         <v>6.0598201751709</v>
       </c>
       <c r="O297" s="4" t="inlineStr">
@@ -23856,7 +23871,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G298" s="4" t="n">
+      <c r="G298" s="7" t="n">
         <v>1984</v>
       </c>
       <c r="H298" s="4" t="inlineStr">
@@ -23889,7 +23904,7 @@
           <t>Gasto público en educación como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N298" s="4" t="n">
+      <c r="N298" s="8" t="n">
         <v>4.06372976303101</v>
       </c>
       <c r="O298" s="4" t="inlineStr">
@@ -23935,7 +23950,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G299" s="4" t="n">
+      <c r="G299" s="7" t="n">
         <v>1985</v>
       </c>
       <c r="H299" s="4" t="inlineStr">
@@ -24012,7 +24027,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G300" s="4" t="n">
+      <c r="G300" s="7" t="n">
         <v>1986</v>
       </c>
       <c r="H300" s="4" t="inlineStr">
@@ -24089,7 +24104,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G301" s="4" t="n">
+      <c r="G301" s="7" t="n">
         <v>1987</v>
       </c>
       <c r="H301" s="4" t="inlineStr">
@@ -24122,7 +24137,7 @@
           <t>Gasto público en educación como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N301" s="4" t="n">
+      <c r="N301" s="8" t="n">
         <v>3.92751002311706</v>
       </c>
       <c r="O301" s="4" t="inlineStr">
@@ -24168,7 +24183,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G302" s="4" t="n">
+      <c r="G302" s="7" t="n">
         <v>1988</v>
       </c>
       <c r="H302" s="4" t="inlineStr">
@@ -24201,7 +24216,7 @@
           <t>Gasto público en educación como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N302" s="4" t="n">
+      <c r="N302" s="8" t="n">
         <v>3.62941002845764</v>
       </c>
       <c r="O302" s="4" t="inlineStr">
@@ -24247,7 +24262,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G303" s="4" t="n">
+      <c r="G303" s="7" t="n">
         <v>1989</v>
       </c>
       <c r="H303" s="4" t="inlineStr">
@@ -24324,7 +24339,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G304" s="4" t="n">
+      <c r="G304" s="7" t="n">
         <v>1990</v>
       </c>
       <c r="H304" s="4" t="inlineStr">
@@ -24357,7 +24372,7 @@
           <t>Gasto público en educación como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N304" s="4" t="n">
+      <c r="N304" s="8" t="n">
         <v>2.44671010971069</v>
       </c>
       <c r="O304" s="4" t="inlineStr">
@@ -24403,7 +24418,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G305" s="4" t="n">
+      <c r="G305" s="7" t="n">
         <v>1991</v>
       </c>
       <c r="H305" s="4" t="inlineStr">
@@ -24480,7 +24495,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G306" s="4" t="n">
+      <c r="G306" s="7" t="n">
         <v>1992</v>
       </c>
       <c r="H306" s="4" t="inlineStr">
@@ -24513,7 +24528,7 @@
           <t>Gasto público en educación como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N306" s="4" t="n">
+      <c r="N306" s="8" t="n">
         <v>4.31067991256714</v>
       </c>
       <c r="O306" s="4" t="inlineStr">
@@ -24559,7 +24574,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G307" s="4" t="n">
+      <c r="G307" s="7" t="n">
         <v>1993</v>
       </c>
       <c r="H307" s="4" t="inlineStr">
@@ -24592,7 +24607,7 @@
           <t>Gasto público en educación como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N307" s="4" t="n">
+      <c r="N307" s="8" t="n">
         <v>3.81783008575439</v>
       </c>
       <c r="O307" s="4" t="inlineStr">
@@ -24638,7 +24653,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G308" s="4" t="n">
+      <c r="G308" s="7" t="n">
         <v>1994</v>
       </c>
       <c r="H308" s="4" t="inlineStr">
@@ -24671,7 +24686,7 @@
           <t>Gasto público en educación como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N308" s="4" t="n">
+      <c r="N308" s="8" t="n">
         <v>5.00603008270264</v>
       </c>
       <c r="O308" s="4" t="inlineStr">
@@ -24717,7 +24732,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G309" s="4" t="n">
+      <c r="G309" s="7" t="n">
         <v>1995</v>
       </c>
       <c r="H309" s="4" t="inlineStr">
@@ -24794,7 +24809,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G310" s="4" t="n">
+      <c r="G310" s="7" t="n">
         <v>1996</v>
       </c>
       <c r="H310" s="4" t="inlineStr">
@@ -24871,7 +24886,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G311" s="4" t="n">
+      <c r="G311" s="7" t="n">
         <v>1997</v>
       </c>
       <c r="H311" s="4" t="inlineStr">
@@ -24948,7 +24963,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G312" s="4" t="n">
+      <c r="G312" s="7" t="n">
         <v>1998</v>
       </c>
       <c r="H312" s="4" t="inlineStr">
@@ -25025,7 +25040,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G313" s="4" t="n">
+      <c r="G313" s="7" t="n">
         <v>1999</v>
       </c>
       <c r="H313" s="4" t="inlineStr">
@@ -25102,7 +25117,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G314" s="4" t="n">
+      <c r="G314" s="7" t="n">
         <v>2000</v>
       </c>
       <c r="H314" s="4" t="inlineStr">
@@ -25179,7 +25194,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G315" s="4" t="n">
+      <c r="G315" s="7" t="n">
         <v>2001</v>
       </c>
       <c r="H315" s="4" t="inlineStr">
@@ -25256,7 +25271,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G316" s="4" t="n">
+      <c r="G316" s="7" t="n">
         <v>2002</v>
       </c>
       <c r="H316" s="4" t="inlineStr">
@@ -25333,7 +25348,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G317" s="4" t="n">
+      <c r="G317" s="7" t="n">
         <v>2003</v>
       </c>
       <c r="H317" s="4" t="inlineStr">
@@ -25410,7 +25425,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G318" s="4" t="n">
+      <c r="G318" s="7" t="n">
         <v>2004</v>
       </c>
       <c r="H318" s="4" t="inlineStr">
@@ -25487,7 +25502,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G319" s="4" t="n">
+      <c r="G319" s="7" t="n">
         <v>2005</v>
       </c>
       <c r="H319" s="4" t="inlineStr">
@@ -25564,7 +25579,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G320" s="4" t="n">
+      <c r="G320" s="7" t="n">
         <v>2006</v>
       </c>
       <c r="H320" s="4" t="inlineStr">
@@ -25597,7 +25612,7 @@
           <t>Gasto público en educación como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N320" s="4" t="n">
+      <c r="N320" s="8" t="n">
         <v>3.66905999183655</v>
       </c>
       <c r="O320" s="4" t="inlineStr">
@@ -25643,7 +25658,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G321" s="4" t="n">
+      <c r="G321" s="7" t="n">
         <v>2007</v>
       </c>
       <c r="H321" s="4" t="inlineStr">
@@ -25676,7 +25691,7 @@
           <t>Gasto público en educación como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N321" s="4" t="n">
+      <c r="N321" s="8" t="n">
         <v>3.62732005119324</v>
       </c>
       <c r="O321" s="4" t="inlineStr">
@@ -25722,7 +25737,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G322" s="4" t="n">
+      <c r="G322" s="7" t="n">
         <v>2008</v>
       </c>
       <c r="H322" s="4" t="inlineStr">
@@ -25799,7 +25814,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G323" s="4" t="n">
+      <c r="G323" s="7" t="n">
         <v>2009</v>
       </c>
       <c r="H323" s="4" t="inlineStr">
@@ -25832,7 +25847,7 @@
           <t>Gasto público en educación como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N323" s="4" t="n">
+      <c r="N323" s="8" t="n">
         <v>6.87467002868652</v>
       </c>
       <c r="O323" s="4" t="inlineStr">
@@ -25878,7 +25893,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G324" s="4" t="n">
+      <c r="G324" s="7" t="n">
         <v>2010</v>
       </c>
       <c r="H324" s="4" t="inlineStr">
@@ -25955,7 +25970,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G325" s="4" t="n">
+      <c r="G325" s="7" t="n">
         <v>2011</v>
       </c>
       <c r="H325" s="4" t="inlineStr">
@@ -26032,7 +26047,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G326" s="4" t="n">
+      <c r="G326" s="7" t="n">
         <v>2012</v>
       </c>
       <c r="H326" s="4" t="inlineStr">
@@ -26109,7 +26124,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G327" s="4" t="n">
+      <c r="G327" s="7" t="n">
         <v>2013</v>
       </c>
       <c r="H327" s="4" t="inlineStr">
@@ -26186,7 +26201,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G328" s="4" t="n">
+      <c r="G328" s="7" t="n">
         <v>2014</v>
       </c>
       <c r="H328" s="4" t="inlineStr">
@@ -26263,7 +26278,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G329" s="4" t="n">
+      <c r="G329" s="7" t="n">
         <v>2015</v>
       </c>
       <c r="H329" s="4" t="inlineStr">
@@ -26340,7 +26355,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G330" s="4" t="n">
+      <c r="G330" s="7" t="n">
         <v>2016</v>
       </c>
       <c r="H330" s="4" t="inlineStr">
@@ -26417,7 +26432,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G331" s="4" t="n">
+      <c r="G331" s="7" t="n">
         <v>2017</v>
       </c>
       <c r="H331" s="4" t="inlineStr">
@@ -26494,7 +26509,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G332" s="4" t="n">
+      <c r="G332" s="7" t="n">
         <v>2018</v>
       </c>
       <c r="H332" s="4" t="inlineStr">
@@ -26571,7 +26586,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G333" s="4" t="n">
+      <c r="G333" s="7" t="n">
         <v>2019</v>
       </c>
       <c r="H333" s="4" t="inlineStr">
@@ -26648,7 +26663,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G334" s="4" t="n">
+      <c r="G334" s="7" t="n">
         <v>2020</v>
       </c>
       <c r="H334" s="4" t="inlineStr">
@@ -26725,7 +26740,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G335" s="4" t="n">
+      <c r="G335" s="7" t="n">
         <v>2021</v>
       </c>
       <c r="H335" s="4" t="inlineStr">
@@ -26802,7 +26817,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G336" s="4" t="n">
+      <c r="G336" s="7" t="n">
         <v>2022</v>
       </c>
       <c r="H336" s="4" t="inlineStr">
@@ -26879,7 +26894,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G337" s="4" t="n">
+      <c r="G337" s="7" t="n">
         <v>2023</v>
       </c>
       <c r="H337" s="4" t="inlineStr">
@@ -26956,7 +26971,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G338" s="4" t="n">
+      <c r="G338" s="7" t="n">
         <v>2024</v>
       </c>
       <c r="H338" s="4" t="inlineStr">
@@ -27033,7 +27048,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G339" s="4" t="n">
+      <c r="G339" s="7" t="n">
         <v>2025</v>
       </c>
       <c r="H339" s="4" t="inlineStr">
@@ -27169,7 +27184,7 @@
           <t>Número de indicadores</t>
         </is>
       </c>
-      <c r="B10" s="4" t="n">
+      <c r="B10" s="7" t="n">
         <v>5</v>
       </c>
     </row>
@@ -27179,7 +27194,7 @@
           <t>Número de registros</t>
         </is>
       </c>
-      <c r="B11" s="4" t="n">
+      <c r="B11" s="7" t="n">
         <v>333</v>
       </c>
     </row>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_educacion.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_educacion.xlsx
@@ -715,7 +715,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -792,7 +792,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -869,7 +869,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -946,7 +946,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1485,7 +1485,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1947,7 +1947,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2024,7 +2024,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2255,7 +2255,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2334,7 +2334,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2411,7 +2411,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2642,7 +2642,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2719,7 +2719,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2796,7 +2796,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2873,7 +2873,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3106,7 +3106,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3183,7 +3183,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3260,7 +3260,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3337,7 +3337,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3414,7 +3414,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3491,7 +3491,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3568,7 +3568,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3645,7 +3645,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3722,7 +3722,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3799,7 +3799,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4032,7 +4032,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4109,7 +4109,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4267,7 +4267,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4346,7 +4346,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4425,7 +4425,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4504,7 +4504,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4583,7 +4583,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4662,7 +4662,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4741,7 +4741,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4895,7 +4895,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -4974,7 +4974,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5053,7 +5053,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5132,7 +5132,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5209,7 +5209,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5363,7 +5363,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5440,7 +5440,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5517,7 +5517,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5594,7 +5594,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5671,7 +5671,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5748,7 +5748,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5825,7 +5825,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -5902,7 +5902,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -5979,7 +5979,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6056,7 +6056,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6133,7 +6133,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6210,7 +6210,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6287,7 +6287,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6364,7 +6364,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6441,7 +6441,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6518,7 +6518,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6595,7 +6595,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6674,7 +6674,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6753,7 +6753,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6832,7 +6832,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -6911,7 +6911,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -6990,7 +6990,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7148,7 +7148,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7227,7 +7227,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7306,7 +7306,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7385,7 +7385,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7464,7 +7464,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7543,7 +7543,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7622,7 +7622,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7701,7 +7701,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7780,7 +7780,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7859,7 +7859,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -8017,7 +8017,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8096,7 +8096,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8175,7 +8175,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8254,7 +8254,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8333,7 +8333,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8412,7 +8412,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8489,7 +8489,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8566,7 +8566,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8645,7 +8645,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8724,7 +8724,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8801,7 +8801,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -8880,7 +8880,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -8959,7 +8959,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -9038,7 +9038,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9117,7 +9117,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9196,7 +9196,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9275,7 +9275,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9354,7 +9354,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9433,7 +9433,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9512,7 +9512,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9591,7 +9591,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9670,7 +9670,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9749,7 +9749,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9828,7 +9828,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -9907,7 +9907,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -9986,7 +9986,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10065,7 +10065,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10144,7 +10144,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10223,7 +10223,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10302,7 +10302,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10379,7 +10379,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10456,7 +10456,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10533,7 +10533,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10610,7 +10610,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10689,7 +10689,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10768,7 +10768,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10847,7 +10847,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -10924,7 +10924,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -11001,7 +11001,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11078,7 +11078,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11155,7 +11155,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11232,7 +11232,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11309,7 +11309,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11386,7 +11386,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11463,7 +11463,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11540,7 +11540,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11617,7 +11617,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11694,7 +11694,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11771,7 +11771,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11850,7 +11850,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -11929,7 +11929,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -12008,7 +12008,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12087,7 +12087,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12245,7 +12245,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12324,7 +12324,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12403,7 +12403,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12482,7 +12482,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12561,7 +12561,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12640,7 +12640,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12719,7 +12719,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12798,7 +12798,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -12877,7 +12877,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -12956,7 +12956,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -13035,7 +13035,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13114,7 +13114,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13193,7 +13193,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13351,7 +13351,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13430,7 +13430,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13509,7 +13509,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13588,7 +13588,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13665,7 +13665,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13742,7 +13742,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13819,7 +13819,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -13896,7 +13896,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -13973,7 +13973,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -14052,7 +14052,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14131,7 +14131,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14210,7 +14210,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14289,7 +14289,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14368,7 +14368,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14447,7 +14447,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14526,7 +14526,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14605,7 +14605,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14684,7 +14684,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14763,7 +14763,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -14842,7 +14842,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -14921,7 +14921,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -15000,7 +15000,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -15079,7 +15079,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15158,7 +15158,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15237,7 +15237,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15316,7 +15316,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15395,7 +15395,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15474,7 +15474,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15551,7 +15551,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15628,7 +15628,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15705,7 +15705,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15782,7 +15782,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -15861,7 +15861,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -15940,7 +15940,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -16019,7 +16019,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -16096,7 +16096,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16173,7 +16173,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16250,7 +16250,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16327,7 +16327,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16404,7 +16404,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16481,7 +16481,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16558,7 +16558,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16635,7 +16635,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16712,7 +16712,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16789,7 +16789,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -16866,7 +16866,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -16943,7 +16943,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -17022,7 +17022,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -17101,7 +17101,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17180,7 +17180,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17259,7 +17259,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17338,7 +17338,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17417,7 +17417,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17494,7 +17494,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17573,7 +17573,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17652,7 +17652,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17731,7 +17731,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17810,7 +17810,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -17889,7 +17889,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -17968,7 +17968,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -18047,7 +18047,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -18126,7 +18126,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18205,7 +18205,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18284,7 +18284,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18363,7 +18363,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18442,7 +18442,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18521,7 +18521,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18600,7 +18600,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18679,7 +18679,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18756,7 +18756,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18833,7 +18833,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -18910,7 +18910,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -18987,7 +18987,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -19064,7 +19064,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -19141,7 +19141,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19218,7 +19218,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19297,7 +19297,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19374,7 +19374,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19453,7 +19453,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19532,7 +19532,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19611,7 +19611,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19688,7 +19688,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19765,7 +19765,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -19842,7 +19842,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -19921,7 +19921,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -20000,7 +20000,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -20077,7 +20077,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -20154,7 +20154,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20231,7 +20231,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20308,7 +20308,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20385,7 +20385,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20462,7 +20462,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20539,7 +20539,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20616,7 +20616,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20693,7 +20693,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20770,7 +20770,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -20847,7 +20847,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -20924,7 +20924,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -21001,7 +21001,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -21078,7 +21078,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -21155,7 +21155,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21232,7 +21232,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21309,7 +21309,7 @@
       </c>
       <c r="P271" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q271" s="4" t="n"/>
@@ -21386,7 +21386,7 @@
       </c>
       <c r="P272" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q272" s="4" t="n"/>
@@ -21463,7 +21463,7 @@
       </c>
       <c r="P273" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q273" s="4" t="n"/>
@@ -21540,7 +21540,7 @@
       </c>
       <c r="P274" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q274" s="4" t="n"/>
@@ -21617,7 +21617,7 @@
       </c>
       <c r="P275" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q275" s="4" t="n"/>
@@ -21694,7 +21694,7 @@
       </c>
       <c r="P276" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q276" s="4" t="n"/>
@@ -21771,7 +21771,7 @@
       </c>
       <c r="P277" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q277" s="4" t="n"/>
@@ -21848,7 +21848,7 @@
       </c>
       <c r="P278" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q278" s="4" t="n"/>
@@ -21925,7 +21925,7 @@
       </c>
       <c r="P279" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q279" s="4" t="n"/>
@@ -22002,7 +22002,7 @@
       </c>
       <c r="P280" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q280" s="4" t="n"/>
@@ -22081,7 +22081,7 @@
       </c>
       <c r="P281" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q281" s="4" t="n"/>
@@ -22160,7 +22160,7 @@
       </c>
       <c r="P282" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q282" s="4" t="n"/>
@@ -22239,7 +22239,7 @@
       </c>
       <c r="P283" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q283" s="4" t="n"/>
@@ -22316,7 +22316,7 @@
       </c>
       <c r="P284" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q284" s="4" t="n"/>
@@ -22395,7 +22395,7 @@
       </c>
       <c r="P285" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q285" s="4" t="n"/>
@@ -22474,7 +22474,7 @@
       </c>
       <c r="P286" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q286" s="4" t="n"/>
@@ -22551,7 +22551,7 @@
       </c>
       <c r="P287" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q287" s="4" t="n"/>
@@ -22630,7 +22630,7 @@
       </c>
       <c r="P288" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q288" s="4" t="n"/>
@@ -22707,7 +22707,7 @@
       </c>
       <c r="P289" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q289" s="4" t="n"/>
@@ -22784,7 +22784,7 @@
       </c>
       <c r="P290" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q290" s="4" t="n"/>
@@ -22863,7 +22863,7 @@
       </c>
       <c r="P291" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q291" s="4" t="n"/>
@@ -22942,7 +22942,7 @@
       </c>
       <c r="P292" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q292" s="4" t="n"/>
@@ -23021,7 +23021,7 @@
       </c>
       <c r="P293" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q293" s="4" t="n"/>
@@ -23100,7 +23100,7 @@
       </c>
       <c r="P294" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q294" s="4" t="n"/>
@@ -23179,7 +23179,7 @@
       </c>
       <c r="P295" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q295" s="4" t="n"/>
@@ -23256,7 +23256,7 @@
       </c>
       <c r="P296" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q296" s="4" t="n"/>
@@ -23333,7 +23333,7 @@
       </c>
       <c r="P297" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q297" s="4" t="n"/>
@@ -23412,7 +23412,7 @@
       </c>
       <c r="P298" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q298" s="4" t="n"/>
@@ -23491,7 +23491,7 @@
       </c>
       <c r="P299" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q299" s="4" t="n"/>
@@ -23568,7 +23568,7 @@
       </c>
       <c r="P300" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q300" s="4" t="n"/>
@@ -23647,7 +23647,7 @@
       </c>
       <c r="P301" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q301" s="4" t="n"/>
@@ -23724,7 +23724,7 @@
       </c>
       <c r="P302" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q302" s="4" t="n"/>
@@ -23803,7 +23803,7 @@
       </c>
       <c r="P303" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q303" s="4" t="n"/>
@@ -23882,7 +23882,7 @@
       </c>
       <c r="P304" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q304" s="4" t="n"/>
@@ -23961,7 +23961,7 @@
       </c>
       <c r="P305" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q305" s="4" t="n"/>
@@ -24038,7 +24038,7 @@
       </c>
       <c r="P306" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q306" s="4" t="n"/>
@@ -24115,7 +24115,7 @@
       </c>
       <c r="P307" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q307" s="4" t="n"/>
@@ -24192,7 +24192,7 @@
       </c>
       <c r="P308" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q308" s="4" t="n"/>
@@ -24269,7 +24269,7 @@
       </c>
       <c r="P309" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q309" s="4" t="n"/>
@@ -24346,7 +24346,7 @@
       </c>
       <c r="P310" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q310" s="4" t="n"/>
@@ -24423,7 +24423,7 @@
       </c>
       <c r="P311" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q311" s="4" t="n"/>
@@ -24500,7 +24500,7 @@
       </c>
       <c r="P312" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q312" s="4" t="n"/>
@@ -24577,7 +24577,7 @@
       </c>
       <c r="P313" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q313" s="4" t="n"/>
@@ -24654,7 +24654,7 @@
       </c>
       <c r="P314" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q314" s="4" t="n"/>
@@ -24731,7 +24731,7 @@
       </c>
       <c r="P315" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q315" s="4" t="n"/>
@@ -24808,7 +24808,7 @@
       </c>
       <c r="P316" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q316" s="4" t="n"/>
@@ -24887,7 +24887,7 @@
       </c>
       <c r="P317" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q317" s="4" t="n"/>
@@ -24966,7 +24966,7 @@
       </c>
       <c r="P318" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q318" s="4" t="n"/>
@@ -25043,7 +25043,7 @@
       </c>
       <c r="P319" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q319" s="4" t="n"/>
@@ -25122,7 +25122,7 @@
       </c>
       <c r="P320" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q320" s="4" t="n"/>
@@ -25199,7 +25199,7 @@
       </c>
       <c r="P321" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q321" s="4" t="n"/>
@@ -25276,7 +25276,7 @@
       </c>
       <c r="P322" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q322" s="4" t="n"/>
@@ -25353,7 +25353,7 @@
       </c>
       <c r="P323" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q323" s="4" t="n"/>
@@ -25430,7 +25430,7 @@
       </c>
       <c r="P324" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q324" s="4" t="n"/>
@@ -25507,7 +25507,7 @@
       </c>
       <c r="P325" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q325" s="4" t="n"/>
@@ -25584,7 +25584,7 @@
       </c>
       <c r="P326" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q326" s="4" t="n"/>
@@ -25661,7 +25661,7 @@
       </c>
       <c r="P327" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q327" s="4" t="n"/>
@@ -25738,7 +25738,7 @@
       </c>
       <c r="P328" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q328" s="4" t="n"/>
@@ -25815,7 +25815,7 @@
       </c>
       <c r="P329" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q329" s="4" t="n"/>
@@ -25892,7 +25892,7 @@
       </c>
       <c r="P330" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q330" s="4" t="n"/>
@@ -25969,7 +25969,7 @@
       </c>
       <c r="P331" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q331" s="4" t="n"/>
@@ -26046,7 +26046,7 @@
       </c>
       <c r="P332" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q332" s="4" t="n"/>
@@ -26123,7 +26123,7 @@
       </c>
       <c r="P333" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q333" s="4" t="n"/>
@@ -26200,7 +26200,7 @@
       </c>
       <c r="P334" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q334" s="4" t="n"/>
@@ -26277,7 +26277,7 @@
       </c>
       <c r="P335" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q335" s="4" t="n"/>
@@ -26354,7 +26354,7 @@
       </c>
       <c r="P336" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q336" s="4" t="n"/>
@@ -26439,7 +26439,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_educacion.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_educacion.xlsx
@@ -715,7 +715,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -792,7 +792,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -869,7 +869,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -946,7 +946,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1485,7 +1485,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1947,7 +1947,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2024,7 +2024,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2255,7 +2255,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2334,7 +2334,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2411,7 +2411,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2642,7 +2642,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2719,7 +2719,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2796,7 +2796,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2873,7 +2873,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3106,7 +3106,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3183,7 +3183,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3260,7 +3260,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3337,7 +3337,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3414,7 +3414,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3491,7 +3491,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3568,7 +3568,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3645,7 +3645,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3722,7 +3722,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3799,7 +3799,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4032,7 +4032,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4109,7 +4109,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4267,7 +4267,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4346,7 +4346,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4425,7 +4425,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4504,7 +4504,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4583,7 +4583,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4662,7 +4662,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4741,7 +4741,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4895,7 +4895,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -4974,7 +4974,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5053,7 +5053,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5132,7 +5132,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5209,7 +5209,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5363,7 +5363,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5440,7 +5440,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5517,7 +5517,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5594,7 +5594,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5671,7 +5671,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5748,7 +5748,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5825,7 +5825,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -5902,7 +5902,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -5979,7 +5979,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6056,7 +6056,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6133,7 +6133,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6210,7 +6210,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6287,7 +6287,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6364,7 +6364,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6441,7 +6441,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6518,7 +6518,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6595,7 +6595,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6674,7 +6674,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6753,7 +6753,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6832,7 +6832,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -6911,7 +6911,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -6990,7 +6990,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7148,7 +7148,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7227,7 +7227,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7306,7 +7306,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7385,7 +7385,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7464,7 +7464,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7543,7 +7543,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7622,7 +7622,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7701,7 +7701,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7780,7 +7780,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7859,7 +7859,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -8017,7 +8017,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8096,7 +8096,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8175,7 +8175,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8254,7 +8254,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8333,7 +8333,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8412,7 +8412,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8489,7 +8489,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8566,7 +8566,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8645,7 +8645,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8724,7 +8724,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8801,7 +8801,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -8880,7 +8880,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -8959,7 +8959,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -9038,7 +9038,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9117,7 +9117,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9196,7 +9196,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9275,7 +9275,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9354,7 +9354,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9433,7 +9433,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9512,7 +9512,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9591,7 +9591,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9670,7 +9670,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9749,7 +9749,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9828,7 +9828,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -9907,7 +9907,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -9986,7 +9986,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10065,7 +10065,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10144,7 +10144,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10223,7 +10223,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10302,7 +10302,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10379,7 +10379,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10456,7 +10456,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10533,7 +10533,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10610,7 +10610,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10689,7 +10689,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10768,7 +10768,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10847,7 +10847,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -10924,7 +10924,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -11001,7 +11001,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11078,7 +11078,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11155,7 +11155,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11232,7 +11232,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11309,7 +11309,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11386,7 +11386,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11463,7 +11463,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11540,7 +11540,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11617,7 +11617,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11694,7 +11694,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11771,7 +11771,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11850,7 +11850,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -11929,7 +11929,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -12008,7 +12008,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12087,7 +12087,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12245,7 +12245,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12324,7 +12324,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12403,7 +12403,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12482,7 +12482,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12561,7 +12561,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12640,7 +12640,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12719,7 +12719,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12798,7 +12798,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -12877,7 +12877,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -12956,7 +12956,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -13035,7 +13035,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13114,7 +13114,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13193,7 +13193,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13351,7 +13351,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13430,7 +13430,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13509,7 +13509,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13588,7 +13588,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13665,7 +13665,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13742,7 +13742,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13819,7 +13819,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -13896,7 +13896,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -13973,7 +13973,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -14052,7 +14052,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14131,7 +14131,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14210,7 +14210,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14289,7 +14289,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14368,7 +14368,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14447,7 +14447,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14526,7 +14526,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14605,7 +14605,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14684,7 +14684,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14763,7 +14763,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -14842,7 +14842,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -14921,7 +14921,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -15000,7 +15000,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -15079,7 +15079,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15158,7 +15158,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15237,7 +15237,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15316,7 +15316,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15395,7 +15395,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15474,7 +15474,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15551,7 +15551,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15628,7 +15628,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15705,7 +15705,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15782,7 +15782,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -15861,7 +15861,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -15940,7 +15940,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -16019,7 +16019,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -16096,7 +16096,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16173,7 +16173,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16250,7 +16250,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16327,7 +16327,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16404,7 +16404,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16481,7 +16481,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16558,7 +16558,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16635,7 +16635,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16712,7 +16712,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16789,7 +16789,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -16866,7 +16866,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -16943,7 +16943,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -17022,7 +17022,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -17101,7 +17101,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17180,7 +17180,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17259,7 +17259,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17338,7 +17338,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17417,7 +17417,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17494,7 +17494,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17573,7 +17573,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17652,7 +17652,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17731,7 +17731,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17810,7 +17810,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -17889,7 +17889,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -17968,7 +17968,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -18047,7 +18047,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -18126,7 +18126,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18205,7 +18205,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18284,7 +18284,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18363,7 +18363,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18442,7 +18442,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18521,7 +18521,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18600,7 +18600,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18679,7 +18679,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18756,7 +18756,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18833,7 +18833,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -18910,7 +18910,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -18987,7 +18987,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -19064,7 +19064,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -19141,7 +19141,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19218,7 +19218,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19297,7 +19297,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19374,7 +19374,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19453,7 +19453,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19532,7 +19532,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19611,7 +19611,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19688,7 +19688,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19765,7 +19765,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -19842,7 +19842,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -19921,7 +19921,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -20000,7 +20000,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -20077,7 +20077,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -20154,7 +20154,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20231,7 +20231,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20308,7 +20308,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20385,7 +20385,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20462,7 +20462,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20539,7 +20539,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20616,7 +20616,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20693,7 +20693,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20770,7 +20770,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -20847,7 +20847,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -20924,7 +20924,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -21001,7 +21001,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -21078,7 +21078,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -21155,7 +21155,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21232,7 +21232,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21309,7 +21309,7 @@
       </c>
       <c r="P271" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q271" s="4" t="n"/>
@@ -21386,7 +21386,7 @@
       </c>
       <c r="P272" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q272" s="4" t="n"/>
@@ -21463,7 +21463,7 @@
       </c>
       <c r="P273" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q273" s="4" t="n"/>
@@ -21540,7 +21540,7 @@
       </c>
       <c r="P274" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q274" s="4" t="n"/>
@@ -21617,7 +21617,7 @@
       </c>
       <c r="P275" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q275" s="4" t="n"/>
@@ -21694,7 +21694,7 @@
       </c>
       <c r="P276" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q276" s="4" t="n"/>
@@ -21771,7 +21771,7 @@
       </c>
       <c r="P277" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q277" s="4" t="n"/>
@@ -21848,7 +21848,7 @@
       </c>
       <c r="P278" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q278" s="4" t="n"/>
@@ -21925,7 +21925,7 @@
       </c>
       <c r="P279" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q279" s="4" t="n"/>
@@ -22002,7 +22002,7 @@
       </c>
       <c r="P280" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q280" s="4" t="n"/>
@@ -22081,7 +22081,7 @@
       </c>
       <c r="P281" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q281" s="4" t="n"/>
@@ -22160,7 +22160,7 @@
       </c>
       <c r="P282" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q282" s="4" t="n"/>
@@ -22239,7 +22239,7 @@
       </c>
       <c r="P283" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q283" s="4" t="n"/>
@@ -22316,7 +22316,7 @@
       </c>
       <c r="P284" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q284" s="4" t="n"/>
@@ -22395,7 +22395,7 @@
       </c>
       <c r="P285" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q285" s="4" t="n"/>
@@ -22474,7 +22474,7 @@
       </c>
       <c r="P286" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q286" s="4" t="n"/>
@@ -22551,7 +22551,7 @@
       </c>
       <c r="P287" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q287" s="4" t="n"/>
@@ -22630,7 +22630,7 @@
       </c>
       <c r="P288" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q288" s="4" t="n"/>
@@ -22707,7 +22707,7 @@
       </c>
       <c r="P289" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q289" s="4" t="n"/>
@@ -22784,7 +22784,7 @@
       </c>
       <c r="P290" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q290" s="4" t="n"/>
@@ -22863,7 +22863,7 @@
       </c>
       <c r="P291" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q291" s="4" t="n"/>
@@ -22942,7 +22942,7 @@
       </c>
       <c r="P292" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q292" s="4" t="n"/>
@@ -23021,7 +23021,7 @@
       </c>
       <c r="P293" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q293" s="4" t="n"/>
@@ -23100,7 +23100,7 @@
       </c>
       <c r="P294" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q294" s="4" t="n"/>
@@ -23179,7 +23179,7 @@
       </c>
       <c r="P295" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q295" s="4" t="n"/>
@@ -23256,7 +23256,7 @@
       </c>
       <c r="P296" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q296" s="4" t="n"/>
@@ -23333,7 +23333,7 @@
       </c>
       <c r="P297" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q297" s="4" t="n"/>
@@ -23412,7 +23412,7 @@
       </c>
       <c r="P298" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q298" s="4" t="n"/>
@@ -23491,7 +23491,7 @@
       </c>
       <c r="P299" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q299" s="4" t="n"/>
@@ -23568,7 +23568,7 @@
       </c>
       <c r="P300" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q300" s="4" t="n"/>
@@ -23647,7 +23647,7 @@
       </c>
       <c r="P301" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q301" s="4" t="n"/>
@@ -23724,7 +23724,7 @@
       </c>
       <c r="P302" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q302" s="4" t="n"/>
@@ -23803,7 +23803,7 @@
       </c>
       <c r="P303" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q303" s="4" t="n"/>
@@ -23882,7 +23882,7 @@
       </c>
       <c r="P304" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q304" s="4" t="n"/>
@@ -23961,7 +23961,7 @@
       </c>
       <c r="P305" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q305" s="4" t="n"/>
@@ -24038,7 +24038,7 @@
       </c>
       <c r="P306" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q306" s="4" t="n"/>
@@ -24115,7 +24115,7 @@
       </c>
       <c r="P307" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q307" s="4" t="n"/>
@@ -24192,7 +24192,7 @@
       </c>
       <c r="P308" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q308" s="4" t="n"/>
@@ -24269,7 +24269,7 @@
       </c>
       <c r="P309" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q309" s="4" t="n"/>
@@ -24346,7 +24346,7 @@
       </c>
       <c r="P310" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q310" s="4" t="n"/>
@@ -24423,7 +24423,7 @@
       </c>
       <c r="P311" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q311" s="4" t="n"/>
@@ -24500,7 +24500,7 @@
       </c>
       <c r="P312" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q312" s="4" t="n"/>
@@ -24577,7 +24577,7 @@
       </c>
       <c r="P313" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q313" s="4" t="n"/>
@@ -24654,7 +24654,7 @@
       </c>
       <c r="P314" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q314" s="4" t="n"/>
@@ -24731,7 +24731,7 @@
       </c>
       <c r="P315" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q315" s="4" t="n"/>
@@ -24808,7 +24808,7 @@
       </c>
       <c r="P316" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q316" s="4" t="n"/>
@@ -24887,7 +24887,7 @@
       </c>
       <c r="P317" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q317" s="4" t="n"/>
@@ -24966,7 +24966,7 @@
       </c>
       <c r="P318" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q318" s="4" t="n"/>
@@ -25043,7 +25043,7 @@
       </c>
       <c r="P319" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q319" s="4" t="n"/>
@@ -25122,7 +25122,7 @@
       </c>
       <c r="P320" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q320" s="4" t="n"/>
@@ -25199,7 +25199,7 @@
       </c>
       <c r="P321" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q321" s="4" t="n"/>
@@ -25276,7 +25276,7 @@
       </c>
       <c r="P322" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q322" s="4" t="n"/>
@@ -25353,7 +25353,7 @@
       </c>
       <c r="P323" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q323" s="4" t="n"/>
@@ -25430,7 +25430,7 @@
       </c>
       <c r="P324" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q324" s="4" t="n"/>
@@ -25507,7 +25507,7 @@
       </c>
       <c r="P325" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q325" s="4" t="n"/>
@@ -25584,7 +25584,7 @@
       </c>
       <c r="P326" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q326" s="4" t="n"/>
@@ -25661,7 +25661,7 @@
       </c>
       <c r="P327" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q327" s="4" t="n"/>
@@ -25738,7 +25738,7 @@
       </c>
       <c r="P328" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q328" s="4" t="n"/>
@@ -25815,7 +25815,7 @@
       </c>
       <c r="P329" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q329" s="4" t="n"/>
@@ -25892,7 +25892,7 @@
       </c>
       <c r="P330" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q330" s="4" t="n"/>
@@ -25969,7 +25969,7 @@
       </c>
       <c r="P331" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q331" s="4" t="n"/>
@@ -26046,7 +26046,7 @@
       </c>
       <c r="P332" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q332" s="4" t="n"/>
@@ -26123,7 +26123,7 @@
       </c>
       <c r="P333" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q333" s="4" t="n"/>
@@ -26200,7 +26200,7 @@
       </c>
       <c r="P334" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q334" s="4" t="n"/>
@@ -26277,7 +26277,7 @@
       </c>
       <c r="P335" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q335" s="4" t="n"/>
@@ -26354,7 +26354,7 @@
       </c>
       <c r="P336" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q336" s="4" t="n"/>
@@ -26439,7 +26439,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_educacion.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_educacion.xlsx
@@ -715,7 +715,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -792,7 +792,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -869,7 +869,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -946,7 +946,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1485,7 +1485,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1947,7 +1947,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2024,7 +2024,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2255,7 +2255,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2334,7 +2334,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2411,7 +2411,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2642,7 +2642,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2719,7 +2719,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2796,7 +2796,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2873,7 +2873,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3106,7 +3106,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3183,7 +3183,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3260,7 +3260,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3337,7 +3337,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3414,7 +3414,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3491,7 +3491,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3568,7 +3568,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3645,7 +3645,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3722,7 +3722,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3799,7 +3799,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4032,7 +4032,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4109,7 +4109,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4267,7 +4267,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4346,7 +4346,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4425,7 +4425,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4504,7 +4504,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4583,7 +4583,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4662,7 +4662,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4741,7 +4741,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4895,7 +4895,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -4974,7 +4974,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5053,7 +5053,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5132,7 +5132,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5209,7 +5209,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5363,7 +5363,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5440,7 +5440,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5517,7 +5517,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5594,7 +5594,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5671,7 +5671,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5748,7 +5748,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5825,7 +5825,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -5902,7 +5902,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -5979,7 +5979,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6056,7 +6056,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6133,7 +6133,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6210,7 +6210,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6287,7 +6287,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6364,7 +6364,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6441,7 +6441,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6518,7 +6518,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6595,7 +6595,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6674,7 +6674,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6753,7 +6753,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6832,7 +6832,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -6911,7 +6911,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -6990,7 +6990,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7148,7 +7148,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7227,7 +7227,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7306,7 +7306,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7385,7 +7385,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7464,7 +7464,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7543,7 +7543,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7622,7 +7622,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7701,7 +7701,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7780,7 +7780,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7859,7 +7859,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -8017,7 +8017,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8096,7 +8096,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8175,7 +8175,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8254,7 +8254,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8333,7 +8333,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8412,7 +8412,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8489,7 +8489,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8566,7 +8566,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8645,7 +8645,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8724,7 +8724,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8801,7 +8801,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -8880,7 +8880,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -8959,7 +8959,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -9038,7 +9038,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9117,7 +9117,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9196,7 +9196,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9275,7 +9275,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9354,7 +9354,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9433,7 +9433,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9512,7 +9512,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9591,7 +9591,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9670,7 +9670,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9749,7 +9749,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9828,7 +9828,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -9907,7 +9907,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -9986,7 +9986,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10065,7 +10065,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10144,7 +10144,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10223,7 +10223,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10302,7 +10302,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10379,7 +10379,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10456,7 +10456,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10533,7 +10533,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10610,7 +10610,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10689,7 +10689,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10768,7 +10768,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10847,7 +10847,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -10924,7 +10924,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -11001,7 +11001,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11078,7 +11078,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11155,7 +11155,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11232,7 +11232,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11309,7 +11309,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11386,7 +11386,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11463,7 +11463,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11540,7 +11540,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11617,7 +11617,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11694,7 +11694,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11771,7 +11771,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11850,7 +11850,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -11929,7 +11929,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -12008,7 +12008,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12087,7 +12087,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12245,7 +12245,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12324,7 +12324,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12403,7 +12403,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12482,7 +12482,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12561,7 +12561,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12640,7 +12640,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12719,7 +12719,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12798,7 +12798,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -12877,7 +12877,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -12956,7 +12956,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -13035,7 +13035,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13114,7 +13114,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13193,7 +13193,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13351,7 +13351,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13430,7 +13430,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13509,7 +13509,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13588,7 +13588,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13665,7 +13665,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13742,7 +13742,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13819,7 +13819,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -13896,7 +13896,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -13973,7 +13973,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -14052,7 +14052,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14131,7 +14131,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14210,7 +14210,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14289,7 +14289,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14368,7 +14368,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14447,7 +14447,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14526,7 +14526,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14605,7 +14605,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14684,7 +14684,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14763,7 +14763,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -14842,7 +14842,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -14921,7 +14921,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -15000,7 +15000,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -15079,7 +15079,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15158,7 +15158,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15237,7 +15237,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15316,7 +15316,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15395,7 +15395,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15474,7 +15474,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15551,7 +15551,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15628,7 +15628,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15705,7 +15705,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15782,7 +15782,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -15861,7 +15861,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -15940,7 +15940,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -16019,7 +16019,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -16096,7 +16096,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16173,7 +16173,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16250,7 +16250,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16327,7 +16327,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16404,7 +16404,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16481,7 +16481,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16558,7 +16558,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16635,7 +16635,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16712,7 +16712,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16789,7 +16789,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -16866,7 +16866,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -16943,7 +16943,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -17022,7 +17022,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -17101,7 +17101,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17180,7 +17180,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17259,7 +17259,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17338,7 +17338,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17417,7 +17417,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17494,7 +17494,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17573,7 +17573,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17652,7 +17652,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17731,7 +17731,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17810,7 +17810,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -17889,7 +17889,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -17968,7 +17968,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -18047,7 +18047,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -18126,7 +18126,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18205,7 +18205,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18284,7 +18284,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18363,7 +18363,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18442,7 +18442,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18521,7 +18521,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18600,7 +18600,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18679,7 +18679,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18756,7 +18756,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18833,7 +18833,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -18910,7 +18910,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -18987,7 +18987,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -19064,7 +19064,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -19141,7 +19141,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19218,7 +19218,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19297,7 +19297,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19374,7 +19374,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19453,7 +19453,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19532,7 +19532,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19611,7 +19611,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19688,7 +19688,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19765,7 +19765,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -19842,7 +19842,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -19921,7 +19921,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -20000,7 +20000,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -20077,7 +20077,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -20154,7 +20154,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20231,7 +20231,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20308,7 +20308,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20385,7 +20385,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20462,7 +20462,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20539,7 +20539,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20616,7 +20616,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20693,7 +20693,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20770,7 +20770,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -20847,7 +20847,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -20924,7 +20924,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -21001,7 +21001,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -21078,7 +21078,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -21155,7 +21155,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21232,7 +21232,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21309,7 +21309,7 @@
       </c>
       <c r="P271" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q271" s="4" t="n"/>
@@ -21386,7 +21386,7 @@
       </c>
       <c r="P272" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q272" s="4" t="n"/>
@@ -21463,7 +21463,7 @@
       </c>
       <c r="P273" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q273" s="4" t="n"/>
@@ -21540,7 +21540,7 @@
       </c>
       <c r="P274" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q274" s="4" t="n"/>
@@ -21617,7 +21617,7 @@
       </c>
       <c r="P275" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q275" s="4" t="n"/>
@@ -21694,7 +21694,7 @@
       </c>
       <c r="P276" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q276" s="4" t="n"/>
@@ -21771,7 +21771,7 @@
       </c>
       <c r="P277" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q277" s="4" t="n"/>
@@ -21848,7 +21848,7 @@
       </c>
       <c r="P278" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q278" s="4" t="n"/>
@@ -21925,7 +21925,7 @@
       </c>
       <c r="P279" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q279" s="4" t="n"/>
@@ -22002,7 +22002,7 @@
       </c>
       <c r="P280" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q280" s="4" t="n"/>
@@ -22081,7 +22081,7 @@
       </c>
       <c r="P281" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q281" s="4" t="n"/>
@@ -22160,7 +22160,7 @@
       </c>
       <c r="P282" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q282" s="4" t="n"/>
@@ -22239,7 +22239,7 @@
       </c>
       <c r="P283" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q283" s="4" t="n"/>
@@ -22316,7 +22316,7 @@
       </c>
       <c r="P284" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q284" s="4" t="n"/>
@@ -22395,7 +22395,7 @@
       </c>
       <c r="P285" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q285" s="4" t="n"/>
@@ -22474,7 +22474,7 @@
       </c>
       <c r="P286" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q286" s="4" t="n"/>
@@ -22551,7 +22551,7 @@
       </c>
       <c r="P287" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q287" s="4" t="n"/>
@@ -22630,7 +22630,7 @@
       </c>
       <c r="P288" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q288" s="4" t="n"/>
@@ -22707,7 +22707,7 @@
       </c>
       <c r="P289" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q289" s="4" t="n"/>
@@ -22784,7 +22784,7 @@
       </c>
       <c r="P290" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q290" s="4" t="n"/>
@@ -22863,7 +22863,7 @@
       </c>
       <c r="P291" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q291" s="4" t="n"/>
@@ -22942,7 +22942,7 @@
       </c>
       <c r="P292" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q292" s="4" t="n"/>
@@ -23021,7 +23021,7 @@
       </c>
       <c r="P293" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q293" s="4" t="n"/>
@@ -23100,7 +23100,7 @@
       </c>
       <c r="P294" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q294" s="4" t="n"/>
@@ -23179,7 +23179,7 @@
       </c>
       <c r="P295" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q295" s="4" t="n"/>
@@ -23256,7 +23256,7 @@
       </c>
       <c r="P296" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q296" s="4" t="n"/>
@@ -23333,7 +23333,7 @@
       </c>
       <c r="P297" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q297" s="4" t="n"/>
@@ -23412,7 +23412,7 @@
       </c>
       <c r="P298" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q298" s="4" t="n"/>
@@ -23491,7 +23491,7 @@
       </c>
       <c r="P299" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q299" s="4" t="n"/>
@@ -23568,7 +23568,7 @@
       </c>
       <c r="P300" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q300" s="4" t="n"/>
@@ -23647,7 +23647,7 @@
       </c>
       <c r="P301" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q301" s="4" t="n"/>
@@ -23724,7 +23724,7 @@
       </c>
       <c r="P302" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q302" s="4" t="n"/>
@@ -23803,7 +23803,7 @@
       </c>
       <c r="P303" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q303" s="4" t="n"/>
@@ -23882,7 +23882,7 @@
       </c>
       <c r="P304" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q304" s="4" t="n"/>
@@ -23961,7 +23961,7 @@
       </c>
       <c r="P305" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q305" s="4" t="n"/>
@@ -24038,7 +24038,7 @@
       </c>
       <c r="P306" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q306" s="4" t="n"/>
@@ -24115,7 +24115,7 @@
       </c>
       <c r="P307" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q307" s="4" t="n"/>
@@ -24192,7 +24192,7 @@
       </c>
       <c r="P308" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q308" s="4" t="n"/>
@@ -24269,7 +24269,7 @@
       </c>
       <c r="P309" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q309" s="4" t="n"/>
@@ -24346,7 +24346,7 @@
       </c>
       <c r="P310" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q310" s="4" t="n"/>
@@ -24423,7 +24423,7 @@
       </c>
       <c r="P311" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q311" s="4" t="n"/>
@@ -24500,7 +24500,7 @@
       </c>
       <c r="P312" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q312" s="4" t="n"/>
@@ -24577,7 +24577,7 @@
       </c>
       <c r="P313" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q313" s="4" t="n"/>
@@ -24654,7 +24654,7 @@
       </c>
       <c r="P314" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q314" s="4" t="n"/>
@@ -24731,7 +24731,7 @@
       </c>
       <c r="P315" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q315" s="4" t="n"/>
@@ -24808,7 +24808,7 @@
       </c>
       <c r="P316" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q316" s="4" t="n"/>
@@ -24887,7 +24887,7 @@
       </c>
       <c r="P317" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q317" s="4" t="n"/>
@@ -24966,7 +24966,7 @@
       </c>
       <c r="P318" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q318" s="4" t="n"/>
@@ -25043,7 +25043,7 @@
       </c>
       <c r="P319" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q319" s="4" t="n"/>
@@ -25122,7 +25122,7 @@
       </c>
       <c r="P320" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q320" s="4" t="n"/>
@@ -25199,7 +25199,7 @@
       </c>
       <c r="P321" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q321" s="4" t="n"/>
@@ -25276,7 +25276,7 @@
       </c>
       <c r="P322" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q322" s="4" t="n"/>
@@ -25353,7 +25353,7 @@
       </c>
       <c r="P323" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q323" s="4" t="n"/>
@@ -25430,7 +25430,7 @@
       </c>
       <c r="P324" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q324" s="4" t="n"/>
@@ -25507,7 +25507,7 @@
       </c>
       <c r="P325" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q325" s="4" t="n"/>
@@ -25584,7 +25584,7 @@
       </c>
       <c r="P326" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q326" s="4" t="n"/>
@@ -25661,7 +25661,7 @@
       </c>
       <c r="P327" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q327" s="4" t="n"/>
@@ -25738,7 +25738,7 @@
       </c>
       <c r="P328" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q328" s="4" t="n"/>
@@ -25815,7 +25815,7 @@
       </c>
       <c r="P329" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q329" s="4" t="n"/>
@@ -25892,7 +25892,7 @@
       </c>
       <c r="P330" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q330" s="4" t="n"/>
@@ -25969,7 +25969,7 @@
       </c>
       <c r="P331" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q331" s="4" t="n"/>
@@ -26046,7 +26046,7 @@
       </c>
       <c r="P332" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q332" s="4" t="n"/>
@@ -26123,7 +26123,7 @@
       </c>
       <c r="P333" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q333" s="4" t="n"/>
@@ -26200,7 +26200,7 @@
       </c>
       <c r="P334" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q334" s="4" t="n"/>
@@ -26277,7 +26277,7 @@
       </c>
       <c r="P335" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q335" s="4" t="n"/>
@@ -26354,7 +26354,7 @@
       </c>
       <c r="P336" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q336" s="4" t="n"/>
@@ -26439,7 +26439,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_educacion.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_educacion.xlsx
@@ -715,7 +715,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -792,7 +792,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -869,7 +869,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -946,7 +946,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1485,7 +1485,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1947,7 +1947,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2024,7 +2024,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2255,7 +2255,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2334,7 +2334,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2411,7 +2411,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2642,7 +2642,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2719,7 +2719,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2796,7 +2796,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2873,7 +2873,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3106,7 +3106,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3183,7 +3183,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3260,7 +3260,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3337,7 +3337,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3414,7 +3414,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3491,7 +3491,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3568,7 +3568,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3645,7 +3645,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3722,7 +3722,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3799,7 +3799,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4032,7 +4032,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4109,7 +4109,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4267,7 +4267,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4346,7 +4346,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4425,7 +4425,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4504,7 +4504,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4583,7 +4583,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4662,7 +4662,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4741,7 +4741,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4895,7 +4895,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -4974,7 +4974,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5053,7 +5053,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5132,7 +5132,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5209,7 +5209,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5363,7 +5363,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5440,7 +5440,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5517,7 +5517,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5594,7 +5594,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5671,7 +5671,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5748,7 +5748,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5825,7 +5825,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -5902,7 +5902,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -5979,7 +5979,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6056,7 +6056,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6133,7 +6133,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6210,7 +6210,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6287,7 +6287,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6364,7 +6364,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6441,7 +6441,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6518,7 +6518,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6595,7 +6595,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6674,7 +6674,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6753,7 +6753,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6832,7 +6832,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -6911,7 +6911,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -6990,7 +6990,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7148,7 +7148,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7227,7 +7227,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7306,7 +7306,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7385,7 +7385,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7464,7 +7464,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7543,7 +7543,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7622,7 +7622,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7701,7 +7701,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7780,7 +7780,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7859,7 +7859,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -8017,7 +8017,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8096,7 +8096,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8175,7 +8175,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8254,7 +8254,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8333,7 +8333,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8412,7 +8412,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8489,7 +8489,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8566,7 +8566,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8645,7 +8645,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8724,7 +8724,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8801,7 +8801,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -8880,7 +8880,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -8959,7 +8959,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -9038,7 +9038,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9117,7 +9117,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9196,7 +9196,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9275,7 +9275,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9354,7 +9354,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9433,7 +9433,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9512,7 +9512,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9591,7 +9591,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9670,7 +9670,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9749,7 +9749,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9828,7 +9828,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -9907,7 +9907,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -9986,7 +9986,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10065,7 +10065,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10144,7 +10144,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10223,7 +10223,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10302,7 +10302,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10379,7 +10379,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10456,7 +10456,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10533,7 +10533,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10610,7 +10610,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10689,7 +10689,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10768,7 +10768,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10847,7 +10847,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -10924,7 +10924,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -11001,7 +11001,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11078,7 +11078,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11155,7 +11155,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11232,7 +11232,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11309,7 +11309,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11386,7 +11386,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11463,7 +11463,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11540,7 +11540,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11617,7 +11617,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11694,7 +11694,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11771,7 +11771,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11850,7 +11850,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -11929,7 +11929,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -12008,7 +12008,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12087,7 +12087,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12245,7 +12245,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12324,7 +12324,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12403,7 +12403,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12482,7 +12482,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12561,7 +12561,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12640,7 +12640,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12719,7 +12719,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12798,7 +12798,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -12877,7 +12877,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -12956,7 +12956,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -13035,7 +13035,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13114,7 +13114,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13193,7 +13193,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13351,7 +13351,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13430,7 +13430,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13509,7 +13509,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13588,7 +13588,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13665,7 +13665,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13742,7 +13742,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13819,7 +13819,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -13896,7 +13896,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -13973,7 +13973,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -14052,7 +14052,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14131,7 +14131,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14210,7 +14210,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14289,7 +14289,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14368,7 +14368,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14447,7 +14447,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14526,7 +14526,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14605,7 +14605,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14684,7 +14684,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14763,7 +14763,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -14842,7 +14842,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -14921,7 +14921,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -15000,7 +15000,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -15079,7 +15079,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15158,7 +15158,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15237,7 +15237,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15316,7 +15316,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15395,7 +15395,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15474,7 +15474,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15551,7 +15551,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15628,7 +15628,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15705,7 +15705,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15782,7 +15782,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -15861,7 +15861,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -15940,7 +15940,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -16019,7 +16019,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -16096,7 +16096,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16173,7 +16173,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16250,7 +16250,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16327,7 +16327,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16404,7 +16404,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16481,7 +16481,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16558,7 +16558,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16635,7 +16635,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16712,7 +16712,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16789,7 +16789,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -16866,7 +16866,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -16943,7 +16943,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -17022,7 +17022,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -17101,7 +17101,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17180,7 +17180,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17259,7 +17259,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17338,7 +17338,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17417,7 +17417,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17494,7 +17494,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17573,7 +17573,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17652,7 +17652,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17731,7 +17731,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17810,7 +17810,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -17889,7 +17889,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -17968,7 +17968,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -18047,7 +18047,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -18126,7 +18126,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18205,7 +18205,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18284,7 +18284,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18363,7 +18363,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18442,7 +18442,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18521,7 +18521,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18600,7 +18600,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18679,7 +18679,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18756,7 +18756,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18833,7 +18833,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -18910,7 +18910,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -18987,7 +18987,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -19064,7 +19064,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -19141,7 +19141,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19218,7 +19218,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19297,7 +19297,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19374,7 +19374,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19453,7 +19453,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19532,7 +19532,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19611,7 +19611,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19688,7 +19688,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19765,7 +19765,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -19842,7 +19842,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -19921,7 +19921,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -20000,7 +20000,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -20077,7 +20077,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -20154,7 +20154,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20231,7 +20231,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20308,7 +20308,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20385,7 +20385,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20462,7 +20462,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20539,7 +20539,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20616,7 +20616,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20693,7 +20693,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20770,7 +20770,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -20847,7 +20847,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -20924,7 +20924,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -21001,7 +21001,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -21078,7 +21078,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -21155,7 +21155,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21232,7 +21232,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21309,7 +21309,7 @@
       </c>
       <c r="P271" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q271" s="4" t="n"/>
@@ -21386,7 +21386,7 @@
       </c>
       <c r="P272" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q272" s="4" t="n"/>
@@ -21463,7 +21463,7 @@
       </c>
       <c r="P273" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q273" s="4" t="n"/>
@@ -21540,7 +21540,7 @@
       </c>
       <c r="P274" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q274" s="4" t="n"/>
@@ -21617,7 +21617,7 @@
       </c>
       <c r="P275" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q275" s="4" t="n"/>
@@ -21694,7 +21694,7 @@
       </c>
       <c r="P276" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q276" s="4" t="n"/>
@@ -21771,7 +21771,7 @@
       </c>
       <c r="P277" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q277" s="4" t="n"/>
@@ -21848,7 +21848,7 @@
       </c>
       <c r="P278" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q278" s="4" t="n"/>
@@ -21925,7 +21925,7 @@
       </c>
       <c r="P279" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q279" s="4" t="n"/>
@@ -22002,7 +22002,7 @@
       </c>
       <c r="P280" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q280" s="4" t="n"/>
@@ -22081,7 +22081,7 @@
       </c>
       <c r="P281" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q281" s="4" t="n"/>
@@ -22160,7 +22160,7 @@
       </c>
       <c r="P282" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q282" s="4" t="n"/>
@@ -22239,7 +22239,7 @@
       </c>
       <c r="P283" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q283" s="4" t="n"/>
@@ -22316,7 +22316,7 @@
       </c>
       <c r="P284" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q284" s="4" t="n"/>
@@ -22395,7 +22395,7 @@
       </c>
       <c r="P285" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q285" s="4" t="n"/>
@@ -22474,7 +22474,7 @@
       </c>
       <c r="P286" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q286" s="4" t="n"/>
@@ -22551,7 +22551,7 @@
       </c>
       <c r="P287" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q287" s="4" t="n"/>
@@ -22630,7 +22630,7 @@
       </c>
       <c r="P288" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q288" s="4" t="n"/>
@@ -22707,7 +22707,7 @@
       </c>
       <c r="P289" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q289" s="4" t="n"/>
@@ -22784,7 +22784,7 @@
       </c>
       <c r="P290" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q290" s="4" t="n"/>
@@ -22863,7 +22863,7 @@
       </c>
       <c r="P291" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q291" s="4" t="n"/>
@@ -22942,7 +22942,7 @@
       </c>
       <c r="P292" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q292" s="4" t="n"/>
@@ -23021,7 +23021,7 @@
       </c>
       <c r="P293" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q293" s="4" t="n"/>
@@ -23100,7 +23100,7 @@
       </c>
       <c r="P294" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q294" s="4" t="n"/>
@@ -23179,7 +23179,7 @@
       </c>
       <c r="P295" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q295" s="4" t="n"/>
@@ -23256,7 +23256,7 @@
       </c>
       <c r="P296" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q296" s="4" t="n"/>
@@ -23333,7 +23333,7 @@
       </c>
       <c r="P297" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q297" s="4" t="n"/>
@@ -23412,7 +23412,7 @@
       </c>
       <c r="P298" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q298" s="4" t="n"/>
@@ -23491,7 +23491,7 @@
       </c>
       <c r="P299" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q299" s="4" t="n"/>
@@ -23568,7 +23568,7 @@
       </c>
       <c r="P300" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q300" s="4" t="n"/>
@@ -23647,7 +23647,7 @@
       </c>
       <c r="P301" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q301" s="4" t="n"/>
@@ -23724,7 +23724,7 @@
       </c>
       <c r="P302" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q302" s="4" t="n"/>
@@ -23803,7 +23803,7 @@
       </c>
       <c r="P303" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q303" s="4" t="n"/>
@@ -23882,7 +23882,7 @@
       </c>
       <c r="P304" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q304" s="4" t="n"/>
@@ -23961,7 +23961,7 @@
       </c>
       <c r="P305" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q305" s="4" t="n"/>
@@ -24038,7 +24038,7 @@
       </c>
       <c r="P306" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q306" s="4" t="n"/>
@@ -24115,7 +24115,7 @@
       </c>
       <c r="P307" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q307" s="4" t="n"/>
@@ -24192,7 +24192,7 @@
       </c>
       <c r="P308" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q308" s="4" t="n"/>
@@ -24269,7 +24269,7 @@
       </c>
       <c r="P309" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q309" s="4" t="n"/>
@@ -24346,7 +24346,7 @@
       </c>
       <c r="P310" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q310" s="4" t="n"/>
@@ -24423,7 +24423,7 @@
       </c>
       <c r="P311" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q311" s="4" t="n"/>
@@ -24500,7 +24500,7 @@
       </c>
       <c r="P312" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q312" s="4" t="n"/>
@@ -24577,7 +24577,7 @@
       </c>
       <c r="P313" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q313" s="4" t="n"/>
@@ -24654,7 +24654,7 @@
       </c>
       <c r="P314" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q314" s="4" t="n"/>
@@ -24731,7 +24731,7 @@
       </c>
       <c r="P315" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q315" s="4" t="n"/>
@@ -24808,7 +24808,7 @@
       </c>
       <c r="P316" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q316" s="4" t="n"/>
@@ -24887,7 +24887,7 @@
       </c>
       <c r="P317" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q317" s="4" t="n"/>
@@ -24966,7 +24966,7 @@
       </c>
       <c r="P318" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q318" s="4" t="n"/>
@@ -25043,7 +25043,7 @@
       </c>
       <c r="P319" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q319" s="4" t="n"/>
@@ -25122,7 +25122,7 @@
       </c>
       <c r="P320" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q320" s="4" t="n"/>
@@ -25199,7 +25199,7 @@
       </c>
       <c r="P321" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q321" s="4" t="n"/>
@@ -25276,7 +25276,7 @@
       </c>
       <c r="P322" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q322" s="4" t="n"/>
@@ -25353,7 +25353,7 @@
       </c>
       <c r="P323" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q323" s="4" t="n"/>
@@ -25430,7 +25430,7 @@
       </c>
       <c r="P324" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q324" s="4" t="n"/>
@@ -25507,7 +25507,7 @@
       </c>
       <c r="P325" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q325" s="4" t="n"/>
@@ -25584,7 +25584,7 @@
       </c>
       <c r="P326" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q326" s="4" t="n"/>
@@ -25661,7 +25661,7 @@
       </c>
       <c r="P327" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q327" s="4" t="n"/>
@@ -25738,7 +25738,7 @@
       </c>
       <c r="P328" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q328" s="4" t="n"/>
@@ -25815,7 +25815,7 @@
       </c>
       <c r="P329" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q329" s="4" t="n"/>
@@ -25892,7 +25892,7 @@
       </c>
       <c r="P330" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q330" s="4" t="n"/>
@@ -25969,7 +25969,7 @@
       </c>
       <c r="P331" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q331" s="4" t="n"/>
@@ -26046,7 +26046,7 @@
       </c>
       <c r="P332" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q332" s="4" t="n"/>
@@ -26123,7 +26123,7 @@
       </c>
       <c r="P333" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q333" s="4" t="n"/>
@@ -26200,7 +26200,7 @@
       </c>
       <c r="P334" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q334" s="4" t="n"/>
@@ -26277,7 +26277,7 @@
       </c>
       <c r="P335" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q335" s="4" t="n"/>
@@ -26354,7 +26354,7 @@
       </c>
       <c r="P336" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q336" s="4" t="n"/>
@@ -26439,7 +26439,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_educacion.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_educacion.xlsx
@@ -715,7 +715,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -792,7 +792,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -869,7 +869,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -946,7 +946,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1485,7 +1485,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1947,7 +1947,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2024,7 +2024,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2255,7 +2255,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2334,7 +2334,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2411,7 +2411,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2642,7 +2642,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2719,7 +2719,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2796,7 +2796,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2873,7 +2873,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3106,7 +3106,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3183,7 +3183,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3260,7 +3260,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3337,7 +3337,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3414,7 +3414,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3491,7 +3491,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3568,7 +3568,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3645,7 +3645,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3722,7 +3722,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3799,7 +3799,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4032,7 +4032,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4109,7 +4109,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4267,7 +4267,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4346,7 +4346,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4425,7 +4425,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4504,7 +4504,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4583,7 +4583,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4662,7 +4662,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4741,7 +4741,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4895,7 +4895,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -4974,7 +4974,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5053,7 +5053,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5132,7 +5132,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5209,7 +5209,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5363,7 +5363,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5440,7 +5440,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5517,7 +5517,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5594,7 +5594,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5671,7 +5671,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5748,7 +5748,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5825,7 +5825,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -5902,7 +5902,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -5979,7 +5979,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6056,7 +6056,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6133,7 +6133,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6210,7 +6210,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6287,7 +6287,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6364,7 +6364,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6441,7 +6441,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6518,7 +6518,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6595,7 +6595,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6674,7 +6674,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6753,7 +6753,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6832,7 +6832,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -6911,7 +6911,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -6990,7 +6990,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7148,7 +7148,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7227,7 +7227,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7306,7 +7306,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7385,7 +7385,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7464,7 +7464,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7543,7 +7543,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7622,7 +7622,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7701,7 +7701,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7780,7 +7780,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7859,7 +7859,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -8017,7 +8017,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8096,7 +8096,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8175,7 +8175,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8254,7 +8254,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8333,7 +8333,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8412,7 +8412,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8489,7 +8489,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8566,7 +8566,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8645,7 +8645,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8724,7 +8724,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8801,7 +8801,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -8880,7 +8880,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -8959,7 +8959,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -9038,7 +9038,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9117,7 +9117,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9196,7 +9196,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9275,7 +9275,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9354,7 +9354,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9433,7 +9433,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9512,7 +9512,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9591,7 +9591,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9670,7 +9670,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9749,7 +9749,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9828,7 +9828,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -9907,7 +9907,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -9986,7 +9986,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10065,7 +10065,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10144,7 +10144,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10223,7 +10223,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10302,7 +10302,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10379,7 +10379,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10456,7 +10456,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10533,7 +10533,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10610,7 +10610,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10689,7 +10689,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10768,7 +10768,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10847,7 +10847,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -10924,7 +10924,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -11001,7 +11001,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11078,7 +11078,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11155,7 +11155,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11232,7 +11232,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11309,7 +11309,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11386,7 +11386,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11463,7 +11463,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11540,7 +11540,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11617,7 +11617,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11694,7 +11694,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11771,7 +11771,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11850,7 +11850,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -11929,7 +11929,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -12008,7 +12008,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12087,7 +12087,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12245,7 +12245,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12324,7 +12324,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12403,7 +12403,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12482,7 +12482,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12561,7 +12561,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12640,7 +12640,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12719,7 +12719,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12798,7 +12798,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -12877,7 +12877,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -12956,7 +12956,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -13035,7 +13035,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13114,7 +13114,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13193,7 +13193,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13351,7 +13351,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13430,7 +13430,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13509,7 +13509,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13588,7 +13588,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13665,7 +13665,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13742,7 +13742,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13819,7 +13819,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -13896,7 +13896,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -13973,7 +13973,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -14052,7 +14052,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14131,7 +14131,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14210,7 +14210,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14289,7 +14289,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14368,7 +14368,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14447,7 +14447,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14526,7 +14526,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14605,7 +14605,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14684,7 +14684,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14763,7 +14763,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -14842,7 +14842,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -14921,7 +14921,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -15000,7 +15000,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -15079,7 +15079,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15158,7 +15158,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15237,7 +15237,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15316,7 +15316,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15395,7 +15395,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15474,7 +15474,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15551,7 +15551,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15628,7 +15628,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15705,7 +15705,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15782,7 +15782,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -15861,7 +15861,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -15940,7 +15940,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -16019,7 +16019,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -16096,7 +16096,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16173,7 +16173,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16250,7 +16250,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16327,7 +16327,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16404,7 +16404,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16481,7 +16481,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16558,7 +16558,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16635,7 +16635,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16712,7 +16712,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16789,7 +16789,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -16866,7 +16866,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -16943,7 +16943,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -17022,7 +17022,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -17101,7 +17101,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17180,7 +17180,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17259,7 +17259,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17338,7 +17338,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17417,7 +17417,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17494,7 +17494,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17573,7 +17573,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17652,7 +17652,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17731,7 +17731,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17810,7 +17810,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -17889,7 +17889,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -17968,7 +17968,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -18047,7 +18047,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -18126,7 +18126,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18205,7 +18205,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18284,7 +18284,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18363,7 +18363,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18442,7 +18442,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18521,7 +18521,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18600,7 +18600,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18679,7 +18679,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18756,7 +18756,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18833,7 +18833,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -18910,7 +18910,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -18987,7 +18987,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -19064,7 +19064,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -19141,7 +19141,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19218,7 +19218,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19297,7 +19297,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19374,7 +19374,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19453,7 +19453,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19532,7 +19532,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19611,7 +19611,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19688,7 +19688,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19765,7 +19765,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -19842,7 +19842,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -19921,7 +19921,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -20000,7 +20000,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -20077,7 +20077,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -20154,7 +20154,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20231,7 +20231,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20308,7 +20308,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20385,7 +20385,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20462,7 +20462,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20539,7 +20539,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20616,7 +20616,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20693,7 +20693,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20770,7 +20770,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -20847,7 +20847,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -20924,7 +20924,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -21001,7 +21001,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -21078,7 +21078,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -21155,7 +21155,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21232,7 +21232,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21309,7 +21309,7 @@
       </c>
       <c r="P271" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q271" s="4" t="n"/>
@@ -21386,7 +21386,7 @@
       </c>
       <c r="P272" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q272" s="4" t="n"/>
@@ -21463,7 +21463,7 @@
       </c>
       <c r="P273" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q273" s="4" t="n"/>
@@ -21540,7 +21540,7 @@
       </c>
       <c r="P274" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q274" s="4" t="n"/>
@@ -21617,7 +21617,7 @@
       </c>
       <c r="P275" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q275" s="4" t="n"/>
@@ -21694,7 +21694,7 @@
       </c>
       <c r="P276" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q276" s="4" t="n"/>
@@ -21771,7 +21771,7 @@
       </c>
       <c r="P277" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q277" s="4" t="n"/>
@@ -21848,7 +21848,7 @@
       </c>
       <c r="P278" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q278" s="4" t="n"/>
@@ -21925,7 +21925,7 @@
       </c>
       <c r="P279" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q279" s="4" t="n"/>
@@ -22002,7 +22002,7 @@
       </c>
       <c r="P280" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q280" s="4" t="n"/>
@@ -22081,7 +22081,7 @@
       </c>
       <c r="P281" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q281" s="4" t="n"/>
@@ -22160,7 +22160,7 @@
       </c>
       <c r="P282" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q282" s="4" t="n"/>
@@ -22239,7 +22239,7 @@
       </c>
       <c r="P283" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q283" s="4" t="n"/>
@@ -22316,7 +22316,7 @@
       </c>
       <c r="P284" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q284" s="4" t="n"/>
@@ -22395,7 +22395,7 @@
       </c>
       <c r="P285" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q285" s="4" t="n"/>
@@ -22474,7 +22474,7 @@
       </c>
       <c r="P286" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q286" s="4" t="n"/>
@@ -22551,7 +22551,7 @@
       </c>
       <c r="P287" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q287" s="4" t="n"/>
@@ -22630,7 +22630,7 @@
       </c>
       <c r="P288" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q288" s="4" t="n"/>
@@ -22707,7 +22707,7 @@
       </c>
       <c r="P289" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q289" s="4" t="n"/>
@@ -22784,7 +22784,7 @@
       </c>
       <c r="P290" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q290" s="4" t="n"/>
@@ -22863,7 +22863,7 @@
       </c>
       <c r="P291" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q291" s="4" t="n"/>
@@ -22942,7 +22942,7 @@
       </c>
       <c r="P292" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q292" s="4" t="n"/>
@@ -23021,7 +23021,7 @@
       </c>
       <c r="P293" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q293" s="4" t="n"/>
@@ -23100,7 +23100,7 @@
       </c>
       <c r="P294" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q294" s="4" t="n"/>
@@ -23179,7 +23179,7 @@
       </c>
       <c r="P295" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q295" s="4" t="n"/>
@@ -23256,7 +23256,7 @@
       </c>
       <c r="P296" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q296" s="4" t="n"/>
@@ -23333,7 +23333,7 @@
       </c>
       <c r="P297" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q297" s="4" t="n"/>
@@ -23412,7 +23412,7 @@
       </c>
       <c r="P298" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q298" s="4" t="n"/>
@@ -23491,7 +23491,7 @@
       </c>
       <c r="P299" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q299" s="4" t="n"/>
@@ -23568,7 +23568,7 @@
       </c>
       <c r="P300" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q300" s="4" t="n"/>
@@ -23647,7 +23647,7 @@
       </c>
       <c r="P301" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q301" s="4" t="n"/>
@@ -23724,7 +23724,7 @@
       </c>
       <c r="P302" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q302" s="4" t="n"/>
@@ -23803,7 +23803,7 @@
       </c>
       <c r="P303" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q303" s="4" t="n"/>
@@ -23882,7 +23882,7 @@
       </c>
       <c r="P304" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q304" s="4" t="n"/>
@@ -23961,7 +23961,7 @@
       </c>
       <c r="P305" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q305" s="4" t="n"/>
@@ -24038,7 +24038,7 @@
       </c>
       <c r="P306" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q306" s="4" t="n"/>
@@ -24115,7 +24115,7 @@
       </c>
       <c r="P307" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q307" s="4" t="n"/>
@@ -24192,7 +24192,7 @@
       </c>
       <c r="P308" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q308" s="4" t="n"/>
@@ -24269,7 +24269,7 @@
       </c>
       <c r="P309" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q309" s="4" t="n"/>
@@ -24346,7 +24346,7 @@
       </c>
       <c r="P310" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q310" s="4" t="n"/>
@@ -24423,7 +24423,7 @@
       </c>
       <c r="P311" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q311" s="4" t="n"/>
@@ -24500,7 +24500,7 @@
       </c>
       <c r="P312" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q312" s="4" t="n"/>
@@ -24577,7 +24577,7 @@
       </c>
       <c r="P313" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q313" s="4" t="n"/>
@@ -24654,7 +24654,7 @@
       </c>
       <c r="P314" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q314" s="4" t="n"/>
@@ -24731,7 +24731,7 @@
       </c>
       <c r="P315" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q315" s="4" t="n"/>
@@ -24808,7 +24808,7 @@
       </c>
       <c r="P316" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q316" s="4" t="n"/>
@@ -24887,7 +24887,7 @@
       </c>
       <c r="P317" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q317" s="4" t="n"/>
@@ -24966,7 +24966,7 @@
       </c>
       <c r="P318" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q318" s="4" t="n"/>
@@ -25043,7 +25043,7 @@
       </c>
       <c r="P319" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q319" s="4" t="n"/>
@@ -25122,7 +25122,7 @@
       </c>
       <c r="P320" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q320" s="4" t="n"/>
@@ -25199,7 +25199,7 @@
       </c>
       <c r="P321" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q321" s="4" t="n"/>
@@ -25276,7 +25276,7 @@
       </c>
       <c r="P322" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q322" s="4" t="n"/>
@@ -25353,7 +25353,7 @@
       </c>
       <c r="P323" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q323" s="4" t="n"/>
@@ -25430,7 +25430,7 @@
       </c>
       <c r="P324" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q324" s="4" t="n"/>
@@ -25507,7 +25507,7 @@
       </c>
       <c r="P325" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q325" s="4" t="n"/>
@@ -25584,7 +25584,7 @@
       </c>
       <c r="P326" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q326" s="4" t="n"/>
@@ -25661,7 +25661,7 @@
       </c>
       <c r="P327" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q327" s="4" t="n"/>
@@ -25738,7 +25738,7 @@
       </c>
       <c r="P328" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q328" s="4" t="n"/>
@@ -25815,7 +25815,7 @@
       </c>
       <c r="P329" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q329" s="4" t="n"/>
@@ -25892,7 +25892,7 @@
       </c>
       <c r="P330" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q330" s="4" t="n"/>
@@ -25969,7 +25969,7 @@
       </c>
       <c r="P331" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q331" s="4" t="n"/>
@@ -26046,7 +26046,7 @@
       </c>
       <c r="P332" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q332" s="4" t="n"/>
@@ -26123,7 +26123,7 @@
       </c>
       <c r="P333" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q333" s="4" t="n"/>
@@ -26200,7 +26200,7 @@
       </c>
       <c r="P334" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q334" s="4" t="n"/>
@@ -26277,7 +26277,7 @@
       </c>
       <c r="P335" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q335" s="4" t="n"/>
@@ -26354,7 +26354,7 @@
       </c>
       <c r="P336" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q336" s="4" t="n"/>
@@ -26439,7 +26439,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
     </row>
